--- a/public/Plantilla_Quimica_Bethel_2.0.xlsx
+++ b/public/Plantilla_Quimica_Bethel_2.0.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\facun\Desktop\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E1218050-BCAD-4FFA-8B5B-77BD1FB75206}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BDB9F4EF-D6A5-4A90-BE3A-61278325AC0C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="19440" windowHeight="14880" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-105" yWindow="0" windowWidth="9810" windowHeight="14745" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="PRODUCTOS" sheetId="1" r:id="rId1"/>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3805" uniqueCount="1360">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3811" uniqueCount="1364">
   <si>
     <t>ID</t>
   </si>
@@ -4119,6 +4119,18 @@
   </si>
   <si>
     <t>NO</t>
+  </si>
+  <si>
+    <t>AUT002</t>
+  </si>
+  <si>
+    <t>Esponja</t>
+  </si>
+  <si>
+    <t>Esponja para auto</t>
+  </si>
+  <si>
+    <t>AUT002.jpg</t>
   </si>
 </sst>
 </file>
@@ -7944,15 +7956,36 @@
       <c r="A78" t="s">
         <v>92</v>
       </c>
+      <c r="B78" t="s">
+        <v>1360</v>
+      </c>
+      <c r="C78" t="s">
+        <v>1353</v>
+      </c>
+      <c r="D78" t="s">
+        <v>1361</v>
+      </c>
+      <c r="E78" t="s">
+        <v>1074</v>
+      </c>
       <c r="F78" t="s">
-        <v>1132</v>
+        <v>1362</v>
+      </c>
+      <c r="H78" t="s">
+        <v>1164</v>
+      </c>
+      <c r="I78" t="s">
+        <v>1363</v>
+      </c>
+      <c r="J78">
+        <v>800</v>
       </c>
       <c r="K78">
-        <v>1</v>
-      </c>
-      <c r="L78" t="str">
+        <v>1.7</v>
+      </c>
+      <c r="L78">
         <f t="shared" si="1"/>
-        <v/>
+        <v>2160</v>
       </c>
       <c r="M78" t="s">
         <v>16</v>

--- a/public/Plantilla_Quimica_Bethel_2.0.xlsx
+++ b/public/Plantilla_Quimica_Bethel_2.0.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\facun\Desktop\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BDB9F4EF-D6A5-4A90-BE3A-61278325AC0C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B5C0D174-FD4A-4DC5-AED4-73CCBCD5E57B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-105" yWindow="0" windowWidth="9810" windowHeight="14745" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="19440" windowHeight="14880" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="PRODUCTOS" sheetId="1" r:id="rId1"/>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3811" uniqueCount="1364">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4245" uniqueCount="1537">
   <si>
     <t>ID</t>
   </si>
@@ -4131,6 +4131,525 @@
   </si>
   <si>
     <t>AUT002.jpg</t>
+  </si>
+  <si>
+    <t>AUT003</t>
+  </si>
+  <si>
+    <t>AUT004</t>
+  </si>
+  <si>
+    <t>AUT005</t>
+  </si>
+  <si>
+    <t>AUT006</t>
+  </si>
+  <si>
+    <t>Silicona</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Silicona para auto por litro </t>
+  </si>
+  <si>
+    <t>AUT003.jpg</t>
+  </si>
+  <si>
+    <t>AUT004.jpg</t>
+  </si>
+  <si>
+    <t>AUT005.jpg</t>
+  </si>
+  <si>
+    <t>AUT006.jpg</t>
+  </si>
+  <si>
+    <t>Walker</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Silicona en Aerosol </t>
+  </si>
+  <si>
+    <t>AUT007</t>
+  </si>
+  <si>
+    <t>AUT008</t>
+  </si>
+  <si>
+    <t>AUT009</t>
+  </si>
+  <si>
+    <t>AUT010</t>
+  </si>
+  <si>
+    <t>AUT011</t>
+  </si>
+  <si>
+    <t>AUT012</t>
+  </si>
+  <si>
+    <t>Black</t>
+  </si>
+  <si>
+    <t>Carolina Herrera</t>
+  </si>
+  <si>
+    <t>Frutilla</t>
+  </si>
+  <si>
+    <t>Kenzo</t>
+  </si>
+  <si>
+    <t>Lavanda</t>
+  </si>
+  <si>
+    <t>One Million</t>
+  </si>
+  <si>
+    <t>Sensual</t>
+  </si>
+  <si>
+    <t>Vainilla</t>
+  </si>
+  <si>
+    <t>Paco rabanne</t>
+  </si>
+  <si>
+    <t>AUT007.jpg</t>
+  </si>
+  <si>
+    <t>AUT008.jpg</t>
+  </si>
+  <si>
+    <t>AUT009.jpg</t>
+  </si>
+  <si>
+    <t>AUT010.jpg</t>
+  </si>
+  <si>
+    <t>AUT011.jpg</t>
+  </si>
+  <si>
+    <t>AUT012.jpg</t>
+  </si>
+  <si>
+    <t>Shampoo Siliconado</t>
+  </si>
+  <si>
+    <t>AUT013</t>
+  </si>
+  <si>
+    <t>Shampoo Siliconado por litro</t>
+  </si>
+  <si>
+    <t>AUT013.jpg</t>
+  </si>
+  <si>
+    <t>AUT014</t>
+  </si>
+  <si>
+    <t>AUT015</t>
+  </si>
+  <si>
+    <t>AUT016</t>
+  </si>
+  <si>
+    <t>AUT017</t>
+  </si>
+  <si>
+    <t>Mini Lata Walker</t>
+  </si>
+  <si>
+    <t>Mini Lata Walker para auto</t>
+  </si>
+  <si>
+    <t>AUT014.jpg</t>
+  </si>
+  <si>
+    <t>AUT015.jpg</t>
+  </si>
+  <si>
+    <t>AUT016.jpg</t>
+  </si>
+  <si>
+    <t>AUT017.jpg</t>
+  </si>
+  <si>
+    <t>AUT018</t>
+  </si>
+  <si>
+    <t>AUT019</t>
+  </si>
+  <si>
+    <t>Perfume en Lata Walker</t>
+  </si>
+  <si>
+    <t>universal</t>
+  </si>
+  <si>
+    <t>Aqua</t>
+  </si>
+  <si>
+    <t>Limon</t>
+  </si>
+  <si>
+    <t>AUT018.jpg</t>
+  </si>
+  <si>
+    <t>AUT019.jpg</t>
+  </si>
+  <si>
+    <t>AUT020</t>
+  </si>
+  <si>
+    <t>Cera</t>
+  </si>
+  <si>
+    <t>AUT020.jpg</t>
+  </si>
+  <si>
+    <t>Cera para auto por litro</t>
+  </si>
+  <si>
+    <t>AUT021</t>
+  </si>
+  <si>
+    <t>Limpia Tapizado en Aerosol</t>
+  </si>
+  <si>
+    <t>AUT021.jpg</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Shampoo </t>
+  </si>
+  <si>
+    <t>Shampoo para manos</t>
+  </si>
+  <si>
+    <t>blanco</t>
+  </si>
+  <si>
+    <t>vaini coco</t>
+  </si>
+  <si>
+    <t>manzana</t>
+  </si>
+  <si>
+    <t>uva</t>
+  </si>
+  <si>
+    <t>antibacterial</t>
+  </si>
+  <si>
+    <t>SHA001</t>
+  </si>
+  <si>
+    <t>Shampoo para manos por 5 litros</t>
+  </si>
+  <si>
+    <t>SHA002</t>
+  </si>
+  <si>
+    <t>SHA003</t>
+  </si>
+  <si>
+    <t>SHA004</t>
+  </si>
+  <si>
+    <t>SHA005</t>
+  </si>
+  <si>
+    <t>SHA006</t>
+  </si>
+  <si>
+    <t>DAV001</t>
+  </si>
+  <si>
+    <t>DAV002</t>
+  </si>
+  <si>
+    <t>DAV003</t>
+  </si>
+  <si>
+    <t>DAV004</t>
+  </si>
+  <si>
+    <t>DAV005</t>
+  </si>
+  <si>
+    <t>DAV006</t>
+  </si>
+  <si>
+    <t>DAV007</t>
+  </si>
+  <si>
+    <t>DAV008</t>
+  </si>
+  <si>
+    <t>DAV009</t>
+  </si>
+  <si>
+    <t>DAV010</t>
+  </si>
+  <si>
+    <t>DAV011</t>
+  </si>
+  <si>
+    <t>DAV012</t>
+  </si>
+  <si>
+    <t>DAV013</t>
+  </si>
+  <si>
+    <t>DAV014</t>
+  </si>
+  <si>
+    <t>Difusores Aromaticos</t>
+  </si>
+  <si>
+    <t>Saphirus</t>
+  </si>
+  <si>
+    <t>Difusor Aromatico Saphirus por 50 CC</t>
+  </si>
+  <si>
+    <t>vainilla</t>
+  </si>
+  <si>
+    <t>lavanda</t>
+  </si>
+  <si>
+    <t>palito de la selva</t>
+  </si>
+  <si>
+    <t>coniglio</t>
+  </si>
+  <si>
+    <t>limon</t>
+  </si>
+  <si>
+    <t>coco</t>
+  </si>
+  <si>
+    <t>frutilla</t>
+  </si>
+  <si>
+    <t>j.baby</t>
+  </si>
+  <si>
+    <t>papaya</t>
+  </si>
+  <si>
+    <t>flores blancas</t>
+  </si>
+  <si>
+    <t>citrus</t>
+  </si>
+  <si>
+    <t>jazmin</t>
+  </si>
+  <si>
+    <t>DAV001.jpg</t>
+  </si>
+  <si>
+    <t>DAV002.jpg</t>
+  </si>
+  <si>
+    <t>DAV003.jpg</t>
+  </si>
+  <si>
+    <t>DAV004.jpg</t>
+  </si>
+  <si>
+    <t>DAV005.jpg</t>
+  </si>
+  <si>
+    <t>DAV006.jpg</t>
+  </si>
+  <si>
+    <t>DAV007.jpg</t>
+  </si>
+  <si>
+    <t>DAV008.jpg</t>
+  </si>
+  <si>
+    <t>DAV009.jpg</t>
+  </si>
+  <si>
+    <t>DAV010.jpg</t>
+  </si>
+  <si>
+    <t>DAV011.jpg</t>
+  </si>
+  <si>
+    <t>DAV012.jpg</t>
+  </si>
+  <si>
+    <t>DAV013.jpg</t>
+  </si>
+  <si>
+    <t>DAV014.jpg</t>
+  </si>
+  <si>
+    <t>DAV015</t>
+  </si>
+  <si>
+    <t>DAV016</t>
+  </si>
+  <si>
+    <t>DAV017</t>
+  </si>
+  <si>
+    <t>DAV018</t>
+  </si>
+  <si>
+    <t>DAV019</t>
+  </si>
+  <si>
+    <t>DAV020</t>
+  </si>
+  <si>
+    <t>DAV021</t>
+  </si>
+  <si>
+    <t>DAV022</t>
+  </si>
+  <si>
+    <t>Difusor Aromatico Saphirus por 120 CC</t>
+  </si>
+  <si>
+    <t>vainilla madagascar</t>
+  </si>
+  <si>
+    <t>floral</t>
+  </si>
+  <si>
+    <t>chicle</t>
+  </si>
+  <si>
+    <t>nag champa</t>
+  </si>
+  <si>
+    <t>DAV015.jpg</t>
+  </si>
+  <si>
+    <t>DAV016.jpg</t>
+  </si>
+  <si>
+    <t>DAV017.jpg</t>
+  </si>
+  <si>
+    <t>DAV018.jpg</t>
+  </si>
+  <si>
+    <t>DAV019.jpg</t>
+  </si>
+  <si>
+    <t>DAV020.jpg</t>
+  </si>
+  <si>
+    <t>DAV021.jpg</t>
+  </si>
+  <si>
+    <t>DAV022.jpg</t>
+  </si>
+  <si>
+    <t>DAV023</t>
+  </si>
+  <si>
+    <t>DAV024</t>
+  </si>
+  <si>
+    <t>DAV025</t>
+  </si>
+  <si>
+    <t>DAV026</t>
+  </si>
+  <si>
+    <t>DAV027</t>
+  </si>
+  <si>
+    <t>Difusor Aromatico Saphirus combinados por 120 CC</t>
+  </si>
+  <si>
+    <t>sandia / melon</t>
+  </si>
+  <si>
+    <t>vainilla / frambruesa</t>
+  </si>
+  <si>
+    <t>vainilla / chocolate</t>
+  </si>
+  <si>
+    <t>vaini / coco</t>
+  </si>
+  <si>
+    <t>flores blancas / uvas</t>
+  </si>
+  <si>
+    <t>DAV023.jpg</t>
+  </si>
+  <si>
+    <t>DAV024.jpg</t>
+  </si>
+  <si>
+    <t>DAV025.jpg</t>
+  </si>
+  <si>
+    <t>DAV026.jpg</t>
+  </si>
+  <si>
+    <t>DAV027.jpg</t>
+  </si>
+  <si>
+    <t>PROM001</t>
+  </si>
+  <si>
+    <t>PROM002</t>
+  </si>
+  <si>
+    <t>PROM003</t>
+  </si>
+  <si>
+    <t>Promociones</t>
+  </si>
+  <si>
+    <t>Promo 15 litros</t>
+  </si>
+  <si>
+    <t>Promo 12 litros</t>
+  </si>
+  <si>
+    <t>Promo 12 litros + 5 de regalo</t>
+  </si>
+  <si>
+    <t>Promo 10 litros</t>
+  </si>
+  <si>
+    <t>PROM001.png</t>
+  </si>
+  <si>
+    <t>PROM002.png</t>
+  </si>
+  <si>
+    <t>PROM003.png</t>
+  </si>
+  <si>
+    <t>SHA001.png</t>
+  </si>
+  <si>
+    <t>SHA002.png</t>
+  </si>
+  <si>
+    <t>SHA003.png</t>
+  </si>
+  <si>
+    <t>SHA004.png</t>
+  </si>
+  <si>
+    <t>SHA005.png</t>
+  </si>
+  <si>
+    <t>SHA006.png</t>
   </si>
 </sst>
 </file>
@@ -4589,7 +5108,7 @@
         <v>16</v>
       </c>
       <c r="P2" t="s">
-        <v>1358</v>
+        <v>1359</v>
       </c>
     </row>
     <row r="3" spans="1:16" x14ac:dyDescent="0.25">
@@ -4756,14 +5275,14 @@
         <v>1098</v>
       </c>
       <c r="J6">
-        <v>2250</v>
+        <v>5000</v>
       </c>
       <c r="K6">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="L6">
         <f t="shared" si="0"/>
-        <v>11250</v>
+        <v>10000</v>
       </c>
       <c r="M6" t="s">
         <v>16</v>
@@ -4772,7 +5291,7 @@
         <v>16</v>
       </c>
       <c r="P6" t="s">
-        <v>1358</v>
+        <v>1359</v>
       </c>
     </row>
     <row r="7" spans="1:16" x14ac:dyDescent="0.25">
@@ -4804,14 +5323,14 @@
         <v>1099</v>
       </c>
       <c r="J7">
-        <v>1650</v>
+        <v>4000</v>
       </c>
       <c r="K7">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="L7">
         <f t="shared" si="0"/>
-        <v>11550</v>
+        <v>8000</v>
       </c>
       <c r="M7" t="s">
         <v>16</v>
@@ -4820,7 +5339,7 @@
         <v>16</v>
       </c>
       <c r="P7" t="s">
-        <v>1358</v>
+        <v>1359</v>
       </c>
     </row>
     <row r="8" spans="1:16" x14ac:dyDescent="0.25">
@@ -4852,11 +5371,11 @@
         <v>20000</v>
       </c>
       <c r="K8">
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="L8">
         <f t="shared" si="0"/>
-        <v>40000</v>
+        <v>30000</v>
       </c>
       <c r="M8" t="s">
         <v>16</v>
@@ -7993,41 +8512,92 @@
       <c r="O78" t="s">
         <v>16</v>
       </c>
+      <c r="P78" t="s">
+        <v>1359</v>
+      </c>
     </row>
     <row r="79" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A79" t="s">
         <v>93</v>
       </c>
+      <c r="B79" t="s">
+        <v>1364</v>
+      </c>
+      <c r="C79" t="s">
+        <v>1353</v>
+      </c>
+      <c r="D79" t="s">
+        <v>1368</v>
+      </c>
+      <c r="E79" t="s">
+        <v>1074</v>
+      </c>
       <c r="F79" t="s">
-        <v>1132</v>
+        <v>1369</v>
+      </c>
+      <c r="H79" t="s">
+        <v>1164</v>
+      </c>
+      <c r="I79" t="s">
+        <v>1370</v>
+      </c>
+      <c r="J79">
+        <v>5000</v>
       </c>
       <c r="K79">
-        <v>1</v>
-      </c>
-      <c r="L79" t="str">
+        <v>0.7</v>
+      </c>
+      <c r="L79">
         <f t="shared" si="1"/>
-        <v/>
+        <v>8500</v>
       </c>
       <c r="M79" t="s">
         <v>16</v>
       </c>
       <c r="O79" t="s">
         <v>16</v>
+      </c>
+      <c r="P79" t="s">
+        <v>1359</v>
       </c>
     </row>
     <row r="80" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A80" t="s">
         <v>94</v>
       </c>
+      <c r="B80" t="s">
+        <v>1365</v>
+      </c>
+      <c r="C80" t="s">
+        <v>1353</v>
+      </c>
+      <c r="D80" t="s">
+        <v>1375</v>
+      </c>
+      <c r="E80" t="s">
+        <v>1374</v>
+      </c>
       <c r="F80" t="s">
-        <v>1132</v>
+        <v>1375</v>
+      </c>
+      <c r="G80" t="s">
+        <v>1382</v>
+      </c>
+      <c r="H80" t="s">
+        <v>1164</v>
+      </c>
+      <c r="I80" t="s">
+        <v>1371</v>
+      </c>
+      <c r="J80">
+        <v>4100</v>
       </c>
       <c r="K80">
-        <v>1</v>
-      </c>
-      <c r="L80" t="str">
+        <v>0.7</v>
+      </c>
+      <c r="L80">
         <f t="shared" si="1"/>
-        <v/>
+        <v>6970</v>
       </c>
       <c r="M80" t="s">
         <v>16</v>
@@ -8035,20 +8605,47 @@
       <c r="O80" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="81" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="P80" t="s">
+        <v>1359</v>
+      </c>
+    </row>
+    <row r="81" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A81" t="s">
         <v>95</v>
       </c>
+      <c r="B81" t="s">
+        <v>1366</v>
+      </c>
+      <c r="C81" t="s">
+        <v>1353</v>
+      </c>
+      <c r="D81" t="s">
+        <v>1375</v>
+      </c>
+      <c r="E81" t="s">
+        <v>1374</v>
+      </c>
       <c r="F81" t="s">
-        <v>1132</v>
+        <v>1375</v>
+      </c>
+      <c r="G81" t="s">
+        <v>1383</v>
+      </c>
+      <c r="H81" t="s">
+        <v>1164</v>
+      </c>
+      <c r="I81" t="s">
+        <v>1372</v>
+      </c>
+      <c r="J81">
+        <v>4100</v>
       </c>
       <c r="K81">
-        <v>1</v>
-      </c>
-      <c r="L81" t="str">
+        <v>0.7</v>
+      </c>
+      <c r="L81">
         <f t="shared" si="1"/>
-        <v/>
+        <v>6970</v>
       </c>
       <c r="M81" t="s">
         <v>16</v>
@@ -8056,20 +8653,47 @@
       <c r="O81" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="82" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="P81" t="s">
+        <v>1359</v>
+      </c>
+    </row>
+    <row r="82" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A82" t="s">
         <v>96</v>
       </c>
+      <c r="B82" t="s">
+        <v>1367</v>
+      </c>
+      <c r="C82" t="s">
+        <v>1353</v>
+      </c>
+      <c r="D82" t="s">
+        <v>1375</v>
+      </c>
+      <c r="E82" t="s">
+        <v>1374</v>
+      </c>
       <c r="F82" t="s">
-        <v>1132</v>
+        <v>1375</v>
+      </c>
+      <c r="G82" t="s">
+        <v>1384</v>
+      </c>
+      <c r="H82" t="s">
+        <v>1164</v>
+      </c>
+      <c r="I82" t="s">
+        <v>1373</v>
+      </c>
+      <c r="J82">
+        <v>4100</v>
       </c>
       <c r="K82">
-        <v>1</v>
-      </c>
-      <c r="L82" t="str">
+        <v>0.7</v>
+      </c>
+      <c r="L82">
         <f t="shared" si="1"/>
-        <v/>
+        <v>6970</v>
       </c>
       <c r="M82" t="s">
         <v>16</v>
@@ -8077,20 +8701,47 @@
       <c r="O82" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="83" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="P82" t="s">
+        <v>1359</v>
+      </c>
+    </row>
+    <row r="83" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A83" t="s">
         <v>97</v>
       </c>
+      <c r="B83" t="s">
+        <v>1376</v>
+      </c>
+      <c r="C83" t="s">
+        <v>1353</v>
+      </c>
+      <c r="D83" t="s">
+        <v>1375</v>
+      </c>
+      <c r="E83" t="s">
+        <v>1374</v>
+      </c>
       <c r="F83" t="s">
-        <v>1132</v>
+        <v>1375</v>
+      </c>
+      <c r="G83" t="s">
+        <v>1385</v>
+      </c>
+      <c r="H83" t="s">
+        <v>1164</v>
+      </c>
+      <c r="I83" t="s">
+        <v>1391</v>
+      </c>
+      <c r="J83">
+        <v>4100</v>
       </c>
       <c r="K83">
-        <v>1</v>
-      </c>
-      <c r="L83" t="str">
+        <v>0.7</v>
+      </c>
+      <c r="L83">
         <f t="shared" si="1"/>
-        <v/>
+        <v>6970</v>
       </c>
       <c r="M83" t="s">
         <v>16</v>
@@ -8098,20 +8749,47 @@
       <c r="O83" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="84" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="P83" t="s">
+        <v>1359</v>
+      </c>
+    </row>
+    <row r="84" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A84" t="s">
         <v>98</v>
       </c>
+      <c r="B84" t="s">
+        <v>1377</v>
+      </c>
+      <c r="C84" t="s">
+        <v>1353</v>
+      </c>
+      <c r="D84" t="s">
+        <v>1375</v>
+      </c>
+      <c r="E84" t="s">
+        <v>1374</v>
+      </c>
       <c r="F84" t="s">
-        <v>1132</v>
+        <v>1375</v>
+      </c>
+      <c r="G84" t="s">
+        <v>1386</v>
+      </c>
+      <c r="H84" t="s">
+        <v>1164</v>
+      </c>
+      <c r="I84" t="s">
+        <v>1392</v>
+      </c>
+      <c r="J84">
+        <v>4100</v>
       </c>
       <c r="K84">
-        <v>1</v>
-      </c>
-      <c r="L84" t="str">
+        <v>0.7</v>
+      </c>
+      <c r="L84">
         <f t="shared" si="1"/>
-        <v/>
+        <v>6970</v>
       </c>
       <c r="M84" t="s">
         <v>16</v>
@@ -8119,20 +8797,47 @@
       <c r="O84" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="85" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="P84" t="s">
+        <v>1359</v>
+      </c>
+    </row>
+    <row r="85" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A85" t="s">
         <v>99</v>
       </c>
+      <c r="B85" t="s">
+        <v>1378</v>
+      </c>
+      <c r="C85" t="s">
+        <v>1353</v>
+      </c>
+      <c r="D85" t="s">
+        <v>1375</v>
+      </c>
+      <c r="E85" t="s">
+        <v>1374</v>
+      </c>
       <c r="F85" t="s">
-        <v>1132</v>
+        <v>1375</v>
+      </c>
+      <c r="G85" t="s">
+        <v>1387</v>
+      </c>
+      <c r="H85" t="s">
+        <v>1164</v>
+      </c>
+      <c r="I85" t="s">
+        <v>1393</v>
+      </c>
+      <c r="J85">
+        <v>4100</v>
       </c>
       <c r="K85">
-        <v>1</v>
-      </c>
-      <c r="L85" t="str">
+        <v>0.7</v>
+      </c>
+      <c r="L85">
         <f t="shared" si="1"/>
-        <v/>
+        <v>6970</v>
       </c>
       <c r="M85" t="s">
         <v>16</v>
@@ -8140,20 +8845,47 @@
       <c r="O85" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="86" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="P85" t="s">
+        <v>1359</v>
+      </c>
+    </row>
+    <row r="86" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A86" t="s">
         <v>100</v>
       </c>
+      <c r="B86" t="s">
+        <v>1379</v>
+      </c>
+      <c r="C86" t="s">
+        <v>1353</v>
+      </c>
+      <c r="D86" t="s">
+        <v>1375</v>
+      </c>
+      <c r="E86" t="s">
+        <v>1374</v>
+      </c>
       <c r="F86" t="s">
-        <v>1132</v>
+        <v>1375</v>
+      </c>
+      <c r="G86" t="s">
+        <v>1390</v>
+      </c>
+      <c r="H86" t="s">
+        <v>1164</v>
+      </c>
+      <c r="I86" t="s">
+        <v>1394</v>
+      </c>
+      <c r="J86">
+        <v>4100</v>
       </c>
       <c r="K86">
-        <v>1</v>
-      </c>
-      <c r="L86" t="str">
+        <v>0.7</v>
+      </c>
+      <c r="L86">
         <f t="shared" si="1"/>
-        <v/>
+        <v>6970</v>
       </c>
       <c r="M86" t="s">
         <v>16</v>
@@ -8161,20 +8893,47 @@
       <c r="O86" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="87" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="P86" t="s">
+        <v>1359</v>
+      </c>
+    </row>
+    <row r="87" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A87" t="s">
         <v>101</v>
       </c>
+      <c r="B87" t="s">
+        <v>1380</v>
+      </c>
+      <c r="C87" t="s">
+        <v>1353</v>
+      </c>
+      <c r="D87" t="s">
+        <v>1375</v>
+      </c>
+      <c r="E87" t="s">
+        <v>1374</v>
+      </c>
       <c r="F87" t="s">
-        <v>1132</v>
+        <v>1375</v>
+      </c>
+      <c r="G87" t="s">
+        <v>1388</v>
+      </c>
+      <c r="H87" t="s">
+        <v>1164</v>
+      </c>
+      <c r="I87" t="s">
+        <v>1395</v>
+      </c>
+      <c r="J87">
+        <v>4100</v>
       </c>
       <c r="K87">
-        <v>1</v>
-      </c>
-      <c r="L87" t="str">
+        <v>0.7</v>
+      </c>
+      <c r="L87">
         <f t="shared" si="1"/>
-        <v/>
+        <v>6970</v>
       </c>
       <c r="M87" t="s">
         <v>16</v>
@@ -8182,20 +8941,47 @@
       <c r="O87" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="88" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="P87" t="s">
+        <v>1359</v>
+      </c>
+    </row>
+    <row r="88" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A88" t="s">
         <v>102</v>
       </c>
+      <c r="B88" t="s">
+        <v>1381</v>
+      </c>
+      <c r="C88" t="s">
+        <v>1353</v>
+      </c>
+      <c r="D88" t="s">
+        <v>1375</v>
+      </c>
+      <c r="E88" t="s">
+        <v>1374</v>
+      </c>
       <c r="F88" t="s">
-        <v>1132</v>
+        <v>1375</v>
+      </c>
+      <c r="G88" t="s">
+        <v>1389</v>
+      </c>
+      <c r="H88" t="s">
+        <v>1164</v>
+      </c>
+      <c r="I88" t="s">
+        <v>1396</v>
+      </c>
+      <c r="J88">
+        <v>4100</v>
       </c>
       <c r="K88">
-        <v>1</v>
-      </c>
-      <c r="L88" t="str">
+        <v>0.7</v>
+      </c>
+      <c r="L88">
         <f t="shared" si="1"/>
-        <v/>
+        <v>6970</v>
       </c>
       <c r="M88" t="s">
         <v>16</v>
@@ -8203,20 +8989,44 @@
       <c r="O88" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="89" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="P88" t="s">
+        <v>1359</v>
+      </c>
+    </row>
+    <row r="89" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A89" t="s">
         <v>103</v>
       </c>
+      <c r="B89" t="s">
+        <v>1398</v>
+      </c>
+      <c r="C89" t="s">
+        <v>1353</v>
+      </c>
+      <c r="D89" t="s">
+        <v>1397</v>
+      </c>
+      <c r="E89" t="s">
+        <v>1074</v>
+      </c>
       <c r="F89" t="s">
-        <v>1132</v>
+        <v>1399</v>
+      </c>
+      <c r="H89" t="s">
+        <v>1164</v>
+      </c>
+      <c r="I89" t="s">
+        <v>1400</v>
+      </c>
+      <c r="J89">
+        <v>3000</v>
       </c>
       <c r="K89">
         <v>1</v>
       </c>
-      <c r="L89" t="str">
+      <c r="L89">
         <f t="shared" si="1"/>
-        <v/>
+        <v>6000</v>
       </c>
       <c r="M89" t="s">
         <v>16</v>
@@ -8224,20 +9034,47 @@
       <c r="O89" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="90" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="P89" t="s">
+        <v>1359</v>
+      </c>
+    </row>
+    <row r="90" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A90" t="s">
         <v>104</v>
       </c>
+      <c r="B90" t="s">
+        <v>1401</v>
+      </c>
+      <c r="C90" t="s">
+        <v>1353</v>
+      </c>
+      <c r="D90" t="s">
+        <v>1405</v>
+      </c>
+      <c r="E90" t="s">
+        <v>1374</v>
+      </c>
       <c r="F90" t="s">
-        <v>1132</v>
+        <v>1406</v>
+      </c>
+      <c r="G90" t="s">
+        <v>1414</v>
+      </c>
+      <c r="H90" t="s">
+        <v>1164</v>
+      </c>
+      <c r="I90" t="s">
+        <v>1407</v>
+      </c>
+      <c r="J90">
+        <v>4300</v>
       </c>
       <c r="K90">
         <v>1</v>
       </c>
-      <c r="L90" t="str">
+      <c r="L90">
         <f t="shared" si="1"/>
-        <v/>
+        <v>8600</v>
       </c>
       <c r="M90" t="s">
         <v>16</v>
@@ -8245,20 +9082,47 @@
       <c r="O90" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="91" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="P90" t="s">
+        <v>1359</v>
+      </c>
+    </row>
+    <row r="91" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A91" t="s">
         <v>105</v>
       </c>
+      <c r="B91" t="s">
+        <v>1402</v>
+      </c>
+      <c r="C91" t="s">
+        <v>1353</v>
+      </c>
+      <c r="D91" t="s">
+        <v>1413</v>
+      </c>
+      <c r="E91" t="s">
+        <v>1374</v>
+      </c>
       <c r="F91" t="s">
-        <v>1132</v>
+        <v>1413</v>
+      </c>
+      <c r="G91" t="s">
+        <v>1382</v>
+      </c>
+      <c r="H91" t="s">
+        <v>1164</v>
+      </c>
+      <c r="I91" t="s">
+        <v>1408</v>
+      </c>
+      <c r="J91">
+        <v>6500</v>
       </c>
       <c r="K91">
-        <v>1</v>
-      </c>
-      <c r="L91" t="str">
+        <v>0.5</v>
+      </c>
+      <c r="L91">
         <f t="shared" si="1"/>
-        <v/>
+        <v>9750</v>
       </c>
       <c r="M91" t="s">
         <v>16</v>
@@ -8266,20 +9130,47 @@
       <c r="O91" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="92" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="P91" t="s">
+        <v>1359</v>
+      </c>
+    </row>
+    <row r="92" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A92" t="s">
         <v>106</v>
       </c>
+      <c r="B92" t="s">
+        <v>1403</v>
+      </c>
+      <c r="C92" t="s">
+        <v>1353</v>
+      </c>
+      <c r="D92" t="s">
+        <v>1413</v>
+      </c>
+      <c r="E92" t="s">
+        <v>1374</v>
+      </c>
       <c r="F92" t="s">
-        <v>1132</v>
+        <v>1413</v>
+      </c>
+      <c r="G92" t="s">
+        <v>1384</v>
+      </c>
+      <c r="H92" t="s">
+        <v>1164</v>
+      </c>
+      <c r="I92" t="s">
+        <v>1409</v>
+      </c>
+      <c r="J92">
+        <v>6500</v>
       </c>
       <c r="K92">
-        <v>1</v>
-      </c>
-      <c r="L92" t="str">
+        <v>0.5</v>
+      </c>
+      <c r="L92">
         <f t="shared" si="1"/>
-        <v/>
+        <v>9750</v>
       </c>
       <c r="M92" t="s">
         <v>16</v>
@@ -8287,20 +9178,47 @@
       <c r="O92" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="93" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="P92" t="s">
+        <v>1359</v>
+      </c>
+    </row>
+    <row r="93" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A93" t="s">
         <v>107</v>
       </c>
+      <c r="B93" t="s">
+        <v>1404</v>
+      </c>
+      <c r="C93" t="s">
+        <v>1353</v>
+      </c>
+      <c r="D93" t="s">
+        <v>1413</v>
+      </c>
+      <c r="E93" t="s">
+        <v>1374</v>
+      </c>
       <c r="F93" t="s">
-        <v>1132</v>
+        <v>1413</v>
+      </c>
+      <c r="G93" t="s">
+        <v>1416</v>
+      </c>
+      <c r="H93" t="s">
+        <v>1164</v>
+      </c>
+      <c r="I93" t="s">
+        <v>1410</v>
+      </c>
+      <c r="J93">
+        <v>6500</v>
       </c>
       <c r="K93">
-        <v>1</v>
-      </c>
-      <c r="L93" t="str">
+        <v>0.5</v>
+      </c>
+      <c r="L93">
         <f t="shared" si="1"/>
-        <v/>
+        <v>9750</v>
       </c>
       <c r="M93" t="s">
         <v>16</v>
@@ -8308,20 +9226,47 @@
       <c r="O93" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="94" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="P93" t="s">
+        <v>1359</v>
+      </c>
+    </row>
+    <row r="94" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A94" t="s">
         <v>108</v>
       </c>
+      <c r="B94" t="s">
+        <v>1411</v>
+      </c>
+      <c r="C94" t="s">
+        <v>1353</v>
+      </c>
+      <c r="D94" t="s">
+        <v>1413</v>
+      </c>
+      <c r="E94" t="s">
+        <v>1374</v>
+      </c>
       <c r="F94" t="s">
-        <v>1132</v>
+        <v>1413</v>
+      </c>
+      <c r="G94" t="s">
+        <v>1389</v>
+      </c>
+      <c r="H94" t="s">
+        <v>1164</v>
+      </c>
+      <c r="I94" t="s">
+        <v>1417</v>
+      </c>
+      <c r="J94">
+        <v>6500</v>
       </c>
       <c r="K94">
-        <v>1</v>
-      </c>
-      <c r="L94" t="str">
+        <v>0.5</v>
+      </c>
+      <c r="L94">
         <f t="shared" si="1"/>
-        <v/>
+        <v>9750</v>
       </c>
       <c r="M94" t="s">
         <v>16</v>
@@ -8329,20 +9274,47 @@
       <c r="O94" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="95" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="P94" t="s">
+        <v>1359</v>
+      </c>
+    </row>
+    <row r="95" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A95" t="s">
         <v>109</v>
       </c>
+      <c r="B95" t="s">
+        <v>1412</v>
+      </c>
+      <c r="C95" t="s">
+        <v>1353</v>
+      </c>
+      <c r="D95" t="s">
+        <v>1413</v>
+      </c>
+      <c r="E95" t="s">
+        <v>1374</v>
+      </c>
       <c r="F95" t="s">
-        <v>1132</v>
+        <v>1413</v>
+      </c>
+      <c r="G95" t="s">
+        <v>1415</v>
+      </c>
+      <c r="H95" t="s">
+        <v>1164</v>
+      </c>
+      <c r="I95" t="s">
+        <v>1418</v>
+      </c>
+      <c r="J95">
+        <v>6500</v>
       </c>
       <c r="K95">
-        <v>1</v>
-      </c>
-      <c r="L95" t="str">
+        <v>0.5</v>
+      </c>
+      <c r="L95">
         <f t="shared" si="1"/>
-        <v/>
+        <v>9750</v>
       </c>
       <c r="M95" t="s">
         <v>16</v>
@@ -8350,20 +9322,44 @@
       <c r="O95" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="96" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="P95" t="s">
+        <v>1359</v>
+      </c>
+    </row>
+    <row r="96" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A96" t="s">
         <v>110</v>
       </c>
+      <c r="B96" t="s">
+        <v>1419</v>
+      </c>
+      <c r="C96" t="s">
+        <v>1353</v>
+      </c>
+      <c r="D96" t="s">
+        <v>1420</v>
+      </c>
+      <c r="E96" t="s">
+        <v>1074</v>
+      </c>
       <c r="F96" t="s">
-        <v>1132</v>
+        <v>1422</v>
+      </c>
+      <c r="H96" t="s">
+        <v>1164</v>
+      </c>
+      <c r="I96" t="s">
+        <v>1421</v>
+      </c>
+      <c r="J96">
+        <v>2500</v>
       </c>
       <c r="K96">
         <v>1</v>
       </c>
-      <c r="L96" t="str">
+      <c r="L96">
         <f t="shared" si="1"/>
-        <v/>
+        <v>5000</v>
       </c>
       <c r="M96" t="s">
         <v>16</v>
@@ -8371,20 +9367,44 @@
       <c r="O96" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="97" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="P96" t="s">
+        <v>1359</v>
+      </c>
+    </row>
+    <row r="97" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A97" t="s">
         <v>111</v>
       </c>
+      <c r="B97" t="s">
+        <v>1423</v>
+      </c>
+      <c r="C97" t="s">
+        <v>1353</v>
+      </c>
+      <c r="D97" t="s">
+        <v>1424</v>
+      </c>
+      <c r="E97" t="s">
+        <v>1374</v>
+      </c>
       <c r="F97" t="s">
-        <v>1132</v>
+        <v>1424</v>
+      </c>
+      <c r="H97" t="s">
+        <v>1164</v>
+      </c>
+      <c r="I97" t="s">
+        <v>1425</v>
+      </c>
+      <c r="J97">
+        <v>3400</v>
       </c>
       <c r="K97">
-        <v>1</v>
-      </c>
-      <c r="L97" t="str">
+        <v>0.5</v>
+      </c>
+      <c r="L97">
         <f t="shared" si="1"/>
-        <v/>
+        <v>5100</v>
       </c>
       <c r="M97" t="s">
         <v>16</v>
@@ -8392,20 +9412,47 @@
       <c r="O97" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="98" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="P97" t="s">
+        <v>1359</v>
+      </c>
+    </row>
+    <row r="98" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A98" t="s">
         <v>112</v>
       </c>
+      <c r="B98" t="s">
+        <v>1433</v>
+      </c>
+      <c r="C98" t="s">
+        <v>1426</v>
+      </c>
+      <c r="D98" t="s">
+        <v>1427</v>
+      </c>
+      <c r="E98" t="s">
+        <v>1074</v>
+      </c>
       <c r="F98" t="s">
-        <v>1132</v>
+        <v>1427</v>
+      </c>
+      <c r="G98" t="s">
+        <v>1384</v>
+      </c>
+      <c r="H98" t="s">
+        <v>1164</v>
+      </c>
+      <c r="I98" t="s">
+        <v>1531</v>
+      </c>
+      <c r="J98">
+        <v>4300</v>
       </c>
       <c r="K98">
         <v>1</v>
       </c>
-      <c r="L98" t="str">
+      <c r="L98">
         <f t="shared" si="1"/>
-        <v/>
+        <v>8600</v>
       </c>
       <c r="M98" t="s">
         <v>16</v>
@@ -8413,20 +9460,47 @@
       <c r="O98" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="99" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="P98" t="s">
+        <v>1359</v>
+      </c>
+    </row>
+    <row r="99" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A99" t="s">
         <v>113</v>
       </c>
+      <c r="B99" t="s">
+        <v>1435</v>
+      </c>
+      <c r="C99" t="s">
+        <v>1426</v>
+      </c>
+      <c r="D99" t="s">
+        <v>1427</v>
+      </c>
+      <c r="E99" t="s">
+        <v>1074</v>
+      </c>
       <c r="F99" t="s">
-        <v>1132</v>
+        <v>1434</v>
+      </c>
+      <c r="G99" t="s">
+        <v>1428</v>
+      </c>
+      <c r="H99" t="s">
+        <v>1164</v>
+      </c>
+      <c r="I99" t="s">
+        <v>1532</v>
+      </c>
+      <c r="J99">
+        <v>4300</v>
       </c>
       <c r="K99">
         <v>1</v>
       </c>
-      <c r="L99" t="str">
+      <c r="L99">
         <f t="shared" si="1"/>
-        <v/>
+        <v>8600</v>
       </c>
       <c r="M99" t="s">
         <v>16</v>
@@ -8434,20 +9508,47 @@
       <c r="O99" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="100" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="P99" t="s">
+        <v>1359</v>
+      </c>
+    </row>
+    <row r="100" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A100" t="s">
         <v>114</v>
       </c>
+      <c r="B100" t="s">
+        <v>1436</v>
+      </c>
+      <c r="C100" t="s">
+        <v>1426</v>
+      </c>
+      <c r="D100" t="s">
+        <v>1427</v>
+      </c>
+      <c r="E100" t="s">
+        <v>1074</v>
+      </c>
       <c r="F100" t="s">
-        <v>1132</v>
+        <v>1434</v>
+      </c>
+      <c r="G100" t="s">
+        <v>1429</v>
+      </c>
+      <c r="H100" t="s">
+        <v>1164</v>
+      </c>
+      <c r="I100" t="s">
+        <v>1533</v>
+      </c>
+      <c r="J100">
+        <v>4300</v>
       </c>
       <c r="K100">
         <v>1</v>
       </c>
-      <c r="L100" t="str">
+      <c r="L100">
         <f t="shared" si="1"/>
-        <v/>
+        <v>8600</v>
       </c>
       <c r="M100" t="s">
         <v>16</v>
@@ -8455,20 +9556,47 @@
       <c r="O100" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="101" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="P100" t="s">
+        <v>1359</v>
+      </c>
+    </row>
+    <row r="101" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A101" t="s">
         <v>115</v>
       </c>
+      <c r="B101" t="s">
+        <v>1437</v>
+      </c>
+      <c r="C101" t="s">
+        <v>1426</v>
+      </c>
+      <c r="D101" t="s">
+        <v>1427</v>
+      </c>
+      <c r="E101" t="s">
+        <v>1074</v>
+      </c>
       <c r="F101" t="s">
-        <v>1132</v>
+        <v>1434</v>
+      </c>
+      <c r="G101" t="s">
+        <v>1430</v>
+      </c>
+      <c r="H101" t="s">
+        <v>1164</v>
+      </c>
+      <c r="I101" t="s">
+        <v>1534</v>
+      </c>
+      <c r="J101">
+        <v>4300</v>
       </c>
       <c r="K101">
         <v>1</v>
       </c>
-      <c r="L101" t="str">
+      <c r="L101">
         <f t="shared" si="1"/>
-        <v/>
+        <v>8600</v>
       </c>
       <c r="M101" t="s">
         <v>16</v>
@@ -8476,20 +9604,47 @@
       <c r="O101" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="102" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="P101" t="s">
+        <v>1359</v>
+      </c>
+    </row>
+    <row r="102" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A102" t="s">
         <v>116</v>
       </c>
+      <c r="B102" t="s">
+        <v>1438</v>
+      </c>
+      <c r="C102" t="s">
+        <v>1426</v>
+      </c>
+      <c r="D102" t="s">
+        <v>1427</v>
+      </c>
+      <c r="E102" t="s">
+        <v>1074</v>
+      </c>
       <c r="F102" t="s">
-        <v>1132</v>
+        <v>1434</v>
+      </c>
+      <c r="G102" t="s">
+        <v>1431</v>
+      </c>
+      <c r="H102" t="s">
+        <v>1164</v>
+      </c>
+      <c r="I102" t="s">
+        <v>1535</v>
+      </c>
+      <c r="J102">
+        <v>4300</v>
       </c>
       <c r="K102">
         <v>1</v>
       </c>
-      <c r="L102" t="str">
+      <c r="L102">
         <f t="shared" si="1"/>
-        <v/>
+        <v>8600</v>
       </c>
       <c r="M102" t="s">
         <v>16</v>
@@ -8497,20 +9652,47 @@
       <c r="O102" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="103" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="P102" t="s">
+        <v>1359</v>
+      </c>
+    </row>
+    <row r="103" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A103" t="s">
         <v>117</v>
       </c>
+      <c r="B103" t="s">
+        <v>1439</v>
+      </c>
+      <c r="C103" t="s">
+        <v>1426</v>
+      </c>
+      <c r="D103" t="s">
+        <v>1427</v>
+      </c>
+      <c r="E103" t="s">
+        <v>1074</v>
+      </c>
       <c r="F103" t="s">
-        <v>1132</v>
+        <v>1434</v>
+      </c>
+      <c r="G103" t="s">
+        <v>1432</v>
+      </c>
+      <c r="H103" t="s">
+        <v>1164</v>
+      </c>
+      <c r="I103" t="s">
+        <v>1536</v>
+      </c>
+      <c r="J103">
+        <v>4300</v>
       </c>
       <c r="K103">
         <v>1</v>
       </c>
-      <c r="L103" t="str">
+      <c r="L103">
         <f t="shared" si="1"/>
-        <v/>
+        <v>8600</v>
       </c>
       <c r="M103" t="s">
         <v>16</v>
@@ -8518,20 +9700,47 @@
       <c r="O103" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="104" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="P103" t="s">
+        <v>1359</v>
+      </c>
+    </row>
+    <row r="104" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A104" t="s">
         <v>118</v>
       </c>
+      <c r="B104" t="s">
+        <v>1440</v>
+      </c>
+      <c r="C104" t="s">
+        <v>1454</v>
+      </c>
+      <c r="D104" t="s">
+        <v>1456</v>
+      </c>
+      <c r="E104" t="s">
+        <v>1455</v>
+      </c>
       <c r="F104" t="s">
-        <v>1132</v>
+        <v>1456</v>
+      </c>
+      <c r="G104" t="s">
+        <v>1457</v>
+      </c>
+      <c r="H104" t="s">
+        <v>1164</v>
+      </c>
+      <c r="I104" t="s">
+        <v>1469</v>
+      </c>
+      <c r="J104">
+        <v>1600</v>
       </c>
       <c r="K104">
         <v>1</v>
       </c>
-      <c r="L104" t="str">
+      <c r="L104">
         <f t="shared" si="1"/>
-        <v/>
+        <v>3200</v>
       </c>
       <c r="M104" t="s">
         <v>16</v>
@@ -8539,20 +9748,47 @@
       <c r="O104" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="105" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="P104" t="s">
+        <v>1359</v>
+      </c>
+    </row>
+    <row r="105" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A105" t="s">
         <v>119</v>
       </c>
+      <c r="B105" t="s">
+        <v>1441</v>
+      </c>
+      <c r="C105" t="s">
+        <v>1454</v>
+      </c>
+      <c r="D105" t="s">
+        <v>1456</v>
+      </c>
+      <c r="E105" t="s">
+        <v>1455</v>
+      </c>
       <c r="F105" t="s">
-        <v>1132</v>
+        <v>1456</v>
+      </c>
+      <c r="G105" t="s">
+        <v>1458</v>
+      </c>
+      <c r="H105" t="s">
+        <v>1164</v>
+      </c>
+      <c r="I105" t="s">
+        <v>1470</v>
+      </c>
+      <c r="J105">
+        <v>1600</v>
       </c>
       <c r="K105">
         <v>1</v>
       </c>
-      <c r="L105" t="str">
+      <c r="L105">
         <f t="shared" si="1"/>
-        <v/>
+        <v>3200</v>
       </c>
       <c r="M105" t="s">
         <v>16</v>
@@ -8560,20 +9796,47 @@
       <c r="O105" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="106" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="P105" t="s">
+        <v>1359</v>
+      </c>
+    </row>
+    <row r="106" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A106" t="s">
         <v>120</v>
       </c>
+      <c r="B106" t="s">
+        <v>1442</v>
+      </c>
+      <c r="C106" t="s">
+        <v>1454</v>
+      </c>
+      <c r="D106" t="s">
+        <v>1456</v>
+      </c>
+      <c r="E106" t="s">
+        <v>1455</v>
+      </c>
       <c r="F106" t="s">
-        <v>1132</v>
+        <v>1456</v>
+      </c>
+      <c r="G106" t="s">
+        <v>1431</v>
+      </c>
+      <c r="H106" t="s">
+        <v>1164</v>
+      </c>
+      <c r="I106" t="s">
+        <v>1471</v>
+      </c>
+      <c r="J106">
+        <v>1600</v>
       </c>
       <c r="K106">
         <v>1</v>
       </c>
-      <c r="L106" t="str">
+      <c r="L106">
         <f t="shared" si="1"/>
-        <v/>
+        <v>3200</v>
       </c>
       <c r="M106" t="s">
         <v>16</v>
@@ -8581,20 +9844,47 @@
       <c r="O106" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="107" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="P106" t="s">
+        <v>1359</v>
+      </c>
+    </row>
+    <row r="107" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A107" t="s">
         <v>121</v>
       </c>
+      <c r="B107" t="s">
+        <v>1443</v>
+      </c>
+      <c r="C107" t="s">
+        <v>1454</v>
+      </c>
+      <c r="D107" t="s">
+        <v>1456</v>
+      </c>
+      <c r="E107" t="s">
+        <v>1455</v>
+      </c>
       <c r="F107" t="s">
-        <v>1132</v>
+        <v>1456</v>
+      </c>
+      <c r="G107" t="s">
+        <v>1459</v>
+      </c>
+      <c r="H107" t="s">
+        <v>1164</v>
+      </c>
+      <c r="I107" t="s">
+        <v>1472</v>
+      </c>
+      <c r="J107">
+        <v>1600</v>
       </c>
       <c r="K107">
         <v>1</v>
       </c>
-      <c r="L107" t="str">
+      <c r="L107">
         <f t="shared" si="1"/>
-        <v/>
+        <v>3200</v>
       </c>
       <c r="M107" t="s">
         <v>16</v>
@@ -8602,20 +9892,47 @@
       <c r="O107" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="108" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="P107" t="s">
+        <v>1359</v>
+      </c>
+    </row>
+    <row r="108" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A108" t="s">
         <v>122</v>
       </c>
+      <c r="B108" t="s">
+        <v>1444</v>
+      </c>
+      <c r="C108" t="s">
+        <v>1454</v>
+      </c>
+      <c r="D108" t="s">
+        <v>1456</v>
+      </c>
+      <c r="E108" t="s">
+        <v>1455</v>
+      </c>
       <c r="F108" t="s">
-        <v>1132</v>
+        <v>1456</v>
+      </c>
+      <c r="G108" t="s">
+        <v>1429</v>
+      </c>
+      <c r="H108" t="s">
+        <v>1164</v>
+      </c>
+      <c r="I108" t="s">
+        <v>1473</v>
+      </c>
+      <c r="J108">
+        <v>1600</v>
       </c>
       <c r="K108">
         <v>1</v>
       </c>
-      <c r="L108" t="str">
+      <c r="L108">
         <f t="shared" si="1"/>
-        <v/>
+        <v>3200</v>
       </c>
       <c r="M108" t="s">
         <v>16</v>
@@ -8623,20 +9940,47 @@
       <c r="O108" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="109" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="P108" t="s">
+        <v>1359</v>
+      </c>
+    </row>
+    <row r="109" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A109" t="s">
         <v>123</v>
       </c>
+      <c r="B109" t="s">
+        <v>1445</v>
+      </c>
+      <c r="C109" t="s">
+        <v>1454</v>
+      </c>
+      <c r="D109" t="s">
+        <v>1456</v>
+      </c>
+      <c r="E109" t="s">
+        <v>1455</v>
+      </c>
       <c r="F109" t="s">
-        <v>1132</v>
+        <v>1456</v>
+      </c>
+      <c r="G109" t="s">
+        <v>1460</v>
+      </c>
+      <c r="H109" t="s">
+        <v>1164</v>
+      </c>
+      <c r="I109" t="s">
+        <v>1474</v>
+      </c>
+      <c r="J109">
+        <v>1600</v>
       </c>
       <c r="K109">
         <v>1</v>
       </c>
-      <c r="L109" t="str">
+      <c r="L109">
         <f t="shared" si="1"/>
-        <v/>
+        <v>3200</v>
       </c>
       <c r="M109" t="s">
         <v>16</v>
@@ -8644,20 +9988,47 @@
       <c r="O109" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="110" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="P109" t="s">
+        <v>1359</v>
+      </c>
+    </row>
+    <row r="110" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A110" t="s">
         <v>124</v>
       </c>
+      <c r="B110" t="s">
+        <v>1446</v>
+      </c>
+      <c r="C110" t="s">
+        <v>1454</v>
+      </c>
+      <c r="D110" t="s">
+        <v>1456</v>
+      </c>
+      <c r="E110" t="s">
+        <v>1455</v>
+      </c>
       <c r="F110" t="s">
-        <v>1132</v>
+        <v>1456</v>
+      </c>
+      <c r="G110" t="s">
+        <v>1461</v>
+      </c>
+      <c r="H110" t="s">
+        <v>1164</v>
+      </c>
+      <c r="I110" t="s">
+        <v>1475</v>
+      </c>
+      <c r="J110">
+        <v>1600</v>
       </c>
       <c r="K110">
         <v>1</v>
       </c>
-      <c r="L110" t="str">
+      <c r="L110">
         <f t="shared" si="1"/>
-        <v/>
+        <v>3200</v>
       </c>
       <c r="M110" t="s">
         <v>16</v>
@@ -8665,20 +10036,47 @@
       <c r="O110" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="111" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="P110" t="s">
+        <v>1359</v>
+      </c>
+    </row>
+    <row r="111" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A111" t="s">
         <v>125</v>
       </c>
+      <c r="B111" t="s">
+        <v>1447</v>
+      </c>
+      <c r="C111" t="s">
+        <v>1454</v>
+      </c>
+      <c r="D111" t="s">
+        <v>1456</v>
+      </c>
+      <c r="E111" t="s">
+        <v>1455</v>
+      </c>
       <c r="F111" t="s">
-        <v>1132</v>
+        <v>1456</v>
+      </c>
+      <c r="G111" t="s">
+        <v>1462</v>
+      </c>
+      <c r="H111" t="s">
+        <v>1164</v>
+      </c>
+      <c r="I111" t="s">
+        <v>1476</v>
+      </c>
+      <c r="J111">
+        <v>1600</v>
       </c>
       <c r="K111">
         <v>1</v>
       </c>
-      <c r="L111" t="str">
+      <c r="L111">
         <f t="shared" si="1"/>
-        <v/>
+        <v>3200</v>
       </c>
       <c r="M111" t="s">
         <v>16</v>
@@ -8686,20 +10084,47 @@
       <c r="O111" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="112" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="P111" t="s">
+        <v>1359</v>
+      </c>
+    </row>
+    <row r="112" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A112" t="s">
         <v>126</v>
       </c>
+      <c r="B112" t="s">
+        <v>1448</v>
+      </c>
+      <c r="C112" t="s">
+        <v>1454</v>
+      </c>
+      <c r="D112" t="s">
+        <v>1456</v>
+      </c>
+      <c r="E112" t="s">
+        <v>1455</v>
+      </c>
       <c r="F112" t="s">
-        <v>1132</v>
+        <v>1456</v>
+      </c>
+      <c r="G112" t="s">
+        <v>1463</v>
+      </c>
+      <c r="H112" t="s">
+        <v>1164</v>
+      </c>
+      <c r="I112" t="s">
+        <v>1477</v>
+      </c>
+      <c r="J112">
+        <v>1600</v>
       </c>
       <c r="K112">
         <v>1</v>
       </c>
-      <c r="L112" t="str">
+      <c r="L112">
         <f t="shared" si="1"/>
-        <v/>
+        <v>3200</v>
       </c>
       <c r="M112" t="s">
         <v>16</v>
@@ -8707,20 +10132,47 @@
       <c r="O112" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="113" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="P112" t="s">
+        <v>1359</v>
+      </c>
+    </row>
+    <row r="113" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A113" t="s">
         <v>127</v>
       </c>
+      <c r="B113" t="s">
+        <v>1449</v>
+      </c>
+      <c r="C113" t="s">
+        <v>1454</v>
+      </c>
+      <c r="D113" t="s">
+        <v>1456</v>
+      </c>
+      <c r="E113" t="s">
+        <v>1455</v>
+      </c>
       <c r="F113" t="s">
-        <v>1132</v>
+        <v>1456</v>
+      </c>
+      <c r="G113" t="s">
+        <v>1464</v>
+      </c>
+      <c r="H113" t="s">
+        <v>1164</v>
+      </c>
+      <c r="I113" t="s">
+        <v>1478</v>
+      </c>
+      <c r="J113">
+        <v>1600</v>
       </c>
       <c r="K113">
         <v>1</v>
       </c>
-      <c r="L113" t="str">
+      <c r="L113">
         <f t="shared" si="1"/>
-        <v/>
+        <v>3200</v>
       </c>
       <c r="M113" t="s">
         <v>16</v>
@@ -8728,20 +10180,47 @@
       <c r="O113" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="114" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="P113" t="s">
+        <v>1359</v>
+      </c>
+    </row>
+    <row r="114" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A114" t="s">
         <v>128</v>
       </c>
+      <c r="B114" t="s">
+        <v>1450</v>
+      </c>
+      <c r="C114" t="s">
+        <v>1454</v>
+      </c>
+      <c r="D114" t="s">
+        <v>1456</v>
+      </c>
+      <c r="E114" t="s">
+        <v>1455</v>
+      </c>
       <c r="F114" t="s">
-        <v>1132</v>
+        <v>1456</v>
+      </c>
+      <c r="G114" t="s">
+        <v>1465</v>
+      </c>
+      <c r="H114" t="s">
+        <v>1164</v>
+      </c>
+      <c r="I114" t="s">
+        <v>1479</v>
+      </c>
+      <c r="J114">
+        <v>1600</v>
       </c>
       <c r="K114">
         <v>1</v>
       </c>
-      <c r="L114" t="str">
+      <c r="L114">
         <f t="shared" si="1"/>
-        <v/>
+        <v>3200</v>
       </c>
       <c r="M114" t="s">
         <v>16</v>
@@ -8749,20 +10228,47 @@
       <c r="O114" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="115" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="P114" t="s">
+        <v>1359</v>
+      </c>
+    </row>
+    <row r="115" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A115" t="s">
         <v>129</v>
       </c>
+      <c r="B115" t="s">
+        <v>1451</v>
+      </c>
+      <c r="C115" t="s">
+        <v>1454</v>
+      </c>
+      <c r="D115" t="s">
+        <v>1456</v>
+      </c>
+      <c r="E115" t="s">
+        <v>1455</v>
+      </c>
       <c r="F115" t="s">
-        <v>1132</v>
+        <v>1456</v>
+      </c>
+      <c r="G115" t="s">
+        <v>1466</v>
+      </c>
+      <c r="H115" t="s">
+        <v>1164</v>
+      </c>
+      <c r="I115" t="s">
+        <v>1480</v>
+      </c>
+      <c r="J115">
+        <v>1600</v>
       </c>
       <c r="K115">
         <v>1</v>
       </c>
-      <c r="L115" t="str">
+      <c r="L115">
         <f t="shared" si="1"/>
-        <v/>
+        <v>3200</v>
       </c>
       <c r="M115" t="s">
         <v>16</v>
@@ -8770,20 +10276,47 @@
       <c r="O115" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="116" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="P115" t="s">
+        <v>1359</v>
+      </c>
+    </row>
+    <row r="116" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A116" t="s">
         <v>130</v>
       </c>
+      <c r="B116" t="s">
+        <v>1452</v>
+      </c>
+      <c r="C116" t="s">
+        <v>1454</v>
+      </c>
+      <c r="D116" t="s">
+        <v>1456</v>
+      </c>
+      <c r="E116" t="s">
+        <v>1455</v>
+      </c>
       <c r="F116" t="s">
-        <v>1132</v>
+        <v>1456</v>
+      </c>
+      <c r="G116" t="s">
+        <v>1467</v>
+      </c>
+      <c r="H116" t="s">
+        <v>1164</v>
+      </c>
+      <c r="I116" t="s">
+        <v>1481</v>
+      </c>
+      <c r="J116">
+        <v>1600</v>
       </c>
       <c r="K116">
         <v>1</v>
       </c>
-      <c r="L116" t="str">
+      <c r="L116">
         <f t="shared" si="1"/>
-        <v/>
+        <v>3200</v>
       </c>
       <c r="M116" t="s">
         <v>16</v>
@@ -8791,20 +10324,47 @@
       <c r="O116" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="117" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="P116" t="s">
+        <v>1359</v>
+      </c>
+    </row>
+    <row r="117" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A117" t="s">
         <v>131</v>
       </c>
+      <c r="B117" t="s">
+        <v>1453</v>
+      </c>
+      <c r="C117" t="s">
+        <v>1454</v>
+      </c>
+      <c r="D117" t="s">
+        <v>1456</v>
+      </c>
+      <c r="E117" t="s">
+        <v>1455</v>
+      </c>
       <c r="F117" t="s">
-        <v>1132</v>
+        <v>1456</v>
+      </c>
+      <c r="G117" t="s">
+        <v>1468</v>
+      </c>
+      <c r="H117" t="s">
+        <v>1164</v>
+      </c>
+      <c r="I117" t="s">
+        <v>1482</v>
+      </c>
+      <c r="J117">
+        <v>1600</v>
       </c>
       <c r="K117">
         <v>1</v>
       </c>
-      <c r="L117" t="str">
+      <c r="L117">
         <f t="shared" si="1"/>
-        <v/>
+        <v>3200</v>
       </c>
       <c r="M117" t="s">
         <v>16</v>
@@ -8812,20 +10372,47 @@
       <c r="O117" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="118" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="P117" t="s">
+        <v>1359</v>
+      </c>
+    </row>
+    <row r="118" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A118" t="s">
         <v>132</v>
       </c>
+      <c r="B118" t="s">
+        <v>1483</v>
+      </c>
+      <c r="C118" t="s">
+        <v>1454</v>
+      </c>
+      <c r="D118" t="s">
+        <v>1491</v>
+      </c>
+      <c r="E118" t="s">
+        <v>1455</v>
+      </c>
       <c r="F118" t="s">
-        <v>1132</v>
+        <v>1491</v>
+      </c>
+      <c r="G118" t="s">
+        <v>1457</v>
+      </c>
+      <c r="H118" t="s">
+        <v>1164</v>
+      </c>
+      <c r="I118" t="s">
+        <v>1496</v>
+      </c>
+      <c r="J118">
+        <v>2000</v>
       </c>
       <c r="K118">
         <v>1</v>
       </c>
-      <c r="L118" t="str">
+      <c r="L118">
         <f t="shared" si="1"/>
-        <v/>
+        <v>4000</v>
       </c>
       <c r="M118" t="s">
         <v>16</v>
@@ -8833,20 +10420,47 @@
       <c r="O118" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="119" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="P118" t="s">
+        <v>1359</v>
+      </c>
+    </row>
+    <row r="119" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A119" t="s">
         <v>133</v>
       </c>
+      <c r="B119" t="s">
+        <v>1484</v>
+      </c>
+      <c r="C119" t="s">
+        <v>1454</v>
+      </c>
+      <c r="D119" t="s">
+        <v>1491</v>
+      </c>
+      <c r="E119" t="s">
+        <v>1455</v>
+      </c>
       <c r="F119" t="s">
-        <v>1132</v>
+        <v>1491</v>
+      </c>
+      <c r="G119" t="s">
+        <v>1458</v>
+      </c>
+      <c r="H119" t="s">
+        <v>1164</v>
+      </c>
+      <c r="I119" t="s">
+        <v>1497</v>
+      </c>
+      <c r="J119">
+        <v>2000</v>
       </c>
       <c r="K119">
         <v>1</v>
       </c>
-      <c r="L119" t="str">
+      <c r="L119">
         <f t="shared" si="1"/>
-        <v/>
+        <v>4000</v>
       </c>
       <c r="M119" t="s">
         <v>16</v>
@@ -8854,20 +10468,47 @@
       <c r="O119" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="120" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="P119" t="s">
+        <v>1359</v>
+      </c>
+    </row>
+    <row r="120" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A120" t="s">
         <v>134</v>
       </c>
+      <c r="B120" t="s">
+        <v>1485</v>
+      </c>
+      <c r="C120" t="s">
+        <v>1454</v>
+      </c>
+      <c r="D120" t="s">
+        <v>1491</v>
+      </c>
+      <c r="E120" t="s">
+        <v>1455</v>
+      </c>
       <c r="F120" t="s">
-        <v>1132</v>
+        <v>1491</v>
+      </c>
+      <c r="G120" t="s">
+        <v>1461</v>
+      </c>
+      <c r="H120" t="s">
+        <v>1164</v>
+      </c>
+      <c r="I120" t="s">
+        <v>1498</v>
+      </c>
+      <c r="J120">
+        <v>2000</v>
       </c>
       <c r="K120">
         <v>1</v>
       </c>
-      <c r="L120" t="str">
+      <c r="L120">
         <f t="shared" si="1"/>
-        <v/>
+        <v>4000</v>
       </c>
       <c r="M120" t="s">
         <v>16</v>
@@ -8875,20 +10516,47 @@
       <c r="O120" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="121" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="P120" t="s">
+        <v>1359</v>
+      </c>
+    </row>
+    <row r="121" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A121" t="s">
         <v>135</v>
       </c>
+      <c r="B121" t="s">
+        <v>1486</v>
+      </c>
+      <c r="C121" t="s">
+        <v>1454</v>
+      </c>
+      <c r="D121" t="s">
+        <v>1491</v>
+      </c>
+      <c r="E121" t="s">
+        <v>1455</v>
+      </c>
       <c r="F121" t="s">
-        <v>1132</v>
+        <v>1491</v>
+      </c>
+      <c r="G121" t="s">
+        <v>1492</v>
+      </c>
+      <c r="H121" t="s">
+        <v>1164</v>
+      </c>
+      <c r="I121" t="s">
+        <v>1499</v>
+      </c>
+      <c r="J121">
+        <v>2000</v>
       </c>
       <c r="K121">
         <v>1</v>
       </c>
-      <c r="L121" t="str">
+      <c r="L121">
         <f t="shared" si="1"/>
-        <v/>
+        <v>4000</v>
       </c>
       <c r="M121" t="s">
         <v>16</v>
@@ -8896,20 +10564,47 @@
       <c r="O121" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="122" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="P121" t="s">
+        <v>1359</v>
+      </c>
+    </row>
+    <row r="122" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A122" t="s">
         <v>136</v>
       </c>
+      <c r="B122" t="s">
+        <v>1487</v>
+      </c>
+      <c r="C122" t="s">
+        <v>1454</v>
+      </c>
+      <c r="D122" t="s">
+        <v>1491</v>
+      </c>
+      <c r="E122" t="s">
+        <v>1455</v>
+      </c>
       <c r="F122" t="s">
-        <v>1132</v>
+        <v>1491</v>
+      </c>
+      <c r="G122" t="s">
+        <v>1493</v>
+      </c>
+      <c r="H122" t="s">
+        <v>1164</v>
+      </c>
+      <c r="I122" t="s">
+        <v>1500</v>
+      </c>
+      <c r="J122">
+        <v>2000</v>
       </c>
       <c r="K122">
         <v>1</v>
       </c>
-      <c r="L122" t="str">
+      <c r="L122">
         <f t="shared" si="1"/>
-        <v/>
+        <v>4000</v>
       </c>
       <c r="M122" t="s">
         <v>16</v>
@@ -8917,20 +10612,47 @@
       <c r="O122" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="123" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="P122" t="s">
+        <v>1359</v>
+      </c>
+    </row>
+    <row r="123" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A123" t="s">
         <v>137</v>
       </c>
+      <c r="B123" t="s">
+        <v>1488</v>
+      </c>
+      <c r="C123" t="s">
+        <v>1454</v>
+      </c>
+      <c r="D123" t="s">
+        <v>1491</v>
+      </c>
+      <c r="E123" t="s">
+        <v>1455</v>
+      </c>
       <c r="F123" t="s">
-        <v>1132</v>
+        <v>1491</v>
+      </c>
+      <c r="G123" t="s">
+        <v>1494</v>
+      </c>
+      <c r="H123" t="s">
+        <v>1164</v>
+      </c>
+      <c r="I123" t="s">
+        <v>1501</v>
+      </c>
+      <c r="J123">
+        <v>2000</v>
       </c>
       <c r="K123">
         <v>1</v>
       </c>
-      <c r="L123" t="str">
+      <c r="L123">
         <f t="shared" si="1"/>
-        <v/>
+        <v>4000</v>
       </c>
       <c r="M123" t="s">
         <v>16</v>
@@ -8938,20 +10660,47 @@
       <c r="O123" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="124" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="P123" t="s">
+        <v>1359</v>
+      </c>
+    </row>
+    <row r="124" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A124" t="s">
         <v>138</v>
       </c>
+      <c r="B124" t="s">
+        <v>1489</v>
+      </c>
+      <c r="C124" t="s">
+        <v>1454</v>
+      </c>
+      <c r="D124" t="s">
+        <v>1491</v>
+      </c>
+      <c r="E124" t="s">
+        <v>1455</v>
+      </c>
       <c r="F124" t="s">
-        <v>1132</v>
+        <v>1491</v>
+      </c>
+      <c r="G124" t="s">
+        <v>1459</v>
+      </c>
+      <c r="H124" t="s">
+        <v>1164</v>
+      </c>
+      <c r="I124" t="s">
+        <v>1502</v>
+      </c>
+      <c r="J124">
+        <v>2000</v>
       </c>
       <c r="K124">
         <v>1</v>
       </c>
-      <c r="L124" t="str">
+      <c r="L124">
         <f t="shared" si="1"/>
-        <v/>
+        <v>4000</v>
       </c>
       <c r="M124" t="s">
         <v>16</v>
@@ -8959,20 +10708,47 @@
       <c r="O124" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="125" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="P124" t="s">
+        <v>1359</v>
+      </c>
+    </row>
+    <row r="125" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A125" t="s">
         <v>139</v>
       </c>
+      <c r="B125" t="s">
+        <v>1490</v>
+      </c>
+      <c r="C125" t="s">
+        <v>1454</v>
+      </c>
+      <c r="D125" t="s">
+        <v>1491</v>
+      </c>
+      <c r="E125" t="s">
+        <v>1455</v>
+      </c>
       <c r="F125" t="s">
-        <v>1132</v>
+        <v>1491</v>
+      </c>
+      <c r="G125" t="s">
+        <v>1495</v>
+      </c>
+      <c r="H125" t="s">
+        <v>1164</v>
+      </c>
+      <c r="I125" t="s">
+        <v>1503</v>
+      </c>
+      <c r="J125">
+        <v>2000</v>
       </c>
       <c r="K125">
         <v>1</v>
       </c>
-      <c r="L125" t="str">
+      <c r="L125">
         <f t="shared" si="1"/>
-        <v/>
+        <v>4000</v>
       </c>
       <c r="M125" t="s">
         <v>16</v>
@@ -8980,20 +10756,47 @@
       <c r="O125" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="126" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="P125" t="s">
+        <v>1359</v>
+      </c>
+    </row>
+    <row r="126" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A126" t="s">
         <v>140</v>
       </c>
+      <c r="B126" t="s">
+        <v>1504</v>
+      </c>
+      <c r="C126" t="s">
+        <v>1454</v>
+      </c>
+      <c r="D126" t="s">
+        <v>1509</v>
+      </c>
+      <c r="E126" t="s">
+        <v>1455</v>
+      </c>
       <c r="F126" t="s">
-        <v>1132</v>
+        <v>1509</v>
+      </c>
+      <c r="G126" t="s">
+        <v>1510</v>
+      </c>
+      <c r="H126" t="s">
+        <v>1164</v>
+      </c>
+      <c r="I126" t="s">
+        <v>1515</v>
+      </c>
+      <c r="J126">
+        <v>2000</v>
       </c>
       <c r="K126">
         <v>1</v>
       </c>
-      <c r="L126" t="str">
+      <c r="L126">
         <f t="shared" si="1"/>
-        <v/>
+        <v>4000</v>
       </c>
       <c r="M126" t="s">
         <v>16</v>
@@ -9001,20 +10804,47 @@
       <c r="O126" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="127" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="P126" t="s">
+        <v>1359</v>
+      </c>
+    </row>
+    <row r="127" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A127" t="s">
         <v>141</v>
       </c>
+      <c r="B127" t="s">
+        <v>1505</v>
+      </c>
+      <c r="C127" t="s">
+        <v>1454</v>
+      </c>
+      <c r="D127" t="s">
+        <v>1509</v>
+      </c>
+      <c r="E127" t="s">
+        <v>1455</v>
+      </c>
       <c r="F127" t="s">
-        <v>1132</v>
+        <v>1509</v>
+      </c>
+      <c r="G127" t="s">
+        <v>1511</v>
+      </c>
+      <c r="H127" t="s">
+        <v>1164</v>
+      </c>
+      <c r="I127" t="s">
+        <v>1516</v>
+      </c>
+      <c r="J127">
+        <v>2000</v>
       </c>
       <c r="K127">
         <v>1</v>
       </c>
-      <c r="L127" t="str">
+      <c r="L127">
         <f t="shared" si="1"/>
-        <v/>
+        <v>4000</v>
       </c>
       <c r="M127" t="s">
         <v>16</v>
@@ -9022,20 +10852,47 @@
       <c r="O127" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="128" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="P127" t="s">
+        <v>1359</v>
+      </c>
+    </row>
+    <row r="128" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A128" t="s">
         <v>142</v>
       </c>
+      <c r="B128" t="s">
+        <v>1506</v>
+      </c>
+      <c r="C128" t="s">
+        <v>1454</v>
+      </c>
+      <c r="D128" t="s">
+        <v>1509</v>
+      </c>
+      <c r="E128" t="s">
+        <v>1455</v>
+      </c>
       <c r="F128" t="s">
-        <v>1132</v>
+        <v>1509</v>
+      </c>
+      <c r="G128" t="s">
+        <v>1512</v>
+      </c>
+      <c r="H128" t="s">
+        <v>1164</v>
+      </c>
+      <c r="I128" t="s">
+        <v>1517</v>
+      </c>
+      <c r="J128">
+        <v>2000</v>
       </c>
       <c r="K128">
         <v>1</v>
       </c>
-      <c r="L128" t="str">
+      <c r="L128">
         <f t="shared" si="1"/>
-        <v/>
+        <v>4000</v>
       </c>
       <c r="M128" t="s">
         <v>16</v>
@@ -9043,20 +10900,47 @@
       <c r="O128" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="129" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="P128" t="s">
+        <v>1359</v>
+      </c>
+    </row>
+    <row r="129" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A129" t="s">
         <v>143</v>
       </c>
+      <c r="B129" t="s">
+        <v>1507</v>
+      </c>
+      <c r="C129" t="s">
+        <v>1454</v>
+      </c>
+      <c r="D129" t="s">
+        <v>1509</v>
+      </c>
+      <c r="E129" t="s">
+        <v>1455</v>
+      </c>
       <c r="F129" t="s">
-        <v>1132</v>
+        <v>1509</v>
+      </c>
+      <c r="G129" t="s">
+        <v>1513</v>
+      </c>
+      <c r="H129" t="s">
+        <v>1164</v>
+      </c>
+      <c r="I129" t="s">
+        <v>1518</v>
+      </c>
+      <c r="J129">
+        <v>2000</v>
       </c>
       <c r="K129">
         <v>1</v>
       </c>
-      <c r="L129" t="str">
+      <c r="L129">
         <f t="shared" si="1"/>
-        <v/>
+        <v>4000</v>
       </c>
       <c r="M129" t="s">
         <v>16</v>
@@ -9064,20 +10948,47 @@
       <c r="O129" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="130" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="P129" t="s">
+        <v>1359</v>
+      </c>
+    </row>
+    <row r="130" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A130" t="s">
         <v>144</v>
       </c>
+      <c r="B130" t="s">
+        <v>1508</v>
+      </c>
+      <c r="C130" t="s">
+        <v>1454</v>
+      </c>
+      <c r="D130" t="s">
+        <v>1509</v>
+      </c>
+      <c r="E130" t="s">
+        <v>1455</v>
+      </c>
       <c r="F130" t="s">
-        <v>1132</v>
+        <v>1509</v>
+      </c>
+      <c r="G130" t="s">
+        <v>1514</v>
+      </c>
+      <c r="H130" t="s">
+        <v>1164</v>
+      </c>
+      <c r="I130" t="s">
+        <v>1519</v>
+      </c>
+      <c r="J130">
+        <v>2000</v>
       </c>
       <c r="K130">
         <v>1</v>
       </c>
-      <c r="L130" t="str">
+      <c r="L130">
         <f t="shared" ref="L130:L193" si="2">IF(J130="","",J130*(1+K130))</f>
-        <v/>
+        <v>4000</v>
       </c>
       <c r="M130" t="s">
         <v>16</v>
@@ -9085,20 +10996,44 @@
       <c r="O130" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="131" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="P130" t="s">
+        <v>1359</v>
+      </c>
+    </row>
+    <row r="131" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A131" t="s">
         <v>145</v>
       </c>
+      <c r="B131" t="s">
+        <v>1520</v>
+      </c>
+      <c r="C131" t="s">
+        <v>1523</v>
+      </c>
+      <c r="D131" t="s">
+        <v>1524</v>
+      </c>
+      <c r="E131" t="s">
+        <v>1074</v>
+      </c>
       <c r="F131" t="s">
-        <v>1132</v>
+        <v>1524</v>
+      </c>
+      <c r="H131" t="s">
+        <v>1164</v>
+      </c>
+      <c r="I131" t="s">
+        <v>1528</v>
+      </c>
+      <c r="J131">
+        <v>20000</v>
       </c>
       <c r="K131">
         <v>1</v>
       </c>
-      <c r="L131" t="str">
+      <c r="L131">
         <f t="shared" si="2"/>
-        <v/>
+        <v>40000</v>
       </c>
       <c r="M131" t="s">
         <v>16</v>
@@ -9106,20 +11041,44 @@
       <c r="O131" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="132" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="P131" t="s">
+        <v>1358</v>
+      </c>
+    </row>
+    <row r="132" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A132" t="s">
         <v>146</v>
       </c>
+      <c r="B132" t="s">
+        <v>1521</v>
+      </c>
+      <c r="C132" t="s">
+        <v>1523</v>
+      </c>
+      <c r="D132" t="s">
+        <v>1525</v>
+      </c>
+      <c r="E132" t="s">
+        <v>1074</v>
+      </c>
       <c r="F132" t="s">
-        <v>1132</v>
+        <v>1526</v>
+      </c>
+      <c r="H132" t="s">
+        <v>1164</v>
+      </c>
+      <c r="I132" t="s">
+        <v>1529</v>
+      </c>
+      <c r="J132">
+        <v>6500</v>
       </c>
       <c r="K132">
         <v>1</v>
       </c>
-      <c r="L132" t="str">
+      <c r="L132">
         <f t="shared" si="2"/>
-        <v/>
+        <v>13000</v>
       </c>
       <c r="M132" t="s">
         <v>16</v>
@@ -9127,20 +11086,44 @@
       <c r="O132" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="133" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="P132" t="s">
+        <v>1358</v>
+      </c>
+    </row>
+    <row r="133" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A133" t="s">
         <v>147</v>
       </c>
+      <c r="B133" t="s">
+        <v>1522</v>
+      </c>
+      <c r="C133" t="s">
+        <v>1523</v>
+      </c>
+      <c r="D133" t="s">
+        <v>1527</v>
+      </c>
+      <c r="E133" t="s">
+        <v>1074</v>
+      </c>
       <c r="F133" t="s">
-        <v>1132</v>
+        <v>1527</v>
+      </c>
+      <c r="H133" t="s">
+        <v>1164</v>
+      </c>
+      <c r="I133" t="s">
+        <v>1530</v>
+      </c>
+      <c r="J133">
+        <v>9000</v>
       </c>
       <c r="K133">
         <v>1</v>
       </c>
-      <c r="L133" t="str">
+      <c r="L133">
         <f t="shared" si="2"/>
-        <v/>
+        <v>18000</v>
       </c>
       <c r="M133" t="s">
         <v>16</v>
@@ -9148,8 +11131,11 @@
       <c r="O133" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="134" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="P133" t="s">
+        <v>1358</v>
+      </c>
+    </row>
+    <row r="134" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A134" t="s">
         <v>148</v>
       </c>
@@ -9170,7 +11156,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="135" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="135" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A135" t="s">
         <v>149</v>
       </c>
@@ -9191,7 +11177,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="136" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="136" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A136" t="s">
         <v>150</v>
       </c>
@@ -9212,7 +11198,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="137" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="137" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A137" t="s">
         <v>151</v>
       </c>
@@ -9233,7 +11219,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="138" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="138" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A138" t="s">
         <v>152</v>
       </c>
@@ -9254,7 +11240,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="139" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="139" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A139" t="s">
         <v>153</v>
       </c>
@@ -9275,7 +11261,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="140" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="140" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A140" t="s">
         <v>154</v>
       </c>
@@ -9296,7 +11282,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="141" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="141" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A141" t="s">
         <v>155</v>
       </c>
@@ -9317,7 +11303,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="142" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="142" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A142" t="s">
         <v>156</v>
       </c>
@@ -9338,7 +11324,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="143" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="143" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A143" t="s">
         <v>157</v>
       </c>
@@ -9359,7 +11345,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="144" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="144" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A144" t="s">
         <v>158</v>
       </c>

--- a/public/Plantilla_Quimica_Bethel_2.0.xlsx
+++ b/public/Plantilla_Quimica_Bethel_2.0.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\facun\Desktop\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B5C0D174-FD4A-4DC5-AED4-73CCBCD5E57B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{75E5983A-D124-4D35-9A2C-CED096121448}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="19440" windowHeight="14880" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -4343,6 +4343,24 @@
     <t>SHA001</t>
   </si>
   <si>
+    <t>SHA001.jpg</t>
+  </si>
+  <si>
+    <t>SHA002.jpg</t>
+  </si>
+  <si>
+    <t>SHA003.jpg</t>
+  </si>
+  <si>
+    <t>SHA004.jpg</t>
+  </si>
+  <si>
+    <t>SHA005.jpg</t>
+  </si>
+  <si>
+    <t>SHA006.jpg</t>
+  </si>
+  <si>
     <t>Shampoo para manos por 5 litros</t>
   </si>
   <si>
@@ -4632,24 +4650,6 @@
   </si>
   <si>
     <t>PROM003.png</t>
-  </si>
-  <si>
-    <t>SHA001.png</t>
-  </si>
-  <si>
-    <t>SHA002.png</t>
-  </si>
-  <si>
-    <t>SHA003.png</t>
-  </si>
-  <si>
-    <t>SHA004.png</t>
-  </si>
-  <si>
-    <t>SHA005.png</t>
-  </si>
-  <si>
-    <t>SHA006.png</t>
   </si>
 </sst>
 </file>
@@ -9442,7 +9442,7 @@
         <v>1164</v>
       </c>
       <c r="I98" t="s">
-        <v>1531</v>
+        <v>1434</v>
       </c>
       <c r="J98">
         <v>4300</v>
@@ -9469,7 +9469,7 @@
         <v>113</v>
       </c>
       <c r="B99" t="s">
-        <v>1435</v>
+        <v>1441</v>
       </c>
       <c r="C99" t="s">
         <v>1426</v>
@@ -9481,7 +9481,7 @@
         <v>1074</v>
       </c>
       <c r="F99" t="s">
-        <v>1434</v>
+        <v>1440</v>
       </c>
       <c r="G99" t="s">
         <v>1428</v>
@@ -9490,7 +9490,7 @@
         <v>1164</v>
       </c>
       <c r="I99" t="s">
-        <v>1532</v>
+        <v>1435</v>
       </c>
       <c r="J99">
         <v>4300</v>
@@ -9517,7 +9517,7 @@
         <v>114</v>
       </c>
       <c r="B100" t="s">
-        <v>1436</v>
+        <v>1442</v>
       </c>
       <c r="C100" t="s">
         <v>1426</v>
@@ -9529,7 +9529,7 @@
         <v>1074</v>
       </c>
       <c r="F100" t="s">
-        <v>1434</v>
+        <v>1440</v>
       </c>
       <c r="G100" t="s">
         <v>1429</v>
@@ -9538,7 +9538,7 @@
         <v>1164</v>
       </c>
       <c r="I100" t="s">
-        <v>1533</v>
+        <v>1436</v>
       </c>
       <c r="J100">
         <v>4300</v>
@@ -9565,7 +9565,7 @@
         <v>115</v>
       </c>
       <c r="B101" t="s">
-        <v>1437</v>
+        <v>1443</v>
       </c>
       <c r="C101" t="s">
         <v>1426</v>
@@ -9577,7 +9577,7 @@
         <v>1074</v>
       </c>
       <c r="F101" t="s">
-        <v>1434</v>
+        <v>1440</v>
       </c>
       <c r="G101" t="s">
         <v>1430</v>
@@ -9586,7 +9586,7 @@
         <v>1164</v>
       </c>
       <c r="I101" t="s">
-        <v>1534</v>
+        <v>1437</v>
       </c>
       <c r="J101">
         <v>4300</v>
@@ -9613,7 +9613,7 @@
         <v>116</v>
       </c>
       <c r="B102" t="s">
-        <v>1438</v>
+        <v>1444</v>
       </c>
       <c r="C102" t="s">
         <v>1426</v>
@@ -9625,7 +9625,7 @@
         <v>1074</v>
       </c>
       <c r="F102" t="s">
-        <v>1434</v>
+        <v>1440</v>
       </c>
       <c r="G102" t="s">
         <v>1431</v>
@@ -9634,7 +9634,7 @@
         <v>1164</v>
       </c>
       <c r="I102" t="s">
-        <v>1535</v>
+        <v>1438</v>
       </c>
       <c r="J102">
         <v>4300</v>
@@ -9661,7 +9661,7 @@
         <v>117</v>
       </c>
       <c r="B103" t="s">
-        <v>1439</v>
+        <v>1445</v>
       </c>
       <c r="C103" t="s">
         <v>1426</v>
@@ -9673,7 +9673,7 @@
         <v>1074</v>
       </c>
       <c r="F103" t="s">
-        <v>1434</v>
+        <v>1440</v>
       </c>
       <c r="G103" t="s">
         <v>1432</v>
@@ -9682,7 +9682,7 @@
         <v>1164</v>
       </c>
       <c r="I103" t="s">
-        <v>1536</v>
+        <v>1439</v>
       </c>
       <c r="J103">
         <v>4300</v>
@@ -9709,28 +9709,28 @@
         <v>118</v>
       </c>
       <c r="B104" t="s">
-        <v>1440</v>
+        <v>1446</v>
       </c>
       <c r="C104" t="s">
-        <v>1454</v>
+        <v>1460</v>
       </c>
       <c r="D104" t="s">
-        <v>1456</v>
+        <v>1462</v>
       </c>
       <c r="E104" t="s">
-        <v>1455</v>
+        <v>1461</v>
       </c>
       <c r="F104" t="s">
-        <v>1456</v>
+        <v>1462</v>
       </c>
       <c r="G104" t="s">
-        <v>1457</v>
+        <v>1463</v>
       </c>
       <c r="H104" t="s">
         <v>1164</v>
       </c>
       <c r="I104" t="s">
-        <v>1469</v>
+        <v>1475</v>
       </c>
       <c r="J104">
         <v>1600</v>
@@ -9757,28 +9757,28 @@
         <v>119</v>
       </c>
       <c r="B105" t="s">
-        <v>1441</v>
+        <v>1447</v>
       </c>
       <c r="C105" t="s">
-        <v>1454</v>
+        <v>1460</v>
       </c>
       <c r="D105" t="s">
-        <v>1456</v>
+        <v>1462</v>
       </c>
       <c r="E105" t="s">
-        <v>1455</v>
+        <v>1461</v>
       </c>
       <c r="F105" t="s">
-        <v>1456</v>
+        <v>1462</v>
       </c>
       <c r="G105" t="s">
-        <v>1458</v>
+        <v>1464</v>
       </c>
       <c r="H105" t="s">
         <v>1164</v>
       </c>
       <c r="I105" t="s">
-        <v>1470</v>
+        <v>1476</v>
       </c>
       <c r="J105">
         <v>1600</v>
@@ -9805,19 +9805,19 @@
         <v>120</v>
       </c>
       <c r="B106" t="s">
-        <v>1442</v>
+        <v>1448</v>
       </c>
       <c r="C106" t="s">
-        <v>1454</v>
+        <v>1460</v>
       </c>
       <c r="D106" t="s">
-        <v>1456</v>
+        <v>1462</v>
       </c>
       <c r="E106" t="s">
-        <v>1455</v>
+        <v>1461</v>
       </c>
       <c r="F106" t="s">
-        <v>1456</v>
+        <v>1462</v>
       </c>
       <c r="G106" t="s">
         <v>1431</v>
@@ -9826,7 +9826,7 @@
         <v>1164</v>
       </c>
       <c r="I106" t="s">
-        <v>1471</v>
+        <v>1477</v>
       </c>
       <c r="J106">
         <v>1600</v>
@@ -9853,28 +9853,28 @@
         <v>121</v>
       </c>
       <c r="B107" t="s">
-        <v>1443</v>
+        <v>1449</v>
       </c>
       <c r="C107" t="s">
-        <v>1454</v>
+        <v>1460</v>
       </c>
       <c r="D107" t="s">
-        <v>1456</v>
+        <v>1462</v>
       </c>
       <c r="E107" t="s">
-        <v>1455</v>
+        <v>1461</v>
       </c>
       <c r="F107" t="s">
-        <v>1456</v>
+        <v>1462</v>
       </c>
       <c r="G107" t="s">
-        <v>1459</v>
+        <v>1465</v>
       </c>
       <c r="H107" t="s">
         <v>1164</v>
       </c>
       <c r="I107" t="s">
-        <v>1472</v>
+        <v>1478</v>
       </c>
       <c r="J107">
         <v>1600</v>
@@ -9901,19 +9901,19 @@
         <v>122</v>
       </c>
       <c r="B108" t="s">
-        <v>1444</v>
+        <v>1450</v>
       </c>
       <c r="C108" t="s">
-        <v>1454</v>
+        <v>1460</v>
       </c>
       <c r="D108" t="s">
-        <v>1456</v>
+        <v>1462</v>
       </c>
       <c r="E108" t="s">
-        <v>1455</v>
+        <v>1461</v>
       </c>
       <c r="F108" t="s">
-        <v>1456</v>
+        <v>1462</v>
       </c>
       <c r="G108" t="s">
         <v>1429</v>
@@ -9922,7 +9922,7 @@
         <v>1164</v>
       </c>
       <c r="I108" t="s">
-        <v>1473</v>
+        <v>1479</v>
       </c>
       <c r="J108">
         <v>1600</v>
@@ -9949,28 +9949,28 @@
         <v>123</v>
       </c>
       <c r="B109" t="s">
-        <v>1445</v>
+        <v>1451</v>
       </c>
       <c r="C109" t="s">
-        <v>1454</v>
+        <v>1460</v>
       </c>
       <c r="D109" t="s">
-        <v>1456</v>
+        <v>1462</v>
       </c>
       <c r="E109" t="s">
-        <v>1455</v>
+        <v>1461</v>
       </c>
       <c r="F109" t="s">
-        <v>1456</v>
+        <v>1462</v>
       </c>
       <c r="G109" t="s">
-        <v>1460</v>
+        <v>1466</v>
       </c>
       <c r="H109" t="s">
         <v>1164</v>
       </c>
       <c r="I109" t="s">
-        <v>1474</v>
+        <v>1480</v>
       </c>
       <c r="J109">
         <v>1600</v>
@@ -9997,28 +9997,28 @@
         <v>124</v>
       </c>
       <c r="B110" t="s">
-        <v>1446</v>
+        <v>1452</v>
       </c>
       <c r="C110" t="s">
-        <v>1454</v>
+        <v>1460</v>
       </c>
       <c r="D110" t="s">
-        <v>1456</v>
+        <v>1462</v>
       </c>
       <c r="E110" t="s">
-        <v>1455</v>
+        <v>1461</v>
       </c>
       <c r="F110" t="s">
-        <v>1456</v>
+        <v>1462</v>
       </c>
       <c r="G110" t="s">
-        <v>1461</v>
+        <v>1467</v>
       </c>
       <c r="H110" t="s">
         <v>1164</v>
       </c>
       <c r="I110" t="s">
-        <v>1475</v>
+        <v>1481</v>
       </c>
       <c r="J110">
         <v>1600</v>
@@ -10045,28 +10045,28 @@
         <v>125</v>
       </c>
       <c r="B111" t="s">
-        <v>1447</v>
+        <v>1453</v>
       </c>
       <c r="C111" t="s">
-        <v>1454</v>
+        <v>1460</v>
       </c>
       <c r="D111" t="s">
-        <v>1456</v>
+        <v>1462</v>
       </c>
       <c r="E111" t="s">
-        <v>1455</v>
+        <v>1461</v>
       </c>
       <c r="F111" t="s">
-        <v>1456</v>
+        <v>1462</v>
       </c>
       <c r="G111" t="s">
-        <v>1462</v>
+        <v>1468</v>
       </c>
       <c r="H111" t="s">
         <v>1164</v>
       </c>
       <c r="I111" t="s">
-        <v>1476</v>
+        <v>1482</v>
       </c>
       <c r="J111">
         <v>1600</v>
@@ -10093,28 +10093,28 @@
         <v>126</v>
       </c>
       <c r="B112" t="s">
-        <v>1448</v>
+        <v>1454</v>
       </c>
       <c r="C112" t="s">
-        <v>1454</v>
+        <v>1460</v>
       </c>
       <c r="D112" t="s">
-        <v>1456</v>
+        <v>1462</v>
       </c>
       <c r="E112" t="s">
-        <v>1455</v>
+        <v>1461</v>
       </c>
       <c r="F112" t="s">
-        <v>1456</v>
+        <v>1462</v>
       </c>
       <c r="G112" t="s">
-        <v>1463</v>
+        <v>1469</v>
       </c>
       <c r="H112" t="s">
         <v>1164</v>
       </c>
       <c r="I112" t="s">
-        <v>1477</v>
+        <v>1483</v>
       </c>
       <c r="J112">
         <v>1600</v>
@@ -10141,28 +10141,28 @@
         <v>127</v>
       </c>
       <c r="B113" t="s">
-        <v>1449</v>
+        <v>1455</v>
       </c>
       <c r="C113" t="s">
-        <v>1454</v>
+        <v>1460</v>
       </c>
       <c r="D113" t="s">
-        <v>1456</v>
+        <v>1462</v>
       </c>
       <c r="E113" t="s">
-        <v>1455</v>
+        <v>1461</v>
       </c>
       <c r="F113" t="s">
-        <v>1456</v>
+        <v>1462</v>
       </c>
       <c r="G113" t="s">
-        <v>1464</v>
+        <v>1470</v>
       </c>
       <c r="H113" t="s">
         <v>1164</v>
       </c>
       <c r="I113" t="s">
-        <v>1478</v>
+        <v>1484</v>
       </c>
       <c r="J113">
         <v>1600</v>
@@ -10189,28 +10189,28 @@
         <v>128</v>
       </c>
       <c r="B114" t="s">
-        <v>1450</v>
+        <v>1456</v>
       </c>
       <c r="C114" t="s">
-        <v>1454</v>
+        <v>1460</v>
       </c>
       <c r="D114" t="s">
-        <v>1456</v>
+        <v>1462</v>
       </c>
       <c r="E114" t="s">
-        <v>1455</v>
+        <v>1461</v>
       </c>
       <c r="F114" t="s">
-        <v>1456</v>
+        <v>1462</v>
       </c>
       <c r="G114" t="s">
-        <v>1465</v>
+        <v>1471</v>
       </c>
       <c r="H114" t="s">
         <v>1164</v>
       </c>
       <c r="I114" t="s">
-        <v>1479</v>
+        <v>1485</v>
       </c>
       <c r="J114">
         <v>1600</v>
@@ -10237,28 +10237,28 @@
         <v>129</v>
       </c>
       <c r="B115" t="s">
-        <v>1451</v>
+        <v>1457</v>
       </c>
       <c r="C115" t="s">
-        <v>1454</v>
+        <v>1460</v>
       </c>
       <c r="D115" t="s">
-        <v>1456</v>
+        <v>1462</v>
       </c>
       <c r="E115" t="s">
-        <v>1455</v>
+        <v>1461</v>
       </c>
       <c r="F115" t="s">
-        <v>1456</v>
+        <v>1462</v>
       </c>
       <c r="G115" t="s">
-        <v>1466</v>
+        <v>1472</v>
       </c>
       <c r="H115" t="s">
         <v>1164</v>
       </c>
       <c r="I115" t="s">
-        <v>1480</v>
+        <v>1486</v>
       </c>
       <c r="J115">
         <v>1600</v>
@@ -10285,28 +10285,28 @@
         <v>130</v>
       </c>
       <c r="B116" t="s">
-        <v>1452</v>
+        <v>1458</v>
       </c>
       <c r="C116" t="s">
-        <v>1454</v>
+        <v>1460</v>
       </c>
       <c r="D116" t="s">
-        <v>1456</v>
+        <v>1462</v>
       </c>
       <c r="E116" t="s">
-        <v>1455</v>
+        <v>1461</v>
       </c>
       <c r="F116" t="s">
-        <v>1456</v>
+        <v>1462</v>
       </c>
       <c r="G116" t="s">
-        <v>1467</v>
+        <v>1473</v>
       </c>
       <c r="H116" t="s">
         <v>1164</v>
       </c>
       <c r="I116" t="s">
-        <v>1481</v>
+        <v>1487</v>
       </c>
       <c r="J116">
         <v>1600</v>
@@ -10333,28 +10333,28 @@
         <v>131</v>
       </c>
       <c r="B117" t="s">
-        <v>1453</v>
+        <v>1459</v>
       </c>
       <c r="C117" t="s">
-        <v>1454</v>
+        <v>1460</v>
       </c>
       <c r="D117" t="s">
-        <v>1456</v>
+        <v>1462</v>
       </c>
       <c r="E117" t="s">
-        <v>1455</v>
+        <v>1461</v>
       </c>
       <c r="F117" t="s">
-        <v>1456</v>
+        <v>1462</v>
       </c>
       <c r="G117" t="s">
-        <v>1468</v>
+        <v>1474</v>
       </c>
       <c r="H117" t="s">
         <v>1164</v>
       </c>
       <c r="I117" t="s">
-        <v>1482</v>
+        <v>1488</v>
       </c>
       <c r="J117">
         <v>1600</v>
@@ -10381,28 +10381,28 @@
         <v>132</v>
       </c>
       <c r="B118" t="s">
-        <v>1483</v>
+        <v>1489</v>
       </c>
       <c r="C118" t="s">
-        <v>1454</v>
+        <v>1460</v>
       </c>
       <c r="D118" t="s">
-        <v>1491</v>
+        <v>1497</v>
       </c>
       <c r="E118" t="s">
-        <v>1455</v>
+        <v>1461</v>
       </c>
       <c r="F118" t="s">
-        <v>1491</v>
+        <v>1497</v>
       </c>
       <c r="G118" t="s">
-        <v>1457</v>
+        <v>1463</v>
       </c>
       <c r="H118" t="s">
         <v>1164</v>
       </c>
       <c r="I118" t="s">
-        <v>1496</v>
+        <v>1502</v>
       </c>
       <c r="J118">
         <v>2000</v>
@@ -10429,28 +10429,28 @@
         <v>133</v>
       </c>
       <c r="B119" t="s">
-        <v>1484</v>
+        <v>1490</v>
       </c>
       <c r="C119" t="s">
-        <v>1454</v>
+        <v>1460</v>
       </c>
       <c r="D119" t="s">
-        <v>1491</v>
+        <v>1497</v>
       </c>
       <c r="E119" t="s">
-        <v>1455</v>
+        <v>1461</v>
       </c>
       <c r="F119" t="s">
-        <v>1491</v>
+        <v>1497</v>
       </c>
       <c r="G119" t="s">
-        <v>1458</v>
+        <v>1464</v>
       </c>
       <c r="H119" t="s">
         <v>1164</v>
       </c>
       <c r="I119" t="s">
-        <v>1497</v>
+        <v>1503</v>
       </c>
       <c r="J119">
         <v>2000</v>
@@ -10477,28 +10477,28 @@
         <v>134</v>
       </c>
       <c r="B120" t="s">
-        <v>1485</v>
+        <v>1491</v>
       </c>
       <c r="C120" t="s">
-        <v>1454</v>
+        <v>1460</v>
       </c>
       <c r="D120" t="s">
-        <v>1491</v>
+        <v>1497</v>
       </c>
       <c r="E120" t="s">
-        <v>1455</v>
+        <v>1461</v>
       </c>
       <c r="F120" t="s">
-        <v>1491</v>
+        <v>1497</v>
       </c>
       <c r="G120" t="s">
-        <v>1461</v>
+        <v>1467</v>
       </c>
       <c r="H120" t="s">
         <v>1164</v>
       </c>
       <c r="I120" t="s">
-        <v>1498</v>
+        <v>1504</v>
       </c>
       <c r="J120">
         <v>2000</v>
@@ -10525,28 +10525,28 @@
         <v>135</v>
       </c>
       <c r="B121" t="s">
-        <v>1486</v>
+        <v>1492</v>
       </c>
       <c r="C121" t="s">
-        <v>1454</v>
+        <v>1460</v>
       </c>
       <c r="D121" t="s">
-        <v>1491</v>
+        <v>1497</v>
       </c>
       <c r="E121" t="s">
-        <v>1455</v>
+        <v>1461</v>
       </c>
       <c r="F121" t="s">
-        <v>1491</v>
+        <v>1497</v>
       </c>
       <c r="G121" t="s">
-        <v>1492</v>
+        <v>1498</v>
       </c>
       <c r="H121" t="s">
         <v>1164</v>
       </c>
       <c r="I121" t="s">
-        <v>1499</v>
+        <v>1505</v>
       </c>
       <c r="J121">
         <v>2000</v>
@@ -10573,28 +10573,28 @@
         <v>136</v>
       </c>
       <c r="B122" t="s">
-        <v>1487</v>
+        <v>1493</v>
       </c>
       <c r="C122" t="s">
-        <v>1454</v>
+        <v>1460</v>
       </c>
       <c r="D122" t="s">
-        <v>1491</v>
+        <v>1497</v>
       </c>
       <c r="E122" t="s">
-        <v>1455</v>
+        <v>1461</v>
       </c>
       <c r="F122" t="s">
-        <v>1491</v>
+        <v>1497</v>
       </c>
       <c r="G122" t="s">
-        <v>1493</v>
+        <v>1499</v>
       </c>
       <c r="H122" t="s">
         <v>1164</v>
       </c>
       <c r="I122" t="s">
-        <v>1500</v>
+        <v>1506</v>
       </c>
       <c r="J122">
         <v>2000</v>
@@ -10621,28 +10621,28 @@
         <v>137</v>
       </c>
       <c r="B123" t="s">
-        <v>1488</v>
+        <v>1494</v>
       </c>
       <c r="C123" t="s">
-        <v>1454</v>
+        <v>1460</v>
       </c>
       <c r="D123" t="s">
-        <v>1491</v>
+        <v>1497</v>
       </c>
       <c r="E123" t="s">
-        <v>1455</v>
+        <v>1461</v>
       </c>
       <c r="F123" t="s">
-        <v>1491</v>
+        <v>1497</v>
       </c>
       <c r="G123" t="s">
-        <v>1494</v>
+        <v>1500</v>
       </c>
       <c r="H123" t="s">
         <v>1164</v>
       </c>
       <c r="I123" t="s">
-        <v>1501</v>
+        <v>1507</v>
       </c>
       <c r="J123">
         <v>2000</v>
@@ -10669,28 +10669,28 @@
         <v>138</v>
       </c>
       <c r="B124" t="s">
-        <v>1489</v>
+        <v>1495</v>
       </c>
       <c r="C124" t="s">
-        <v>1454</v>
+        <v>1460</v>
       </c>
       <c r="D124" t="s">
-        <v>1491</v>
+        <v>1497</v>
       </c>
       <c r="E124" t="s">
-        <v>1455</v>
+        <v>1461</v>
       </c>
       <c r="F124" t="s">
-        <v>1491</v>
+        <v>1497</v>
       </c>
       <c r="G124" t="s">
-        <v>1459</v>
+        <v>1465</v>
       </c>
       <c r="H124" t="s">
         <v>1164</v>
       </c>
       <c r="I124" t="s">
-        <v>1502</v>
+        <v>1508</v>
       </c>
       <c r="J124">
         <v>2000</v>
@@ -10717,28 +10717,28 @@
         <v>139</v>
       </c>
       <c r="B125" t="s">
-        <v>1490</v>
+        <v>1496</v>
       </c>
       <c r="C125" t="s">
-        <v>1454</v>
+        <v>1460</v>
       </c>
       <c r="D125" t="s">
-        <v>1491</v>
+        <v>1497</v>
       </c>
       <c r="E125" t="s">
-        <v>1455</v>
+        <v>1461</v>
       </c>
       <c r="F125" t="s">
-        <v>1491</v>
+        <v>1497</v>
       </c>
       <c r="G125" t="s">
-        <v>1495</v>
+        <v>1501</v>
       </c>
       <c r="H125" t="s">
         <v>1164</v>
       </c>
       <c r="I125" t="s">
-        <v>1503</v>
+        <v>1509</v>
       </c>
       <c r="J125">
         <v>2000</v>
@@ -10765,28 +10765,28 @@
         <v>140</v>
       </c>
       <c r="B126" t="s">
-        <v>1504</v>
+        <v>1510</v>
       </c>
       <c r="C126" t="s">
-        <v>1454</v>
+        <v>1460</v>
       </c>
       <c r="D126" t="s">
-        <v>1509</v>
+        <v>1515</v>
       </c>
       <c r="E126" t="s">
-        <v>1455</v>
+        <v>1461</v>
       </c>
       <c r="F126" t="s">
-        <v>1509</v>
+        <v>1515</v>
       </c>
       <c r="G126" t="s">
-        <v>1510</v>
+        <v>1516</v>
       </c>
       <c r="H126" t="s">
         <v>1164</v>
       </c>
       <c r="I126" t="s">
-        <v>1515</v>
+        <v>1521</v>
       </c>
       <c r="J126">
         <v>2000</v>
@@ -10813,28 +10813,28 @@
         <v>141</v>
       </c>
       <c r="B127" t="s">
-        <v>1505</v>
+        <v>1511</v>
       </c>
       <c r="C127" t="s">
-        <v>1454</v>
+        <v>1460</v>
       </c>
       <c r="D127" t="s">
-        <v>1509</v>
+        <v>1515</v>
       </c>
       <c r="E127" t="s">
-        <v>1455</v>
+        <v>1461</v>
       </c>
       <c r="F127" t="s">
-        <v>1509</v>
+        <v>1515</v>
       </c>
       <c r="G127" t="s">
-        <v>1511</v>
+        <v>1517</v>
       </c>
       <c r="H127" t="s">
         <v>1164</v>
       </c>
       <c r="I127" t="s">
-        <v>1516</v>
+        <v>1522</v>
       </c>
       <c r="J127">
         <v>2000</v>
@@ -10861,28 +10861,28 @@
         <v>142</v>
       </c>
       <c r="B128" t="s">
-        <v>1506</v>
+        <v>1512</v>
       </c>
       <c r="C128" t="s">
-        <v>1454</v>
+        <v>1460</v>
       </c>
       <c r="D128" t="s">
-        <v>1509</v>
+        <v>1515</v>
       </c>
       <c r="E128" t="s">
-        <v>1455</v>
+        <v>1461</v>
       </c>
       <c r="F128" t="s">
-        <v>1509</v>
+        <v>1515</v>
       </c>
       <c r="G128" t="s">
-        <v>1512</v>
+        <v>1518</v>
       </c>
       <c r="H128" t="s">
         <v>1164</v>
       </c>
       <c r="I128" t="s">
-        <v>1517</v>
+        <v>1523</v>
       </c>
       <c r="J128">
         <v>2000</v>
@@ -10909,28 +10909,28 @@
         <v>143</v>
       </c>
       <c r="B129" t="s">
-        <v>1507</v>
+        <v>1513</v>
       </c>
       <c r="C129" t="s">
-        <v>1454</v>
+        <v>1460</v>
       </c>
       <c r="D129" t="s">
-        <v>1509</v>
+        <v>1515</v>
       </c>
       <c r="E129" t="s">
-        <v>1455</v>
+        <v>1461</v>
       </c>
       <c r="F129" t="s">
-        <v>1509</v>
+        <v>1515</v>
       </c>
       <c r="G129" t="s">
-        <v>1513</v>
+        <v>1519</v>
       </c>
       <c r="H129" t="s">
         <v>1164</v>
       </c>
       <c r="I129" t="s">
-        <v>1518</v>
+        <v>1524</v>
       </c>
       <c r="J129">
         <v>2000</v>
@@ -10957,28 +10957,28 @@
         <v>144</v>
       </c>
       <c r="B130" t="s">
-        <v>1508</v>
+        <v>1514</v>
       </c>
       <c r="C130" t="s">
-        <v>1454</v>
+        <v>1460</v>
       </c>
       <c r="D130" t="s">
-        <v>1509</v>
+        <v>1515</v>
       </c>
       <c r="E130" t="s">
-        <v>1455</v>
+        <v>1461</v>
       </c>
       <c r="F130" t="s">
-        <v>1509</v>
+        <v>1515</v>
       </c>
       <c r="G130" t="s">
-        <v>1514</v>
+        <v>1520</v>
       </c>
       <c r="H130" t="s">
         <v>1164</v>
       </c>
       <c r="I130" t="s">
-        <v>1519</v>
+        <v>1525</v>
       </c>
       <c r="J130">
         <v>2000</v>
@@ -11005,25 +11005,25 @@
         <v>145</v>
       </c>
       <c r="B131" t="s">
-        <v>1520</v>
+        <v>1526</v>
       </c>
       <c r="C131" t="s">
-        <v>1523</v>
+        <v>1529</v>
       </c>
       <c r="D131" t="s">
-        <v>1524</v>
+        <v>1530</v>
       </c>
       <c r="E131" t="s">
         <v>1074</v>
       </c>
       <c r="F131" t="s">
-        <v>1524</v>
+        <v>1530</v>
       </c>
       <c r="H131" t="s">
         <v>1164</v>
       </c>
       <c r="I131" t="s">
-        <v>1528</v>
+        <v>1534</v>
       </c>
       <c r="J131">
         <v>20000</v>
@@ -11050,25 +11050,25 @@
         <v>146</v>
       </c>
       <c r="B132" t="s">
-        <v>1521</v>
+        <v>1527</v>
       </c>
       <c r="C132" t="s">
-        <v>1523</v>
+        <v>1529</v>
       </c>
       <c r="D132" t="s">
-        <v>1525</v>
+        <v>1531</v>
       </c>
       <c r="E132" t="s">
         <v>1074</v>
       </c>
       <c r="F132" t="s">
-        <v>1526</v>
+        <v>1532</v>
       </c>
       <c r="H132" t="s">
         <v>1164</v>
       </c>
       <c r="I132" t="s">
-        <v>1529</v>
+        <v>1535</v>
       </c>
       <c r="J132">
         <v>6500</v>
@@ -11095,25 +11095,25 @@
         <v>147</v>
       </c>
       <c r="B133" t="s">
-        <v>1522</v>
+        <v>1528</v>
       </c>
       <c r="C133" t="s">
-        <v>1523</v>
+        <v>1529</v>
       </c>
       <c r="D133" t="s">
-        <v>1527</v>
+        <v>1533</v>
       </c>
       <c r="E133" t="s">
         <v>1074</v>
       </c>
       <c r="F133" t="s">
-        <v>1527</v>
+        <v>1533</v>
       </c>
       <c r="H133" t="s">
         <v>1164</v>
       </c>
       <c r="I133" t="s">
-        <v>1530</v>
+        <v>1536</v>
       </c>
       <c r="J133">
         <v>9000</v>

--- a/public/Plantilla_Quimica_Bethel_2.0.xlsx
+++ b/public/Plantilla_Quimica_Bethel_2.0.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\facun\Desktop\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{75E5983A-D124-4D35-9A2C-CED096121448}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A584AA08-478B-4A55-966A-14E06A3B5FA0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="19440" windowHeight="14880" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4245" uniqueCount="1537">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4378" uniqueCount="1538">
   <si>
     <t>ID</t>
   </si>
@@ -4343,24 +4343,6 @@
     <t>SHA001</t>
   </si>
   <si>
-    <t>SHA001.jpg</t>
-  </si>
-  <si>
-    <t>SHA002.jpg</t>
-  </si>
-  <si>
-    <t>SHA003.jpg</t>
-  </si>
-  <si>
-    <t>SHA004.jpg</t>
-  </si>
-  <si>
-    <t>SHA005.jpg</t>
-  </si>
-  <si>
-    <t>SHA006.jpg</t>
-  </si>
-  <si>
     <t>Shampoo para manos por 5 litros</t>
   </si>
   <si>
@@ -4650,6 +4632,27 @@
   </si>
   <si>
     <t>PROM003.png</t>
+  </si>
+  <si>
+    <t>SHA001.png</t>
+  </si>
+  <si>
+    <t>SHA002.png</t>
+  </si>
+  <si>
+    <t>SHA003.png</t>
+  </si>
+  <si>
+    <t>SHA004.png</t>
+  </si>
+  <si>
+    <t>SHA005.png</t>
+  </si>
+  <si>
+    <t>SHA006.png</t>
+  </si>
+  <si>
+    <t>SLUG</t>
   </si>
 </sst>
 </file>
@@ -5009,14 +5012,14 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:P1001"/>
+  <dimension ref="A1:Q1001"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="6" max="6" width="26.140625" customWidth="1"/>
     <col min="7" max="7" width="23" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -5065,8 +5068,11 @@
       <c r="P1" s="1" t="s">
         <v>1357</v>
       </c>
-    </row>
-    <row r="2" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="Q1" s="1" t="s">
+        <v>1537</v>
+      </c>
+    </row>
+    <row r="2" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>15</v>
       </c>
@@ -5092,14 +5098,14 @@
         <v>1078</v>
       </c>
       <c r="J2">
-        <v>2300</v>
+        <v>3300</v>
       </c>
       <c r="K2">
-        <v>4</v>
+        <v>0.5</v>
       </c>
       <c r="L2">
         <f t="shared" ref="L2:L65" si="0">IF(J2="","",J2*(1+K2))</f>
-        <v>11500</v>
+        <v>4950</v>
       </c>
       <c r="M2" t="s">
         <v>16</v>
@@ -5110,8 +5116,11 @@
       <c r="P2" t="s">
         <v>1359</v>
       </c>
-    </row>
-    <row r="3" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="Q2" t="s">
+        <v>1077</v>
+      </c>
+    </row>
+    <row r="3" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>17</v>
       </c>
@@ -5155,8 +5164,11 @@
       <c r="P3" t="s">
         <v>1359</v>
       </c>
-    </row>
-    <row r="4" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="Q3" t="s">
+        <v>1079</v>
+      </c>
+    </row>
+    <row r="4" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>18</v>
       </c>
@@ -5200,8 +5212,11 @@
       <c r="P4" t="s">
         <v>1359</v>
       </c>
-    </row>
-    <row r="5" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="Q4" t="s">
+        <v>1084</v>
+      </c>
+    </row>
+    <row r="5" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>19</v>
       </c>
@@ -5245,8 +5260,11 @@
       <c r="P5" t="s">
         <v>1359</v>
       </c>
-    </row>
-    <row r="6" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="Q5" t="s">
+        <v>1085</v>
+      </c>
+    </row>
+    <row r="6" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>20</v>
       </c>
@@ -5293,8 +5311,11 @@
       <c r="P6" t="s">
         <v>1359</v>
       </c>
-    </row>
-    <row r="7" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="Q6" t="s">
+        <v>1092</v>
+      </c>
+    </row>
+    <row r="7" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>21</v>
       </c>
@@ -5341,8 +5362,11 @@
       <c r="P7" t="s">
         <v>1359</v>
       </c>
-    </row>
-    <row r="8" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="Q7" t="s">
+        <v>1093</v>
+      </c>
+    </row>
+    <row r="8" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>22</v>
       </c>
@@ -5386,8 +5410,11 @@
       <c r="P8" t="s">
         <v>1359</v>
       </c>
-    </row>
-    <row r="9" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="Q8" t="s">
+        <v>1100</v>
+      </c>
+    </row>
+    <row r="9" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>23</v>
       </c>
@@ -5434,8 +5461,11 @@
       <c r="P9" t="s">
         <v>1359</v>
       </c>
-    </row>
-    <row r="10" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="Q9" t="s">
+        <v>1106</v>
+      </c>
+    </row>
+    <row r="10" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
         <v>24</v>
       </c>
@@ -5482,8 +5512,11 @@
       <c r="P10" t="s">
         <v>1359</v>
       </c>
-    </row>
-    <row r="11" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="Q10" t="s">
+        <v>1112</v>
+      </c>
+    </row>
+    <row r="11" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
         <v>25</v>
       </c>
@@ -5527,8 +5560,11 @@
       <c r="P11" t="s">
         <v>1359</v>
       </c>
-    </row>
-    <row r="12" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="Q11" t="s">
+        <v>1117</v>
+      </c>
+    </row>
+    <row r="12" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
         <v>26</v>
       </c>
@@ -5572,8 +5608,11 @@
       <c r="P12" t="s">
         <v>1359</v>
       </c>
-    </row>
-    <row r="13" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="Q12" t="s">
+        <v>1118</v>
+      </c>
+    </row>
+    <row r="13" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
         <v>27</v>
       </c>
@@ -5617,8 +5656,11 @@
       <c r="P13" t="s">
         <v>1359</v>
       </c>
-    </row>
-    <row r="14" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="Q13" t="s">
+        <v>1119</v>
+      </c>
+    </row>
+    <row r="14" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
         <v>28</v>
       </c>
@@ -5662,8 +5704,11 @@
       <c r="P14" t="s">
         <v>1359</v>
       </c>
-    </row>
-    <row r="15" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="Q14" t="s">
+        <v>1120</v>
+      </c>
+    </row>
+    <row r="15" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
         <v>29</v>
       </c>
@@ -5707,8 +5752,11 @@
       <c r="P15" t="s">
         <v>1359</v>
       </c>
-    </row>
-    <row r="16" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="Q15" t="s">
+        <v>1121</v>
+      </c>
+    </row>
+    <row r="16" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
         <v>30</v>
       </c>
@@ -5752,8 +5800,11 @@
       <c r="P16" t="s">
         <v>1359</v>
       </c>
-    </row>
-    <row r="17" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="Q16" t="s">
+        <v>1139</v>
+      </c>
+    </row>
+    <row r="17" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
         <v>31</v>
       </c>
@@ -5797,8 +5848,11 @@
       <c r="P17" t="s">
         <v>1359</v>
       </c>
-    </row>
-    <row r="18" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="Q17" t="s">
+        <v>1140</v>
+      </c>
+    </row>
+    <row r="18" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
         <v>32</v>
       </c>
@@ -5842,8 +5896,11 @@
       <c r="P18" t="s">
         <v>1359</v>
       </c>
-    </row>
-    <row r="19" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="Q18" t="s">
+        <v>1141</v>
+      </c>
+    </row>
+    <row r="19" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
         <v>33</v>
       </c>
@@ -5887,8 +5944,11 @@
       <c r="P19" t="s">
         <v>1359</v>
       </c>
-    </row>
-    <row r="20" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="Q19" t="s">
+        <v>1142</v>
+      </c>
+    </row>
+    <row r="20" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
         <v>34</v>
       </c>
@@ -5932,8 +5992,11 @@
       <c r="P20" t="s">
         <v>1359</v>
       </c>
-    </row>
-    <row r="21" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="Q20" t="s">
+        <v>1143</v>
+      </c>
+    </row>
+    <row r="21" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
         <v>35</v>
       </c>
@@ -5977,8 +6040,11 @@
       <c r="P21" t="s">
         <v>1359</v>
       </c>
-    </row>
-    <row r="22" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="Q21" t="s">
+        <v>1144</v>
+      </c>
+    </row>
+    <row r="22" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
         <v>36</v>
       </c>
@@ -6022,8 +6088,11 @@
       <c r="P22" t="s">
         <v>1359</v>
       </c>
-    </row>
-    <row r="23" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="Q22" t="s">
+        <v>1145</v>
+      </c>
+    </row>
+    <row r="23" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
         <v>37</v>
       </c>
@@ -6067,8 +6136,11 @@
       <c r="P23" t="s">
         <v>1359</v>
       </c>
-    </row>
-    <row r="24" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="Q23" t="s">
+        <v>1146</v>
+      </c>
+    </row>
+    <row r="24" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
         <v>38</v>
       </c>
@@ -6112,8 +6184,11 @@
       <c r="P24" t="s">
         <v>1359</v>
       </c>
-    </row>
-    <row r="25" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="Q24" t="s">
+        <v>1147</v>
+      </c>
+    </row>
+    <row r="25" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
         <v>39</v>
       </c>
@@ -6157,8 +6232,11 @@
       <c r="P25" t="s">
         <v>1359</v>
       </c>
-    </row>
-    <row r="26" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="Q25" t="s">
+        <v>1165</v>
+      </c>
+    </row>
+    <row r="26" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
         <v>40</v>
       </c>
@@ -6202,8 +6280,11 @@
       <c r="P26" t="s">
         <v>1359</v>
       </c>
-    </row>
-    <row r="27" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="Q26" t="s">
+        <v>1166</v>
+      </c>
+    </row>
+    <row r="27" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
         <v>41</v>
       </c>
@@ -6247,8 +6328,11 @@
       <c r="P27" t="s">
         <v>1359</v>
       </c>
-    </row>
-    <row r="28" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="Q27" t="s">
+        <v>1167</v>
+      </c>
+    </row>
+    <row r="28" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
         <v>42</v>
       </c>
@@ -6292,8 +6376,11 @@
       <c r="P28" t="s">
         <v>1359</v>
       </c>
-    </row>
-    <row r="29" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="Q28" t="s">
+        <v>1168</v>
+      </c>
+    </row>
+    <row r="29" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
         <v>43</v>
       </c>
@@ -6337,8 +6424,11 @@
       <c r="P29" t="s">
         <v>1359</v>
       </c>
-    </row>
-    <row r="30" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="Q29" t="s">
+        <v>1169</v>
+      </c>
+    </row>
+    <row r="30" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
         <v>44</v>
       </c>
@@ -6382,8 +6472,11 @@
       <c r="P30" t="s">
         <v>1359</v>
       </c>
-    </row>
-    <row r="31" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="Q30" t="s">
+        <v>1169</v>
+      </c>
+    </row>
+    <row r="31" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
         <v>45</v>
       </c>
@@ -6424,8 +6517,11 @@
       <c r="P31" t="s">
         <v>1359</v>
       </c>
-    </row>
-    <row r="32" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="Q31" t="s">
+        <v>1194</v>
+      </c>
+    </row>
+    <row r="32" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
         <v>46</v>
       </c>
@@ -6466,8 +6562,11 @@
       <c r="P32" t="s">
         <v>1359</v>
       </c>
-    </row>
-    <row r="33" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="Q32" t="s">
+        <v>1195</v>
+      </c>
+    </row>
+    <row r="33" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
         <v>47</v>
       </c>
@@ -6508,8 +6607,11 @@
       <c r="P33" t="s">
         <v>1359</v>
       </c>
-    </row>
-    <row r="34" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="Q33" t="s">
+        <v>1196</v>
+      </c>
+    </row>
+    <row r="34" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
         <v>48</v>
       </c>
@@ -6550,8 +6652,11 @@
       <c r="P34" t="s">
         <v>1359</v>
       </c>
-    </row>
-    <row r="35" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="Q34" t="s">
+        <v>1197</v>
+      </c>
+    </row>
+    <row r="35" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
         <v>49</v>
       </c>
@@ -6592,8 +6697,11 @@
       <c r="P35" t="s">
         <v>1359</v>
       </c>
-    </row>
-    <row r="36" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="Q35" t="s">
+        <v>1198</v>
+      </c>
+    </row>
+    <row r="36" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A36" t="s">
         <v>50</v>
       </c>
@@ -6631,8 +6739,11 @@
       <c r="P36" t="s">
         <v>1359</v>
       </c>
-    </row>
-    <row r="37" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="Q36" t="s">
+        <v>1199</v>
+      </c>
+    </row>
+    <row r="37" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A37" t="s">
         <v>51</v>
       </c>
@@ -6673,8 +6784,11 @@
       <c r="P37" t="s">
         <v>1359</v>
       </c>
-    </row>
-    <row r="38" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="Q37" t="s">
+        <v>1200</v>
+      </c>
+    </row>
+    <row r="38" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A38" t="s">
         <v>52</v>
       </c>
@@ -6715,8 +6829,11 @@
       <c r="P38" t="s">
         <v>1359</v>
       </c>
-    </row>
-    <row r="39" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="Q38" t="s">
+        <v>1201</v>
+      </c>
+    </row>
+    <row r="39" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A39" t="s">
         <v>53</v>
       </c>
@@ -6760,8 +6877,11 @@
       <c r="P39" t="s">
         <v>1359</v>
       </c>
-    </row>
-    <row r="40" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="Q39" t="s">
+        <v>1222</v>
+      </c>
+    </row>
+    <row r="40" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A40" t="s">
         <v>54</v>
       </c>
@@ -6805,8 +6925,11 @@
       <c r="P40" t="s">
         <v>1359</v>
       </c>
-    </row>
-    <row r="41" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="Q40" t="s">
+        <v>1223</v>
+      </c>
+    </row>
+    <row r="41" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A41" t="s">
         <v>55</v>
       </c>
@@ -6850,8 +6973,11 @@
       <c r="P41" t="s">
         <v>1359</v>
       </c>
-    </row>
-    <row r="42" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="Q41" t="s">
+        <v>1224</v>
+      </c>
+    </row>
+    <row r="42" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A42" t="s">
         <v>56</v>
       </c>
@@ -6895,8 +7021,11 @@
       <c r="P42" t="s">
         <v>1359</v>
       </c>
-    </row>
-    <row r="43" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="Q42" t="s">
+        <v>1225</v>
+      </c>
+    </row>
+    <row r="43" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A43" t="s">
         <v>57</v>
       </c>
@@ -6940,8 +7069,11 @@
       <c r="P43" t="s">
         <v>1359</v>
       </c>
-    </row>
-    <row r="44" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="Q43" t="s">
+        <v>1226</v>
+      </c>
+    </row>
+    <row r="44" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A44" t="s">
         <v>58</v>
       </c>
@@ -6985,8 +7117,11 @@
       <c r="P44" t="s">
         <v>1359</v>
       </c>
-    </row>
-    <row r="45" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="Q44" t="s">
+        <v>1240</v>
+      </c>
+    </row>
+    <row r="45" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A45" t="s">
         <v>59</v>
       </c>
@@ -7030,8 +7165,11 @@
       <c r="P45" t="s">
         <v>1359</v>
       </c>
-    </row>
-    <row r="46" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="Q45" t="s">
+        <v>1241</v>
+      </c>
+    </row>
+    <row r="46" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A46" t="s">
         <v>60</v>
       </c>
@@ -7075,8 +7213,11 @@
       <c r="P46" t="s">
         <v>1359</v>
       </c>
-    </row>
-    <row r="47" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="Q46" t="s">
+        <v>1242</v>
+      </c>
+    </row>
+    <row r="47" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A47" t="s">
         <v>61</v>
       </c>
@@ -7120,8 +7261,11 @@
       <c r="P47" t="s">
         <v>1359</v>
       </c>
-    </row>
-    <row r="48" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="Q47" t="s">
+        <v>1243</v>
+      </c>
+    </row>
+    <row r="48" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A48" t="s">
         <v>62</v>
       </c>
@@ -7165,8 +7309,11 @@
       <c r="P48" t="s">
         <v>1359</v>
       </c>
-    </row>
-    <row r="49" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="Q48" t="s">
+        <v>1244</v>
+      </c>
+    </row>
+    <row r="49" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A49" t="s">
         <v>63</v>
       </c>
@@ -7210,8 +7357,11 @@
       <c r="P49" t="s">
         <v>1359</v>
       </c>
-    </row>
-    <row r="50" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="Q49" t="s">
+        <v>1257</v>
+      </c>
+    </row>
+    <row r="50" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A50" t="s">
         <v>64</v>
       </c>
@@ -7255,8 +7405,11 @@
       <c r="P50" t="s">
         <v>1359</v>
       </c>
-    </row>
-    <row r="51" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="Q50" t="s">
+        <v>1258</v>
+      </c>
+    </row>
+    <row r="51" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A51" t="s">
         <v>65</v>
       </c>
@@ -7300,8 +7453,11 @@
       <c r="P51" t="s">
         <v>1359</v>
       </c>
-    </row>
-    <row r="52" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="Q51" t="s">
+        <v>1259</v>
+      </c>
+    </row>
+    <row r="52" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A52" t="s">
         <v>66</v>
       </c>
@@ -7345,8 +7501,11 @@
       <c r="P52" t="s">
         <v>1359</v>
       </c>
-    </row>
-    <row r="53" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="Q52" t="s">
+        <v>1260</v>
+      </c>
+    </row>
+    <row r="53" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A53" t="s">
         <v>67</v>
       </c>
@@ -7390,8 +7549,11 @@
       <c r="P53" t="s">
         <v>1359</v>
       </c>
-    </row>
-    <row r="54" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="Q53" t="s">
+        <v>1261</v>
+      </c>
+    </row>
+    <row r="54" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A54" t="s">
         <v>68</v>
       </c>
@@ -7435,8 +7597,11 @@
       <c r="P54" t="s">
         <v>1359</v>
       </c>
-    </row>
-    <row r="55" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="Q54" t="s">
+        <v>1262</v>
+      </c>
+    </row>
+    <row r="55" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A55" t="s">
         <v>69</v>
       </c>
@@ -7480,8 +7645,11 @@
       <c r="P55" t="s">
         <v>1359</v>
       </c>
-    </row>
-    <row r="56" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="Q55" t="s">
+        <v>1281</v>
+      </c>
+    </row>
+    <row r="56" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A56" t="s">
         <v>70</v>
       </c>
@@ -7525,8 +7693,11 @@
       <c r="P56" t="s">
         <v>1359</v>
       </c>
-    </row>
-    <row r="57" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="Q56" t="s">
+        <v>1285</v>
+      </c>
+    </row>
+    <row r="57" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A57" t="s">
         <v>71</v>
       </c>
@@ -7570,8 +7741,11 @@
       <c r="P57" t="s">
         <v>1359</v>
       </c>
-    </row>
-    <row r="58" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="Q57" t="s">
+        <v>1289</v>
+      </c>
+    </row>
+    <row r="58" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A58" t="s">
         <v>72</v>
       </c>
@@ -7615,8 +7789,11 @@
       <c r="P58" t="s">
         <v>1359</v>
       </c>
-    </row>
-    <row r="59" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="Q58" t="s">
+        <v>1294</v>
+      </c>
+    </row>
+    <row r="59" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A59" t="s">
         <v>73</v>
       </c>
@@ -7660,8 +7837,11 @@
       <c r="P59" t="s">
         <v>1359</v>
       </c>
-    </row>
-    <row r="60" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="Q59" t="s">
+        <v>1297</v>
+      </c>
+    </row>
+    <row r="60" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A60" t="s">
         <v>74</v>
       </c>
@@ -7705,8 +7885,11 @@
       <c r="P60" t="s">
         <v>1359</v>
       </c>
-    </row>
-    <row r="61" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="Q60" t="s">
+        <v>1298</v>
+      </c>
+    </row>
+    <row r="61" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A61" t="s">
         <v>75</v>
       </c>
@@ -7750,8 +7933,11 @@
       <c r="P61" t="s">
         <v>1359</v>
       </c>
-    </row>
-    <row r="62" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="Q61" t="s">
+        <v>1299</v>
+      </c>
+    </row>
+    <row r="62" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A62" t="s">
         <v>76</v>
       </c>
@@ -7795,8 +7981,11 @@
       <c r="P62" t="s">
         <v>1359</v>
       </c>
-    </row>
-    <row r="63" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="Q62" t="s">
+        <v>1300</v>
+      </c>
+    </row>
+    <row r="63" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A63" t="s">
         <v>77</v>
       </c>
@@ -7840,8 +8029,11 @@
       <c r="P63" t="s">
         <v>1359</v>
       </c>
-    </row>
-    <row r="64" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="Q63" t="s">
+        <v>1301</v>
+      </c>
+    </row>
+    <row r="64" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A64" t="s">
         <v>78</v>
       </c>
@@ -7885,8 +8077,11 @@
       <c r="P64" t="s">
         <v>1359</v>
       </c>
-    </row>
-    <row r="65" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="Q64" t="s">
+        <v>1302</v>
+      </c>
+    </row>
+    <row r="65" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A65" t="s">
         <v>79</v>
       </c>
@@ -7930,8 +8125,11 @@
       <c r="P65" t="s">
         <v>1359</v>
       </c>
-    </row>
-    <row r="66" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="Q65" t="s">
+        <v>1303</v>
+      </c>
+    </row>
+    <row r="66" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A66" t="s">
         <v>80</v>
       </c>
@@ -7975,8 +8173,11 @@
       <c r="P66" t="s">
         <v>1359</v>
       </c>
-    </row>
-    <row r="67" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="Q66" t="s">
+        <v>1304</v>
+      </c>
+    </row>
+    <row r="67" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A67" t="s">
         <v>81</v>
       </c>
@@ -8020,8 +8221,11 @@
       <c r="P67" t="s">
         <v>1359</v>
       </c>
-    </row>
-    <row r="68" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="Q67" t="s">
+        <v>1305</v>
+      </c>
+    </row>
+    <row r="68" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A68" t="s">
         <v>82</v>
       </c>
@@ -8065,8 +8269,11 @@
       <c r="P68" t="s">
         <v>1359</v>
       </c>
-    </row>
-    <row r="69" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="Q68" t="s">
+        <v>1306</v>
+      </c>
+    </row>
+    <row r="69" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A69" t="s">
         <v>83</v>
       </c>
@@ -8110,8 +8317,11 @@
       <c r="P69" t="s">
         <v>1359</v>
       </c>
-    </row>
-    <row r="70" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="Q69" t="s">
+        <v>1331</v>
+      </c>
+    </row>
+    <row r="70" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A70" t="s">
         <v>84</v>
       </c>
@@ -8155,8 +8365,11 @@
       <c r="P70" t="s">
         <v>1359</v>
       </c>
-    </row>
-    <row r="71" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="Q70" t="s">
+        <v>1332</v>
+      </c>
+    </row>
+    <row r="71" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A71" t="s">
         <v>85</v>
       </c>
@@ -8200,8 +8413,11 @@
       <c r="P71" t="s">
         <v>1359</v>
       </c>
-    </row>
-    <row r="72" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="Q71" t="s">
+        <v>1333</v>
+      </c>
+    </row>
+    <row r="72" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A72" t="s">
         <v>86</v>
       </c>
@@ -8245,8 +8461,11 @@
       <c r="P72" t="s">
         <v>1359</v>
       </c>
-    </row>
-    <row r="73" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="Q72" t="s">
+        <v>1338</v>
+      </c>
+    </row>
+    <row r="73" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A73" t="s">
         <v>87</v>
       </c>
@@ -8290,8 +8509,11 @@
       <c r="P73" t="s">
         <v>1359</v>
       </c>
-    </row>
-    <row r="74" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="Q73" t="s">
+        <v>1341</v>
+      </c>
+    </row>
+    <row r="74" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A74" t="s">
         <v>88</v>
       </c>
@@ -8335,8 +8557,11 @@
       <c r="P74" t="s">
         <v>1359</v>
       </c>
-    </row>
-    <row r="75" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="Q74" t="s">
+        <v>1342</v>
+      </c>
+    </row>
+    <row r="75" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A75" t="s">
         <v>89</v>
       </c>
@@ -8380,8 +8605,11 @@
       <c r="P75" t="s">
         <v>1359</v>
       </c>
-    </row>
-    <row r="76" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="Q75" t="s">
+        <v>1343</v>
+      </c>
+    </row>
+    <row r="76" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A76" t="s">
         <v>90</v>
       </c>
@@ -8425,8 +8653,11 @@
       <c r="P76" t="s">
         <v>1359</v>
       </c>
-    </row>
-    <row r="77" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="Q76" t="s">
+        <v>1349</v>
+      </c>
+    </row>
+    <row r="77" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A77" t="s">
         <v>91</v>
       </c>
@@ -8470,8 +8701,11 @@
       <c r="P77" t="s">
         <v>1359</v>
       </c>
-    </row>
-    <row r="78" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="Q77" t="s">
+        <v>1352</v>
+      </c>
+    </row>
+    <row r="78" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A78" t="s">
         <v>92</v>
       </c>
@@ -8515,8 +8749,11 @@
       <c r="P78" t="s">
         <v>1359</v>
       </c>
-    </row>
-    <row r="79" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="Q78" t="s">
+        <v>1360</v>
+      </c>
+    </row>
+    <row r="79" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A79" t="s">
         <v>93</v>
       </c>
@@ -8560,8 +8797,11 @@
       <c r="P79" t="s">
         <v>1359</v>
       </c>
-    </row>
-    <row r="80" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="Q79" t="s">
+        <v>1364</v>
+      </c>
+    </row>
+    <row r="80" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A80" t="s">
         <v>94</v>
       </c>
@@ -8608,8 +8848,11 @@
       <c r="P80" t="s">
         <v>1359</v>
       </c>
-    </row>
-    <row r="81" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="Q80" t="s">
+        <v>1365</v>
+      </c>
+    </row>
+    <row r="81" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A81" t="s">
         <v>95</v>
       </c>
@@ -8656,8 +8899,11 @@
       <c r="P81" t="s">
         <v>1359</v>
       </c>
-    </row>
-    <row r="82" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="Q81" t="s">
+        <v>1366</v>
+      </c>
+    </row>
+    <row r="82" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A82" t="s">
         <v>96</v>
       </c>
@@ -8704,8 +8950,11 @@
       <c r="P82" t="s">
         <v>1359</v>
       </c>
-    </row>
-    <row r="83" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="Q82" t="s">
+        <v>1367</v>
+      </c>
+    </row>
+    <row r="83" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A83" t="s">
         <v>97</v>
       </c>
@@ -8752,8 +9001,11 @@
       <c r="P83" t="s">
         <v>1359</v>
       </c>
-    </row>
-    <row r="84" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="Q83" t="s">
+        <v>1376</v>
+      </c>
+    </row>
+    <row r="84" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A84" t="s">
         <v>98</v>
       </c>
@@ -8800,8 +9052,11 @@
       <c r="P84" t="s">
         <v>1359</v>
       </c>
-    </row>
-    <row r="85" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="Q84" t="s">
+        <v>1377</v>
+      </c>
+    </row>
+    <row r="85" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A85" t="s">
         <v>99</v>
       </c>
@@ -8848,8 +9103,11 @@
       <c r="P85" t="s">
         <v>1359</v>
       </c>
-    </row>
-    <row r="86" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="Q85" t="s">
+        <v>1378</v>
+      </c>
+    </row>
+    <row r="86" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A86" t="s">
         <v>100</v>
       </c>
@@ -8896,8 +9154,11 @@
       <c r="P86" t="s">
         <v>1359</v>
       </c>
-    </row>
-    <row r="87" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="Q86" t="s">
+        <v>1379</v>
+      </c>
+    </row>
+    <row r="87" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A87" t="s">
         <v>101</v>
       </c>
@@ -8944,8 +9205,11 @@
       <c r="P87" t="s">
         <v>1359</v>
       </c>
-    </row>
-    <row r="88" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="Q87" t="s">
+        <v>1380</v>
+      </c>
+    </row>
+    <row r="88" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A88" t="s">
         <v>102</v>
       </c>
@@ -8992,8 +9256,11 @@
       <c r="P88" t="s">
         <v>1359</v>
       </c>
-    </row>
-    <row r="89" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="Q88" t="s">
+        <v>1381</v>
+      </c>
+    </row>
+    <row r="89" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A89" t="s">
         <v>103</v>
       </c>
@@ -9037,8 +9304,11 @@
       <c r="P89" t="s">
         <v>1359</v>
       </c>
-    </row>
-    <row r="90" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="Q89" t="s">
+        <v>1398</v>
+      </c>
+    </row>
+    <row r="90" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A90" t="s">
         <v>104</v>
       </c>
@@ -9085,8 +9355,11 @@
       <c r="P90" t="s">
         <v>1359</v>
       </c>
-    </row>
-    <row r="91" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="Q90" t="s">
+        <v>1401</v>
+      </c>
+    </row>
+    <row r="91" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A91" t="s">
         <v>105</v>
       </c>
@@ -9133,8 +9406,11 @@
       <c r="P91" t="s">
         <v>1359</v>
       </c>
-    </row>
-    <row r="92" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="Q91" t="s">
+        <v>1402</v>
+      </c>
+    </row>
+    <row r="92" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A92" t="s">
         <v>106</v>
       </c>
@@ -9181,8 +9457,11 @@
       <c r="P92" t="s">
         <v>1359</v>
       </c>
-    </row>
-    <row r="93" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="Q92" t="s">
+        <v>1403</v>
+      </c>
+    </row>
+    <row r="93" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A93" t="s">
         <v>107</v>
       </c>
@@ -9229,8 +9508,11 @@
       <c r="P93" t="s">
         <v>1359</v>
       </c>
-    </row>
-    <row r="94" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="Q93" t="s">
+        <v>1404</v>
+      </c>
+    </row>
+    <row r="94" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A94" t="s">
         <v>108</v>
       </c>
@@ -9277,8 +9559,11 @@
       <c r="P94" t="s">
         <v>1359</v>
       </c>
-    </row>
-    <row r="95" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="Q94" t="s">
+        <v>1411</v>
+      </c>
+    </row>
+    <row r="95" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A95" t="s">
         <v>109</v>
       </c>
@@ -9325,8 +9610,11 @@
       <c r="P95" t="s">
         <v>1359</v>
       </c>
-    </row>
-    <row r="96" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="Q95" t="s">
+        <v>1412</v>
+      </c>
+    </row>
+    <row r="96" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A96" t="s">
         <v>110</v>
       </c>
@@ -9370,8 +9658,11 @@
       <c r="P96" t="s">
         <v>1359</v>
       </c>
-    </row>
-    <row r="97" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="Q96" t="s">
+        <v>1419</v>
+      </c>
+    </row>
+    <row r="97" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A97" t="s">
         <v>111</v>
       </c>
@@ -9415,8 +9706,11 @@
       <c r="P97" t="s">
         <v>1359</v>
       </c>
-    </row>
-    <row r="98" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="Q97" t="s">
+        <v>1423</v>
+      </c>
+    </row>
+    <row r="98" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A98" t="s">
         <v>112</v>
       </c>
@@ -9442,7 +9736,7 @@
         <v>1164</v>
       </c>
       <c r="I98" t="s">
-        <v>1434</v>
+        <v>1531</v>
       </c>
       <c r="J98">
         <v>4300</v>
@@ -9463,13 +9757,16 @@
       <c r="P98" t="s">
         <v>1359</v>
       </c>
-    </row>
-    <row r="99" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="Q98" t="s">
+        <v>1433</v>
+      </c>
+    </row>
+    <row r="99" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A99" t="s">
         <v>113</v>
       </c>
       <c r="B99" t="s">
-        <v>1441</v>
+        <v>1435</v>
       </c>
       <c r="C99" t="s">
         <v>1426</v>
@@ -9481,7 +9778,7 @@
         <v>1074</v>
       </c>
       <c r="F99" t="s">
-        <v>1440</v>
+        <v>1434</v>
       </c>
       <c r="G99" t="s">
         <v>1428</v>
@@ -9490,7 +9787,7 @@
         <v>1164</v>
       </c>
       <c r="I99" t="s">
-        <v>1435</v>
+        <v>1532</v>
       </c>
       <c r="J99">
         <v>4300</v>
@@ -9511,13 +9808,16 @@
       <c r="P99" t="s">
         <v>1359</v>
       </c>
-    </row>
-    <row r="100" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="Q99" t="s">
+        <v>1435</v>
+      </c>
+    </row>
+    <row r="100" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A100" t="s">
         <v>114</v>
       </c>
       <c r="B100" t="s">
-        <v>1442</v>
+        <v>1436</v>
       </c>
       <c r="C100" t="s">
         <v>1426</v>
@@ -9529,7 +9829,7 @@
         <v>1074</v>
       </c>
       <c r="F100" t="s">
-        <v>1440</v>
+        <v>1434</v>
       </c>
       <c r="G100" t="s">
         <v>1429</v>
@@ -9538,7 +9838,7 @@
         <v>1164</v>
       </c>
       <c r="I100" t="s">
-        <v>1436</v>
+        <v>1533</v>
       </c>
       <c r="J100">
         <v>4300</v>
@@ -9559,13 +9859,16 @@
       <c r="P100" t="s">
         <v>1359</v>
       </c>
-    </row>
-    <row r="101" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="Q100" t="s">
+        <v>1436</v>
+      </c>
+    </row>
+    <row r="101" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A101" t="s">
         <v>115</v>
       </c>
       <c r="B101" t="s">
-        <v>1443</v>
+        <v>1437</v>
       </c>
       <c r="C101" t="s">
         <v>1426</v>
@@ -9577,7 +9880,7 @@
         <v>1074</v>
       </c>
       <c r="F101" t="s">
-        <v>1440</v>
+        <v>1434</v>
       </c>
       <c r="G101" t="s">
         <v>1430</v>
@@ -9586,7 +9889,7 @@
         <v>1164</v>
       </c>
       <c r="I101" t="s">
-        <v>1437</v>
+        <v>1534</v>
       </c>
       <c r="J101">
         <v>4300</v>
@@ -9607,13 +9910,16 @@
       <c r="P101" t="s">
         <v>1359</v>
       </c>
-    </row>
-    <row r="102" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="Q101" t="s">
+        <v>1437</v>
+      </c>
+    </row>
+    <row r="102" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A102" t="s">
         <v>116</v>
       </c>
       <c r="B102" t="s">
-        <v>1444</v>
+        <v>1438</v>
       </c>
       <c r="C102" t="s">
         <v>1426</v>
@@ -9625,7 +9931,7 @@
         <v>1074</v>
       </c>
       <c r="F102" t="s">
-        <v>1440</v>
+        <v>1434</v>
       </c>
       <c r="G102" t="s">
         <v>1431</v>
@@ -9634,7 +9940,7 @@
         <v>1164</v>
       </c>
       <c r="I102" t="s">
-        <v>1438</v>
+        <v>1535</v>
       </c>
       <c r="J102">
         <v>4300</v>
@@ -9655,13 +9961,16 @@
       <c r="P102" t="s">
         <v>1359</v>
       </c>
-    </row>
-    <row r="103" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="Q102" t="s">
+        <v>1438</v>
+      </c>
+    </row>
+    <row r="103" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A103" t="s">
         <v>117</v>
       </c>
       <c r="B103" t="s">
-        <v>1445</v>
+        <v>1439</v>
       </c>
       <c r="C103" t="s">
         <v>1426</v>
@@ -9673,7 +9982,7 @@
         <v>1074</v>
       </c>
       <c r="F103" t="s">
-        <v>1440</v>
+        <v>1434</v>
       </c>
       <c r="G103" t="s">
         <v>1432</v>
@@ -9682,7 +9991,7 @@
         <v>1164</v>
       </c>
       <c r="I103" t="s">
-        <v>1439</v>
+        <v>1536</v>
       </c>
       <c r="J103">
         <v>4300</v>
@@ -9703,34 +10012,37 @@
       <c r="P103" t="s">
         <v>1359</v>
       </c>
-    </row>
-    <row r="104" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="Q103" t="s">
+        <v>1439</v>
+      </c>
+    </row>
+    <row r="104" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A104" t="s">
         <v>118</v>
       </c>
       <c r="B104" t="s">
-        <v>1446</v>
+        <v>1440</v>
       </c>
       <c r="C104" t="s">
-        <v>1460</v>
+        <v>1454</v>
       </c>
       <c r="D104" t="s">
-        <v>1462</v>
+        <v>1456</v>
       </c>
       <c r="E104" t="s">
-        <v>1461</v>
+        <v>1455</v>
       </c>
       <c r="F104" t="s">
-        <v>1462</v>
+        <v>1456</v>
       </c>
       <c r="G104" t="s">
-        <v>1463</v>
+        <v>1457</v>
       </c>
       <c r="H104" t="s">
         <v>1164</v>
       </c>
       <c r="I104" t="s">
-        <v>1475</v>
+        <v>1469</v>
       </c>
       <c r="J104">
         <v>1600</v>
@@ -9751,34 +10063,37 @@
       <c r="P104" t="s">
         <v>1359</v>
       </c>
-    </row>
-    <row r="105" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="Q104" t="s">
+        <v>1440</v>
+      </c>
+    </row>
+    <row r="105" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A105" t="s">
         <v>119</v>
       </c>
       <c r="B105" t="s">
-        <v>1447</v>
+        <v>1441</v>
       </c>
       <c r="C105" t="s">
-        <v>1460</v>
+        <v>1454</v>
       </c>
       <c r="D105" t="s">
-        <v>1462</v>
+        <v>1456</v>
       </c>
       <c r="E105" t="s">
-        <v>1461</v>
+        <v>1455</v>
       </c>
       <c r="F105" t="s">
-        <v>1462</v>
+        <v>1456</v>
       </c>
       <c r="G105" t="s">
-        <v>1464</v>
+        <v>1458</v>
       </c>
       <c r="H105" t="s">
         <v>1164</v>
       </c>
       <c r="I105" t="s">
-        <v>1476</v>
+        <v>1470</v>
       </c>
       <c r="J105">
         <v>1600</v>
@@ -9799,25 +10114,28 @@
       <c r="P105" t="s">
         <v>1359</v>
       </c>
-    </row>
-    <row r="106" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="Q105" t="s">
+        <v>1441</v>
+      </c>
+    </row>
+    <row r="106" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A106" t="s">
         <v>120</v>
       </c>
       <c r="B106" t="s">
-        <v>1448</v>
+        <v>1442</v>
       </c>
       <c r="C106" t="s">
-        <v>1460</v>
+        <v>1454</v>
       </c>
       <c r="D106" t="s">
-        <v>1462</v>
+        <v>1456</v>
       </c>
       <c r="E106" t="s">
-        <v>1461</v>
+        <v>1455</v>
       </c>
       <c r="F106" t="s">
-        <v>1462</v>
+        <v>1456</v>
       </c>
       <c r="G106" t="s">
         <v>1431</v>
@@ -9826,7 +10144,7 @@
         <v>1164</v>
       </c>
       <c r="I106" t="s">
-        <v>1477</v>
+        <v>1471</v>
       </c>
       <c r="J106">
         <v>1600</v>
@@ -9847,34 +10165,37 @@
       <c r="P106" t="s">
         <v>1359</v>
       </c>
-    </row>
-    <row r="107" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="Q106" t="s">
+        <v>1442</v>
+      </c>
+    </row>
+    <row r="107" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A107" t="s">
         <v>121</v>
       </c>
       <c r="B107" t="s">
-        <v>1449</v>
+        <v>1443</v>
       </c>
       <c r="C107" t="s">
-        <v>1460</v>
+        <v>1454</v>
       </c>
       <c r="D107" t="s">
-        <v>1462</v>
+        <v>1456</v>
       </c>
       <c r="E107" t="s">
-        <v>1461</v>
+        <v>1455</v>
       </c>
       <c r="F107" t="s">
-        <v>1462</v>
+        <v>1456</v>
       </c>
       <c r="G107" t="s">
-        <v>1465</v>
+        <v>1459</v>
       </c>
       <c r="H107" t="s">
         <v>1164</v>
       </c>
       <c r="I107" t="s">
-        <v>1478</v>
+        <v>1472</v>
       </c>
       <c r="J107">
         <v>1600</v>
@@ -9895,25 +10216,28 @@
       <c r="P107" t="s">
         <v>1359</v>
       </c>
-    </row>
-    <row r="108" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="Q107" t="s">
+        <v>1443</v>
+      </c>
+    </row>
+    <row r="108" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A108" t="s">
         <v>122</v>
       </c>
       <c r="B108" t="s">
-        <v>1450</v>
+        <v>1444</v>
       </c>
       <c r="C108" t="s">
-        <v>1460</v>
+        <v>1454</v>
       </c>
       <c r="D108" t="s">
-        <v>1462</v>
+        <v>1456</v>
       </c>
       <c r="E108" t="s">
-        <v>1461</v>
+        <v>1455</v>
       </c>
       <c r="F108" t="s">
-        <v>1462</v>
+        <v>1456</v>
       </c>
       <c r="G108" t="s">
         <v>1429</v>
@@ -9922,7 +10246,7 @@
         <v>1164</v>
       </c>
       <c r="I108" t="s">
-        <v>1479</v>
+        <v>1473</v>
       </c>
       <c r="J108">
         <v>1600</v>
@@ -9943,34 +10267,37 @@
       <c r="P108" t="s">
         <v>1359</v>
       </c>
-    </row>
-    <row r="109" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="Q108" t="s">
+        <v>1444</v>
+      </c>
+    </row>
+    <row r="109" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A109" t="s">
         <v>123</v>
       </c>
       <c r="B109" t="s">
-        <v>1451</v>
+        <v>1445</v>
       </c>
       <c r="C109" t="s">
+        <v>1454</v>
+      </c>
+      <c r="D109" t="s">
+        <v>1456</v>
+      </c>
+      <c r="E109" t="s">
+        <v>1455</v>
+      </c>
+      <c r="F109" t="s">
+        <v>1456</v>
+      </c>
+      <c r="G109" t="s">
         <v>1460</v>
-      </c>
-      <c r="D109" t="s">
-        <v>1462</v>
-      </c>
-      <c r="E109" t="s">
-        <v>1461</v>
-      </c>
-      <c r="F109" t="s">
-        <v>1462</v>
-      </c>
-      <c r="G109" t="s">
-        <v>1466</v>
       </c>
       <c r="H109" t="s">
         <v>1164</v>
       </c>
       <c r="I109" t="s">
-        <v>1480</v>
+        <v>1474</v>
       </c>
       <c r="J109">
         <v>1600</v>
@@ -9991,34 +10318,37 @@
       <c r="P109" t="s">
         <v>1359</v>
       </c>
-    </row>
-    <row r="110" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="Q109" t="s">
+        <v>1445</v>
+      </c>
+    </row>
+    <row r="110" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A110" t="s">
         <v>124</v>
       </c>
       <c r="B110" t="s">
-        <v>1452</v>
+        <v>1446</v>
       </c>
       <c r="C110" t="s">
-        <v>1460</v>
+        <v>1454</v>
       </c>
       <c r="D110" t="s">
-        <v>1462</v>
+        <v>1456</v>
       </c>
       <c r="E110" t="s">
+        <v>1455</v>
+      </c>
+      <c r="F110" t="s">
+        <v>1456</v>
+      </c>
+      <c r="G110" t="s">
         <v>1461</v>
-      </c>
-      <c r="F110" t="s">
-        <v>1462</v>
-      </c>
-      <c r="G110" t="s">
-        <v>1467</v>
       </c>
       <c r="H110" t="s">
         <v>1164</v>
       </c>
       <c r="I110" t="s">
-        <v>1481</v>
+        <v>1475</v>
       </c>
       <c r="J110">
         <v>1600</v>
@@ -10039,34 +10369,37 @@
       <c r="P110" t="s">
         <v>1359</v>
       </c>
-    </row>
-    <row r="111" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="Q110" t="s">
+        <v>1446</v>
+      </c>
+    </row>
+    <row r="111" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A111" t="s">
         <v>125</v>
       </c>
       <c r="B111" t="s">
-        <v>1453</v>
+        <v>1447</v>
       </c>
       <c r="C111" t="s">
-        <v>1460</v>
+        <v>1454</v>
       </c>
       <c r="D111" t="s">
+        <v>1456</v>
+      </c>
+      <c r="E111" t="s">
+        <v>1455</v>
+      </c>
+      <c r="F111" t="s">
+        <v>1456</v>
+      </c>
+      <c r="G111" t="s">
         <v>1462</v>
-      </c>
-      <c r="E111" t="s">
-        <v>1461</v>
-      </c>
-      <c r="F111" t="s">
-        <v>1462</v>
-      </c>
-      <c r="G111" t="s">
-        <v>1468</v>
       </c>
       <c r="H111" t="s">
         <v>1164</v>
       </c>
       <c r="I111" t="s">
-        <v>1482</v>
+        <v>1476</v>
       </c>
       <c r="J111">
         <v>1600</v>
@@ -10087,34 +10420,37 @@
       <c r="P111" t="s">
         <v>1359</v>
       </c>
-    </row>
-    <row r="112" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="Q111" t="s">
+        <v>1447</v>
+      </c>
+    </row>
+    <row r="112" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A112" t="s">
         <v>126</v>
       </c>
       <c r="B112" t="s">
+        <v>1448</v>
+      </c>
+      <c r="C112" t="s">
         <v>1454</v>
       </c>
-      <c r="C112" t="s">
-        <v>1460</v>
-      </c>
       <c r="D112" t="s">
-        <v>1462</v>
+        <v>1456</v>
       </c>
       <c r="E112" t="s">
-        <v>1461</v>
+        <v>1455</v>
       </c>
       <c r="F112" t="s">
-        <v>1462</v>
+        <v>1456</v>
       </c>
       <c r="G112" t="s">
-        <v>1469</v>
+        <v>1463</v>
       </c>
       <c r="H112" t="s">
         <v>1164</v>
       </c>
       <c r="I112" t="s">
-        <v>1483</v>
+        <v>1477</v>
       </c>
       <c r="J112">
         <v>1600</v>
@@ -10135,34 +10471,37 @@
       <c r="P112" t="s">
         <v>1359</v>
       </c>
-    </row>
-    <row r="113" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="Q112" t="s">
+        <v>1448</v>
+      </c>
+    </row>
+    <row r="113" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A113" t="s">
         <v>127</v>
       </c>
       <c r="B113" t="s">
+        <v>1449</v>
+      </c>
+      <c r="C113" t="s">
+        <v>1454</v>
+      </c>
+      <c r="D113" t="s">
+        <v>1456</v>
+      </c>
+      <c r="E113" t="s">
         <v>1455</v>
       </c>
-      <c r="C113" t="s">
-        <v>1460</v>
-      </c>
-      <c r="D113" t="s">
-        <v>1462</v>
-      </c>
-      <c r="E113" t="s">
-        <v>1461</v>
-      </c>
       <c r="F113" t="s">
-        <v>1462</v>
+        <v>1456</v>
       </c>
       <c r="G113" t="s">
-        <v>1470</v>
+        <v>1464</v>
       </c>
       <c r="H113" t="s">
         <v>1164</v>
       </c>
       <c r="I113" t="s">
-        <v>1484</v>
+        <v>1478</v>
       </c>
       <c r="J113">
         <v>1600</v>
@@ -10183,34 +10522,37 @@
       <c r="P113" t="s">
         <v>1359</v>
       </c>
-    </row>
-    <row r="114" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="Q113" t="s">
+        <v>1449</v>
+      </c>
+    </row>
+    <row r="114" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A114" t="s">
         <v>128</v>
       </c>
       <c r="B114" t="s">
+        <v>1450</v>
+      </c>
+      <c r="C114" t="s">
+        <v>1454</v>
+      </c>
+      <c r="D114" t="s">
         <v>1456</v>
       </c>
-      <c r="C114" t="s">
-        <v>1460</v>
-      </c>
-      <c r="D114" t="s">
-        <v>1462</v>
-      </c>
       <c r="E114" t="s">
-        <v>1461</v>
+        <v>1455</v>
       </c>
       <c r="F114" t="s">
-        <v>1462</v>
+        <v>1456</v>
       </c>
       <c r="G114" t="s">
-        <v>1471</v>
+        <v>1465</v>
       </c>
       <c r="H114" t="s">
         <v>1164</v>
       </c>
       <c r="I114" t="s">
-        <v>1485</v>
+        <v>1479</v>
       </c>
       <c r="J114">
         <v>1600</v>
@@ -10231,34 +10573,37 @@
       <c r="P114" t="s">
         <v>1359</v>
       </c>
-    </row>
-    <row r="115" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="Q114" t="s">
+        <v>1450</v>
+      </c>
+    </row>
+    <row r="115" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A115" t="s">
         <v>129</v>
       </c>
       <c r="B115" t="s">
-        <v>1457</v>
+        <v>1451</v>
       </c>
       <c r="C115" t="s">
-        <v>1460</v>
+        <v>1454</v>
       </c>
       <c r="D115" t="s">
-        <v>1462</v>
+        <v>1456</v>
       </c>
       <c r="E115" t="s">
-        <v>1461</v>
+        <v>1455</v>
       </c>
       <c r="F115" t="s">
-        <v>1462</v>
+        <v>1456</v>
       </c>
       <c r="G115" t="s">
-        <v>1472</v>
+        <v>1466</v>
       </c>
       <c r="H115" t="s">
         <v>1164</v>
       </c>
       <c r="I115" t="s">
-        <v>1486</v>
+        <v>1480</v>
       </c>
       <c r="J115">
         <v>1600</v>
@@ -10279,34 +10624,37 @@
       <c r="P115" t="s">
         <v>1359</v>
       </c>
-    </row>
-    <row r="116" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="Q115" t="s">
+        <v>1451</v>
+      </c>
+    </row>
+    <row r="116" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A116" t="s">
         <v>130</v>
       </c>
       <c r="B116" t="s">
-        <v>1458</v>
+        <v>1452</v>
       </c>
       <c r="C116" t="s">
-        <v>1460</v>
+        <v>1454</v>
       </c>
       <c r="D116" t="s">
-        <v>1462</v>
+        <v>1456</v>
       </c>
       <c r="E116" t="s">
-        <v>1461</v>
+        <v>1455</v>
       </c>
       <c r="F116" t="s">
-        <v>1462</v>
+        <v>1456</v>
       </c>
       <c r="G116" t="s">
-        <v>1473</v>
+        <v>1467</v>
       </c>
       <c r="H116" t="s">
         <v>1164</v>
       </c>
       <c r="I116" t="s">
-        <v>1487</v>
+        <v>1481</v>
       </c>
       <c r="J116">
         <v>1600</v>
@@ -10327,34 +10675,37 @@
       <c r="P116" t="s">
         <v>1359</v>
       </c>
-    </row>
-    <row r="117" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="Q116" t="s">
+        <v>1452</v>
+      </c>
+    </row>
+    <row r="117" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A117" t="s">
         <v>131</v>
       </c>
       <c r="B117" t="s">
-        <v>1459</v>
+        <v>1453</v>
       </c>
       <c r="C117" t="s">
-        <v>1460</v>
+        <v>1454</v>
       </c>
       <c r="D117" t="s">
-        <v>1462</v>
+        <v>1456</v>
       </c>
       <c r="E117" t="s">
-        <v>1461</v>
+        <v>1455</v>
       </c>
       <c r="F117" t="s">
-        <v>1462</v>
+        <v>1456</v>
       </c>
       <c r="G117" t="s">
-        <v>1474</v>
+        <v>1468</v>
       </c>
       <c r="H117" t="s">
         <v>1164</v>
       </c>
       <c r="I117" t="s">
-        <v>1488</v>
+        <v>1482</v>
       </c>
       <c r="J117">
         <v>1600</v>
@@ -10375,34 +10726,37 @@
       <c r="P117" t="s">
         <v>1359</v>
       </c>
-    </row>
-    <row r="118" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="Q117" t="s">
+        <v>1453</v>
+      </c>
+    </row>
+    <row r="118" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A118" t="s">
         <v>132</v>
       </c>
       <c r="B118" t="s">
-        <v>1489</v>
+        <v>1483</v>
       </c>
       <c r="C118" t="s">
-        <v>1460</v>
+        <v>1454</v>
       </c>
       <c r="D118" t="s">
-        <v>1497</v>
+        <v>1491</v>
       </c>
       <c r="E118" t="s">
-        <v>1461</v>
+        <v>1455</v>
       </c>
       <c r="F118" t="s">
-        <v>1497</v>
+        <v>1491</v>
       </c>
       <c r="G118" t="s">
-        <v>1463</v>
+        <v>1457</v>
       </c>
       <c r="H118" t="s">
         <v>1164</v>
       </c>
       <c r="I118" t="s">
-        <v>1502</v>
+        <v>1496</v>
       </c>
       <c r="J118">
         <v>2000</v>
@@ -10423,34 +10777,37 @@
       <c r="P118" t="s">
         <v>1359</v>
       </c>
-    </row>
-    <row r="119" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="Q118" t="s">
+        <v>1483</v>
+      </c>
+    </row>
+    <row r="119" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A119" t="s">
         <v>133</v>
       </c>
       <c r="B119" t="s">
-        <v>1490</v>
+        <v>1484</v>
       </c>
       <c r="C119" t="s">
-        <v>1460</v>
+        <v>1454</v>
       </c>
       <c r="D119" t="s">
-        <v>1497</v>
+        <v>1491</v>
       </c>
       <c r="E119" t="s">
-        <v>1461</v>
+        <v>1455</v>
       </c>
       <c r="F119" t="s">
-        <v>1497</v>
+        <v>1491</v>
       </c>
       <c r="G119" t="s">
-        <v>1464</v>
+        <v>1458</v>
       </c>
       <c r="H119" t="s">
         <v>1164</v>
       </c>
       <c r="I119" t="s">
-        <v>1503</v>
+        <v>1497</v>
       </c>
       <c r="J119">
         <v>2000</v>
@@ -10471,34 +10828,37 @@
       <c r="P119" t="s">
         <v>1359</v>
       </c>
-    </row>
-    <row r="120" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="Q119" t="s">
+        <v>1484</v>
+      </c>
+    </row>
+    <row r="120" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A120" t="s">
         <v>134</v>
       </c>
       <c r="B120" t="s">
+        <v>1485</v>
+      </c>
+      <c r="C120" t="s">
+        <v>1454</v>
+      </c>
+      <c r="D120" t="s">
         <v>1491</v>
       </c>
-      <c r="C120" t="s">
-        <v>1460</v>
-      </c>
-      <c r="D120" t="s">
-        <v>1497</v>
-      </c>
       <c r="E120" t="s">
+        <v>1455</v>
+      </c>
+      <c r="F120" t="s">
+        <v>1491</v>
+      </c>
+      <c r="G120" t="s">
         <v>1461</v>
-      </c>
-      <c r="F120" t="s">
-        <v>1497</v>
-      </c>
-      <c r="G120" t="s">
-        <v>1467</v>
       </c>
       <c r="H120" t="s">
         <v>1164</v>
       </c>
       <c r="I120" t="s">
-        <v>1504</v>
+        <v>1498</v>
       </c>
       <c r="J120">
         <v>2000</v>
@@ -10519,34 +10879,37 @@
       <c r="P120" t="s">
         <v>1359</v>
       </c>
-    </row>
-    <row r="121" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="Q120" t="s">
+        <v>1485</v>
+      </c>
+    </row>
+    <row r="121" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A121" t="s">
         <v>135</v>
       </c>
       <c r="B121" t="s">
+        <v>1486</v>
+      </c>
+      <c r="C121" t="s">
+        <v>1454</v>
+      </c>
+      <c r="D121" t="s">
+        <v>1491</v>
+      </c>
+      <c r="E121" t="s">
+        <v>1455</v>
+      </c>
+      <c r="F121" t="s">
+        <v>1491</v>
+      </c>
+      <c r="G121" t="s">
         <v>1492</v>
-      </c>
-      <c r="C121" t="s">
-        <v>1460</v>
-      </c>
-      <c r="D121" t="s">
-        <v>1497</v>
-      </c>
-      <c r="E121" t="s">
-        <v>1461</v>
-      </c>
-      <c r="F121" t="s">
-        <v>1497</v>
-      </c>
-      <c r="G121" t="s">
-        <v>1498</v>
       </c>
       <c r="H121" t="s">
         <v>1164</v>
       </c>
       <c r="I121" t="s">
-        <v>1505</v>
+        <v>1499</v>
       </c>
       <c r="J121">
         <v>2000</v>
@@ -10567,34 +10930,37 @@
       <c r="P121" t="s">
         <v>1359</v>
       </c>
-    </row>
-    <row r="122" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="Q121" t="s">
+        <v>1486</v>
+      </c>
+    </row>
+    <row r="122" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A122" t="s">
         <v>136</v>
       </c>
       <c r="B122" t="s">
+        <v>1487</v>
+      </c>
+      <c r="C122" t="s">
+        <v>1454</v>
+      </c>
+      <c r="D122" t="s">
+        <v>1491</v>
+      </c>
+      <c r="E122" t="s">
+        <v>1455</v>
+      </c>
+      <c r="F122" t="s">
+        <v>1491</v>
+      </c>
+      <c r="G122" t="s">
         <v>1493</v>
-      </c>
-      <c r="C122" t="s">
-        <v>1460</v>
-      </c>
-      <c r="D122" t="s">
-        <v>1497</v>
-      </c>
-      <c r="E122" t="s">
-        <v>1461</v>
-      </c>
-      <c r="F122" t="s">
-        <v>1497</v>
-      </c>
-      <c r="G122" t="s">
-        <v>1499</v>
       </c>
       <c r="H122" t="s">
         <v>1164</v>
       </c>
       <c r="I122" t="s">
-        <v>1506</v>
+        <v>1500</v>
       </c>
       <c r="J122">
         <v>2000</v>
@@ -10615,34 +10981,37 @@
       <c r="P122" t="s">
         <v>1359</v>
       </c>
-    </row>
-    <row r="123" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="Q122" t="s">
+        <v>1487</v>
+      </c>
+    </row>
+    <row r="123" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A123" t="s">
         <v>137</v>
       </c>
       <c r="B123" t="s">
+        <v>1488</v>
+      </c>
+      <c r="C123" t="s">
+        <v>1454</v>
+      </c>
+      <c r="D123" t="s">
+        <v>1491</v>
+      </c>
+      <c r="E123" t="s">
+        <v>1455</v>
+      </c>
+      <c r="F123" t="s">
+        <v>1491</v>
+      </c>
+      <c r="G123" t="s">
         <v>1494</v>
-      </c>
-      <c r="C123" t="s">
-        <v>1460</v>
-      </c>
-      <c r="D123" t="s">
-        <v>1497</v>
-      </c>
-      <c r="E123" t="s">
-        <v>1461</v>
-      </c>
-      <c r="F123" t="s">
-        <v>1497</v>
-      </c>
-      <c r="G123" t="s">
-        <v>1500</v>
       </c>
       <c r="H123" t="s">
         <v>1164</v>
       </c>
       <c r="I123" t="s">
-        <v>1507</v>
+        <v>1501</v>
       </c>
       <c r="J123">
         <v>2000</v>
@@ -10663,34 +11032,37 @@
       <c r="P123" t="s">
         <v>1359</v>
       </c>
-    </row>
-    <row r="124" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="Q123" t="s">
+        <v>1488</v>
+      </c>
+    </row>
+    <row r="124" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A124" t="s">
         <v>138</v>
       </c>
       <c r="B124" t="s">
-        <v>1495</v>
+        <v>1489</v>
       </c>
       <c r="C124" t="s">
-        <v>1460</v>
+        <v>1454</v>
       </c>
       <c r="D124" t="s">
-        <v>1497</v>
+        <v>1491</v>
       </c>
       <c r="E124" t="s">
-        <v>1461</v>
+        <v>1455</v>
       </c>
       <c r="F124" t="s">
-        <v>1497</v>
+        <v>1491</v>
       </c>
       <c r="G124" t="s">
-        <v>1465</v>
+        <v>1459</v>
       </c>
       <c r="H124" t="s">
         <v>1164</v>
       </c>
       <c r="I124" t="s">
-        <v>1508</v>
+        <v>1502</v>
       </c>
       <c r="J124">
         <v>2000</v>
@@ -10711,34 +11083,37 @@
       <c r="P124" t="s">
         <v>1359</v>
       </c>
-    </row>
-    <row r="125" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="Q124" t="s">
+        <v>1489</v>
+      </c>
+    </row>
+    <row r="125" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A125" t="s">
         <v>139</v>
       </c>
       <c r="B125" t="s">
-        <v>1496</v>
+        <v>1490</v>
       </c>
       <c r="C125" t="s">
-        <v>1460</v>
+        <v>1454</v>
       </c>
       <c r="D125" t="s">
-        <v>1497</v>
+        <v>1491</v>
       </c>
       <c r="E125" t="s">
-        <v>1461</v>
+        <v>1455</v>
       </c>
       <c r="F125" t="s">
-        <v>1497</v>
+        <v>1491</v>
       </c>
       <c r="G125" t="s">
-        <v>1501</v>
+        <v>1495</v>
       </c>
       <c r="H125" t="s">
         <v>1164</v>
       </c>
       <c r="I125" t="s">
-        <v>1509</v>
+        <v>1503</v>
       </c>
       <c r="J125">
         <v>2000</v>
@@ -10759,34 +11134,37 @@
       <c r="P125" t="s">
         <v>1359</v>
       </c>
-    </row>
-    <row r="126" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="Q125" t="s">
+        <v>1490</v>
+      </c>
+    </row>
+    <row r="126" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A126" t="s">
         <v>140</v>
       </c>
       <c r="B126" t="s">
+        <v>1504</v>
+      </c>
+      <c r="C126" t="s">
+        <v>1454</v>
+      </c>
+      <c r="D126" t="s">
+        <v>1509</v>
+      </c>
+      <c r="E126" t="s">
+        <v>1455</v>
+      </c>
+      <c r="F126" t="s">
+        <v>1509</v>
+      </c>
+      <c r="G126" t="s">
         <v>1510</v>
-      </c>
-      <c r="C126" t="s">
-        <v>1460</v>
-      </c>
-      <c r="D126" t="s">
-        <v>1515</v>
-      </c>
-      <c r="E126" t="s">
-        <v>1461</v>
-      </c>
-      <c r="F126" t="s">
-        <v>1515</v>
-      </c>
-      <c r="G126" t="s">
-        <v>1516</v>
       </c>
       <c r="H126" t="s">
         <v>1164</v>
       </c>
       <c r="I126" t="s">
-        <v>1521</v>
+        <v>1515</v>
       </c>
       <c r="J126">
         <v>2000</v>
@@ -10807,34 +11185,37 @@
       <c r="P126" t="s">
         <v>1359</v>
       </c>
-    </row>
-    <row r="127" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="Q126" t="s">
+        <v>1504</v>
+      </c>
+    </row>
+    <row r="127" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A127" t="s">
         <v>141</v>
       </c>
       <c r="B127" t="s">
+        <v>1505</v>
+      </c>
+      <c r="C127" t="s">
+        <v>1454</v>
+      </c>
+      <c r="D127" t="s">
+        <v>1509</v>
+      </c>
+      <c r="E127" t="s">
+        <v>1455</v>
+      </c>
+      <c r="F127" t="s">
+        <v>1509</v>
+      </c>
+      <c r="G127" t="s">
         <v>1511</v>
-      </c>
-      <c r="C127" t="s">
-        <v>1460</v>
-      </c>
-      <c r="D127" t="s">
-        <v>1515</v>
-      </c>
-      <c r="E127" t="s">
-        <v>1461</v>
-      </c>
-      <c r="F127" t="s">
-        <v>1515</v>
-      </c>
-      <c r="G127" t="s">
-        <v>1517</v>
       </c>
       <c r="H127" t="s">
         <v>1164</v>
       </c>
       <c r="I127" t="s">
-        <v>1522</v>
+        <v>1516</v>
       </c>
       <c r="J127">
         <v>2000</v>
@@ -10855,34 +11236,37 @@
       <c r="P127" t="s">
         <v>1359</v>
       </c>
-    </row>
-    <row r="128" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="Q127" t="s">
+        <v>1505</v>
+      </c>
+    </row>
+    <row r="128" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A128" t="s">
         <v>142</v>
       </c>
       <c r="B128" t="s">
+        <v>1506</v>
+      </c>
+      <c r="C128" t="s">
+        <v>1454</v>
+      </c>
+      <c r="D128" t="s">
+        <v>1509</v>
+      </c>
+      <c r="E128" t="s">
+        <v>1455</v>
+      </c>
+      <c r="F128" t="s">
+        <v>1509</v>
+      </c>
+      <c r="G128" t="s">
         <v>1512</v>
-      </c>
-      <c r="C128" t="s">
-        <v>1460</v>
-      </c>
-      <c r="D128" t="s">
-        <v>1515</v>
-      </c>
-      <c r="E128" t="s">
-        <v>1461</v>
-      </c>
-      <c r="F128" t="s">
-        <v>1515</v>
-      </c>
-      <c r="G128" t="s">
-        <v>1518</v>
       </c>
       <c r="H128" t="s">
         <v>1164</v>
       </c>
       <c r="I128" t="s">
-        <v>1523</v>
+        <v>1517</v>
       </c>
       <c r="J128">
         <v>2000</v>
@@ -10903,34 +11287,37 @@
       <c r="P128" t="s">
         <v>1359</v>
       </c>
-    </row>
-    <row r="129" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="Q128" t="s">
+        <v>1506</v>
+      </c>
+    </row>
+    <row r="129" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A129" t="s">
         <v>143</v>
       </c>
       <c r="B129" t="s">
+        <v>1507</v>
+      </c>
+      <c r="C129" t="s">
+        <v>1454</v>
+      </c>
+      <c r="D129" t="s">
+        <v>1509</v>
+      </c>
+      <c r="E129" t="s">
+        <v>1455</v>
+      </c>
+      <c r="F129" t="s">
+        <v>1509</v>
+      </c>
+      <c r="G129" t="s">
         <v>1513</v>
-      </c>
-      <c r="C129" t="s">
-        <v>1460</v>
-      </c>
-      <c r="D129" t="s">
-        <v>1515</v>
-      </c>
-      <c r="E129" t="s">
-        <v>1461</v>
-      </c>
-      <c r="F129" t="s">
-        <v>1515</v>
-      </c>
-      <c r="G129" t="s">
-        <v>1519</v>
       </c>
       <c r="H129" t="s">
         <v>1164</v>
       </c>
       <c r="I129" t="s">
-        <v>1524</v>
+        <v>1518</v>
       </c>
       <c r="J129">
         <v>2000</v>
@@ -10951,34 +11338,37 @@
       <c r="P129" t="s">
         <v>1359</v>
       </c>
-    </row>
-    <row r="130" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="Q129" t="s">
+        <v>1507</v>
+      </c>
+    </row>
+    <row r="130" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A130" t="s">
         <v>144</v>
       </c>
       <c r="B130" t="s">
+        <v>1508</v>
+      </c>
+      <c r="C130" t="s">
+        <v>1454</v>
+      </c>
+      <c r="D130" t="s">
+        <v>1509</v>
+      </c>
+      <c r="E130" t="s">
+        <v>1455</v>
+      </c>
+      <c r="F130" t="s">
+        <v>1509</v>
+      </c>
+      <c r="G130" t="s">
         <v>1514</v>
-      </c>
-      <c r="C130" t="s">
-        <v>1460</v>
-      </c>
-      <c r="D130" t="s">
-        <v>1515</v>
-      </c>
-      <c r="E130" t="s">
-        <v>1461</v>
-      </c>
-      <c r="F130" t="s">
-        <v>1515</v>
-      </c>
-      <c r="G130" t="s">
-        <v>1520</v>
       </c>
       <c r="H130" t="s">
         <v>1164</v>
       </c>
       <c r="I130" t="s">
-        <v>1525</v>
+        <v>1519</v>
       </c>
       <c r="J130">
         <v>2000</v>
@@ -10999,31 +11389,34 @@
       <c r="P130" t="s">
         <v>1359</v>
       </c>
-    </row>
-    <row r="131" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="Q130" t="s">
+        <v>1508</v>
+      </c>
+    </row>
+    <row r="131" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A131" t="s">
         <v>145</v>
       </c>
       <c r="B131" t="s">
-        <v>1526</v>
+        <v>1520</v>
       </c>
       <c r="C131" t="s">
-        <v>1529</v>
+        <v>1523</v>
       </c>
       <c r="D131" t="s">
-        <v>1530</v>
+        <v>1524</v>
       </c>
       <c r="E131" t="s">
         <v>1074</v>
       </c>
       <c r="F131" t="s">
-        <v>1530</v>
+        <v>1524</v>
       </c>
       <c r="H131" t="s">
         <v>1164</v>
       </c>
       <c r="I131" t="s">
-        <v>1534</v>
+        <v>1528</v>
       </c>
       <c r="J131">
         <v>20000</v>
@@ -11044,31 +11437,34 @@
       <c r="P131" t="s">
         <v>1358</v>
       </c>
-    </row>
-    <row r="132" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="Q131" t="s">
+        <v>1520</v>
+      </c>
+    </row>
+    <row r="132" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A132" t="s">
         <v>146</v>
       </c>
       <c r="B132" t="s">
-        <v>1527</v>
+        <v>1521</v>
       </c>
       <c r="C132" t="s">
-        <v>1529</v>
+        <v>1523</v>
       </c>
       <c r="D132" t="s">
-        <v>1531</v>
+        <v>1525</v>
       </c>
       <c r="E132" t="s">
         <v>1074</v>
       </c>
       <c r="F132" t="s">
-        <v>1532</v>
+        <v>1526</v>
       </c>
       <c r="H132" t="s">
         <v>1164</v>
       </c>
       <c r="I132" t="s">
-        <v>1535</v>
+        <v>1529</v>
       </c>
       <c r="J132">
         <v>6500</v>
@@ -11089,31 +11485,34 @@
       <c r="P132" t="s">
         <v>1358</v>
       </c>
-    </row>
-    <row r="133" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="Q132" t="s">
+        <v>1521</v>
+      </c>
+    </row>
+    <row r="133" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A133" t="s">
         <v>147</v>
       </c>
       <c r="B133" t="s">
-        <v>1528</v>
+        <v>1522</v>
       </c>
       <c r="C133" t="s">
-        <v>1529</v>
+        <v>1523</v>
       </c>
       <c r="D133" t="s">
-        <v>1533</v>
+        <v>1527</v>
       </c>
       <c r="E133" t="s">
         <v>1074</v>
       </c>
       <c r="F133" t="s">
-        <v>1533</v>
+        <v>1527</v>
       </c>
       <c r="H133" t="s">
         <v>1164</v>
       </c>
       <c r="I133" t="s">
-        <v>1536</v>
+        <v>1530</v>
       </c>
       <c r="J133">
         <v>9000</v>
@@ -11134,8 +11533,11 @@
       <c r="P133" t="s">
         <v>1358</v>
       </c>
-    </row>
-    <row r="134" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="Q133" t="s">
+        <v>1522</v>
+      </c>
+    </row>
+    <row r="134" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A134" t="s">
         <v>148</v>
       </c>
@@ -11156,7 +11558,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="135" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="135" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A135" t="s">
         <v>149</v>
       </c>
@@ -11177,7 +11579,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="136" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="136" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A136" t="s">
         <v>150</v>
       </c>
@@ -11198,7 +11600,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="137" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="137" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A137" t="s">
         <v>151</v>
       </c>
@@ -11219,7 +11621,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="138" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="138" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A138" t="s">
         <v>152</v>
       </c>
@@ -11240,7 +11642,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="139" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="139" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A139" t="s">
         <v>153</v>
       </c>
@@ -11261,7 +11663,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="140" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="140" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A140" t="s">
         <v>154</v>
       </c>
@@ -11282,7 +11684,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="141" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="141" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A141" t="s">
         <v>155</v>
       </c>
@@ -11303,7 +11705,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="142" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="142" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A142" t="s">
         <v>156</v>
       </c>
@@ -11324,7 +11726,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="143" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="143" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A143" t="s">
         <v>157</v>
       </c>
@@ -11345,7 +11747,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="144" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="144" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A144" t="s">
         <v>158</v>
       </c>

--- a/public/Plantilla_Quimica_Bethel_2.0.xlsx
+++ b/public/Plantilla_Quimica_Bethel_2.0.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\facun\Desktop\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BD242BD2-69A6-42B0-931C-D15CB1477EDB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BE20CAF8-9A1E-45E4-BC13-64511238C9FC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="6585" yWindow="3120" windowWidth="11460" windowHeight="7845" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="19440" windowHeight="14880" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="PRODUCTOS" sheetId="1" r:id="rId1"/>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4477" uniqueCount="1575">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5238" uniqueCount="1886">
   <si>
     <t>ID</t>
   </si>
@@ -4764,6 +4764,939 @@
   </si>
   <si>
     <t>SUA006.png</t>
+  </si>
+  <si>
+    <t>DPP001</t>
+  </si>
+  <si>
+    <t>Desodorante para piso</t>
+  </si>
+  <si>
+    <t>DPP001.png</t>
+  </si>
+  <si>
+    <t>DPP002</t>
+  </si>
+  <si>
+    <t>DPP002.png</t>
+  </si>
+  <si>
+    <t>DPP003.png</t>
+  </si>
+  <si>
+    <t>Desodorante para piso pack x 6 unidades</t>
+  </si>
+  <si>
+    <t>Desodorante para piso x 1 litro</t>
+  </si>
+  <si>
+    <t>Desodorante para piso x 5 litros</t>
+  </si>
+  <si>
+    <t>DPP003</t>
+  </si>
+  <si>
+    <t>DPP004</t>
+  </si>
+  <si>
+    <t>DPP005</t>
+  </si>
+  <si>
+    <t>DPP006</t>
+  </si>
+  <si>
+    <t>Cherry</t>
+  </si>
+  <si>
+    <t>1 pack</t>
+  </si>
+  <si>
+    <t>DPP004.png</t>
+  </si>
+  <si>
+    <t>DPP005.png</t>
+  </si>
+  <si>
+    <t>DPP006.png</t>
+  </si>
+  <si>
+    <t>DPP007</t>
+  </si>
+  <si>
+    <t>DPP008</t>
+  </si>
+  <si>
+    <t>DPP009</t>
+  </si>
+  <si>
+    <t>pino</t>
+  </si>
+  <si>
+    <t>DPP007.png</t>
+  </si>
+  <si>
+    <t>DPP008.png</t>
+  </si>
+  <si>
+    <t>DPP009.png</t>
+  </si>
+  <si>
+    <t>DPP010</t>
+  </si>
+  <si>
+    <t>DPP011</t>
+  </si>
+  <si>
+    <t>DPP012</t>
+  </si>
+  <si>
+    <t>DPP010.png</t>
+  </si>
+  <si>
+    <t>DPP011.png</t>
+  </si>
+  <si>
+    <t>DPP012.png</t>
+  </si>
+  <si>
+    <t>CBS001</t>
+  </si>
+  <si>
+    <t>Cabos de madera</t>
+  </si>
+  <si>
+    <t>Cabo de madera de 1,2 Metros</t>
+  </si>
+  <si>
+    <t>CBS002</t>
+  </si>
+  <si>
+    <t>CBS003</t>
+  </si>
+  <si>
+    <t>Cabo de madera de 1,5 Metros</t>
+  </si>
+  <si>
+    <t>Cabo de madera de 2 Metros</t>
+  </si>
+  <si>
+    <t>1,5 Metros</t>
+  </si>
+  <si>
+    <t>1,2 Metros</t>
+  </si>
+  <si>
+    <t>2 Metros</t>
+  </si>
+  <si>
+    <t>CBS001.jpg</t>
+  </si>
+  <si>
+    <t>CBS002.jpg</t>
+  </si>
+  <si>
+    <t>CBS003.jpg</t>
+  </si>
+  <si>
+    <t>CBS004</t>
+  </si>
+  <si>
+    <t>Cabos de metal</t>
+  </si>
+  <si>
+    <t>CBS004.jpg</t>
+  </si>
+  <si>
+    <t>Cabo de metal make</t>
+  </si>
+  <si>
+    <t>CBS005</t>
+  </si>
+  <si>
+    <t>Cabo Saca Hojas</t>
+  </si>
+  <si>
+    <t>CBS005.jpg</t>
+  </si>
+  <si>
+    <t>CBS006</t>
+  </si>
+  <si>
+    <t>Cabo extensible 2 metros</t>
+  </si>
+  <si>
+    <t>CBS006.jpg</t>
+  </si>
+  <si>
+    <t>CBS007</t>
+  </si>
+  <si>
+    <t>Cabo extensible 3 metros</t>
+  </si>
+  <si>
+    <t>CBS007.jpg</t>
+  </si>
+  <si>
+    <t>ESP001</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Esponja de acero 10 Gr </t>
+  </si>
+  <si>
+    <t>Make</t>
+  </si>
+  <si>
+    <t>ESP001.jpg</t>
+  </si>
+  <si>
+    <t>ESP002</t>
+  </si>
+  <si>
+    <t>ESP003</t>
+  </si>
+  <si>
+    <t>Esponja dorada de 30 Gr</t>
+  </si>
+  <si>
+    <t>Esponja azul para teflon</t>
+  </si>
+  <si>
+    <t>ESP002.jpg</t>
+  </si>
+  <si>
+    <t>ESP003.jpg</t>
+  </si>
+  <si>
+    <t>ESP004</t>
+  </si>
+  <si>
+    <t>Esponja de acero 10 Gr pack de 12 unidades</t>
+  </si>
+  <si>
+    <t>ESP004.jpg</t>
+  </si>
+  <si>
+    <t>ESP005</t>
+  </si>
+  <si>
+    <t>Esponja dorada 30 Gr pack de 12 unidades</t>
+  </si>
+  <si>
+    <t>ESP005.jpg</t>
+  </si>
+  <si>
+    <t>Lana de acero Make</t>
+  </si>
+  <si>
+    <t>ESP006.jpg</t>
+  </si>
+  <si>
+    <t>ESP006</t>
+  </si>
+  <si>
+    <t>ESP007</t>
+  </si>
+  <si>
+    <t>Lana de acero virulana</t>
+  </si>
+  <si>
+    <t>ESP007.jpg</t>
+  </si>
+  <si>
+    <t>APR001</t>
+  </si>
+  <si>
+    <t>APR002</t>
+  </si>
+  <si>
+    <t>APR004</t>
+  </si>
+  <si>
+    <t>APR005</t>
+  </si>
+  <si>
+    <t>APR003</t>
+  </si>
+  <si>
+    <t>Articulos Para Ropa</t>
+  </si>
+  <si>
+    <t>APR001.jpg</t>
+  </si>
+  <si>
+    <t>APR002.jpg</t>
+  </si>
+  <si>
+    <t>APR003.jpg</t>
+  </si>
+  <si>
+    <t>Tender Vertical para Ropa 3 niveles</t>
+  </si>
+  <si>
+    <t>Tender Para Medias de 18 Broches</t>
+  </si>
+  <si>
+    <t>Tender 10 varillas con Alas</t>
+  </si>
+  <si>
+    <t>Tender</t>
+  </si>
+  <si>
+    <t>Broches</t>
+  </si>
+  <si>
+    <t>Broches Plasticos x 12 unidades</t>
+  </si>
+  <si>
+    <t>Broches Madera x 12 unidades</t>
+  </si>
+  <si>
+    <t>APR004.jpg</t>
+  </si>
+  <si>
+    <t>APR005.jpg</t>
+  </si>
+  <si>
+    <t>APB001</t>
+  </si>
+  <si>
+    <t>Accesorios para baño</t>
+  </si>
+  <si>
+    <t>APB002</t>
+  </si>
+  <si>
+    <t>APB003</t>
+  </si>
+  <si>
+    <t>APB004</t>
+  </si>
+  <si>
+    <t>APB005</t>
+  </si>
+  <si>
+    <t>Cepillo Lava Espalda Plastico</t>
+  </si>
+  <si>
+    <t>Jabonera Deseplast</t>
+  </si>
+  <si>
+    <t>Pato</t>
+  </si>
+  <si>
+    <t>Pastilla para inodoro</t>
+  </si>
+  <si>
+    <t>Glade</t>
+  </si>
+  <si>
+    <t>Protector cortina de baño</t>
+  </si>
+  <si>
+    <t>APB001.jpg</t>
+  </si>
+  <si>
+    <t>APB002.jpg</t>
+  </si>
+  <si>
+    <t>Limpiador Adhesivo inodoro</t>
+  </si>
+  <si>
+    <t>APB003.jpg</t>
+  </si>
+  <si>
+    <t>APB004.jpg</t>
+  </si>
+  <si>
+    <t>APB005.jpg</t>
+  </si>
+  <si>
+    <t>AER001</t>
+  </si>
+  <si>
+    <t>AER002</t>
+  </si>
+  <si>
+    <t>AER008</t>
+  </si>
+  <si>
+    <t>AER003</t>
+  </si>
+  <si>
+    <t>AER004</t>
+  </si>
+  <si>
+    <t>AER005</t>
+  </si>
+  <si>
+    <t>AER006</t>
+  </si>
+  <si>
+    <t>AER007</t>
+  </si>
+  <si>
+    <t>Ambiente</t>
+  </si>
+  <si>
+    <t>Poe</t>
+  </si>
+  <si>
+    <t>Poett Desodorante de Ambiente</t>
+  </si>
+  <si>
+    <t>AER001.jpg</t>
+  </si>
+  <si>
+    <t>AER002.jpg</t>
+  </si>
+  <si>
+    <t>AER003.jpg</t>
+  </si>
+  <si>
+    <t>AER004.jpg</t>
+  </si>
+  <si>
+    <t>AER005.jpg</t>
+  </si>
+  <si>
+    <t>AER006.jpg</t>
+  </si>
+  <si>
+    <t>AER007.jpg</t>
+  </si>
+  <si>
+    <t>AER008.jpg</t>
+  </si>
+  <si>
+    <t>Desinfectante</t>
+  </si>
+  <si>
+    <t>Lysoform</t>
+  </si>
+  <si>
+    <t>Lysoform Desisfectante</t>
+  </si>
+  <si>
+    <t>Muebles</t>
+  </si>
+  <si>
+    <t>Blem</t>
+  </si>
+  <si>
+    <t>Lustra Muebles</t>
+  </si>
+  <si>
+    <t>Limpia Horno</t>
+  </si>
+  <si>
+    <t>Mr. Musculo</t>
+  </si>
+  <si>
+    <t>Limpiador para hornos</t>
+  </si>
+  <si>
+    <t>Para Ropa</t>
+  </si>
+  <si>
+    <t>Apresto Danubio</t>
+  </si>
+  <si>
+    <t>Insecticida</t>
+  </si>
+  <si>
+    <t>Fuyi</t>
+  </si>
+  <si>
+    <t>Fuyi Mata Moscas y Mosquitos</t>
+  </si>
+  <si>
+    <t>Raid</t>
+  </si>
+  <si>
+    <t>Raid Azul</t>
+  </si>
+  <si>
+    <t>Raid Negro</t>
+  </si>
+  <si>
+    <t>MYG001</t>
+  </si>
+  <si>
+    <t>MYG002</t>
+  </si>
+  <si>
+    <t>MYG003</t>
+  </si>
+  <si>
+    <t>MYG004</t>
+  </si>
+  <si>
+    <t>Mopas y Guantes</t>
+  </si>
+  <si>
+    <t>Guantes</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Guantes de Goma Make </t>
+  </si>
+  <si>
+    <t>Talle S</t>
+  </si>
+  <si>
+    <t>Talle M</t>
+  </si>
+  <si>
+    <t>Talle L</t>
+  </si>
+  <si>
+    <t>Talle XL</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Guantes de Latex descartable Caja x 100 unidades </t>
+  </si>
+  <si>
+    <t>MYG005</t>
+  </si>
+  <si>
+    <t>MYG006</t>
+  </si>
+  <si>
+    <t>MYG001.jpg</t>
+  </si>
+  <si>
+    <t>MYG005.jpg</t>
+  </si>
+  <si>
+    <t>MYG006.jpg</t>
+  </si>
+  <si>
+    <t>MYG002.jpg</t>
+  </si>
+  <si>
+    <t>MYG003.jpg</t>
+  </si>
+  <si>
+    <t>MYG004.jpg</t>
+  </si>
+  <si>
+    <t>Guantes de Nitrilo Caja x 100 unidades</t>
+  </si>
+  <si>
+    <t>MYG007</t>
+  </si>
+  <si>
+    <t>Iberia</t>
+  </si>
+  <si>
+    <t>Escurre Facil Iberia</t>
+  </si>
+  <si>
+    <t>MYG007.jpg</t>
+  </si>
+  <si>
+    <t>MYG008</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Mopa Algodon Amarillo MrTrapo </t>
+  </si>
+  <si>
+    <t>MrTrapo</t>
+  </si>
+  <si>
+    <t>MYG008.jpg</t>
+  </si>
+  <si>
+    <t>MYG009</t>
+  </si>
+  <si>
+    <t>Romyl</t>
+  </si>
+  <si>
+    <t>Mopa Amarilla Romyl</t>
+  </si>
+  <si>
+    <t>MYG009.jpg</t>
+  </si>
+  <si>
+    <t>Mopa Blanca Algodon FibranSur</t>
+  </si>
+  <si>
+    <t>Fibran Sur</t>
+  </si>
+  <si>
+    <t>MYG010</t>
+  </si>
+  <si>
+    <t>MYG010.jpg</t>
+  </si>
+  <si>
+    <t>MYG011</t>
+  </si>
+  <si>
+    <t>Mopa Blanca Algodon Make</t>
+  </si>
+  <si>
+    <t>MYG011.jpg</t>
+  </si>
+  <si>
+    <t>Repuesto Mopa Pelo Corto Turbo Facil</t>
+  </si>
+  <si>
+    <t>MYG012.jpg</t>
+  </si>
+  <si>
+    <t>Repuestos</t>
+  </si>
+  <si>
+    <t>Turbo Facil</t>
+  </si>
+  <si>
+    <t>MYG012</t>
+  </si>
+  <si>
+    <t>Repuesto Mopa Pelo Largo Turbo Matic</t>
+  </si>
+  <si>
+    <t>MYG013.jpg</t>
+  </si>
+  <si>
+    <t>Turbo Matic</t>
+  </si>
+  <si>
+    <t>MYG013</t>
+  </si>
+  <si>
+    <t>RPP001</t>
+  </si>
+  <si>
+    <t>RPP002</t>
+  </si>
+  <si>
+    <t>RPP003</t>
+  </si>
+  <si>
+    <t>RPP004</t>
+  </si>
+  <si>
+    <t>RPP005</t>
+  </si>
+  <si>
+    <t>RPP006</t>
+  </si>
+  <si>
+    <t>Recipientes Plasticos</t>
+  </si>
+  <si>
+    <t>Baldes</t>
+  </si>
+  <si>
+    <t>Balde Mopa 9 lts Matriplaster</t>
+  </si>
+  <si>
+    <t>RPP001.jpg</t>
+  </si>
+  <si>
+    <t>RPP002.jpg</t>
+  </si>
+  <si>
+    <t>Balde Mopa 14 lts Matriplaster</t>
+  </si>
+  <si>
+    <t>Matriplaster</t>
+  </si>
+  <si>
+    <t>Balde x 10 lts</t>
+  </si>
+  <si>
+    <t>RPP003.jpg</t>
+  </si>
+  <si>
+    <t>RPP004.jpg</t>
+  </si>
+  <si>
+    <t>Balde x 12 lts</t>
+  </si>
+  <si>
+    <t>Balde Mopa Duo Matriplaster</t>
+  </si>
+  <si>
+    <t>RPP005.jpg</t>
+  </si>
+  <si>
+    <t>Balde Mopa Plana</t>
+  </si>
+  <si>
+    <t>RPP006.jpg</t>
+  </si>
+  <si>
+    <t>PPP001</t>
+  </si>
+  <si>
+    <t>Productos para Piletas</t>
+  </si>
+  <si>
+    <t>Liquidos</t>
+  </si>
+  <si>
+    <t>Alguicida Clorotec 1 litro</t>
+  </si>
+  <si>
+    <t>PPP001.jpg</t>
+  </si>
+  <si>
+    <t>Clorotec</t>
+  </si>
+  <si>
+    <t>Clarificante Clorotec  1 litro</t>
+  </si>
+  <si>
+    <t>PPP002.jpg</t>
+  </si>
+  <si>
+    <t>PPP003</t>
+  </si>
+  <si>
+    <t>PPP002</t>
+  </si>
+  <si>
+    <t>Regulador PH 5 litros</t>
+  </si>
+  <si>
+    <t>PPP003.jpg</t>
+  </si>
+  <si>
+    <t>PPP004</t>
+  </si>
+  <si>
+    <t>PPP005</t>
+  </si>
+  <si>
+    <t>Quimicos</t>
+  </si>
+  <si>
+    <t>Cloro Granulado Lento x 50 kg</t>
+  </si>
+  <si>
+    <t>50 kilos</t>
+  </si>
+  <si>
+    <t>PPP004.jpg</t>
+  </si>
+  <si>
+    <t>PPP005.jpg</t>
+  </si>
+  <si>
+    <t>Cloro Granulado Lento 1 kg</t>
+  </si>
+  <si>
+    <t>1 kilo</t>
+  </si>
+  <si>
+    <t>PPP006</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Reactivos x 2 </t>
+  </si>
+  <si>
+    <t>PPP006.jpg</t>
+  </si>
+  <si>
+    <t>Pastillas de Cloro triple Accion de 200 gr pack x 5 pastillas</t>
+  </si>
+  <si>
+    <t>PPP007</t>
+  </si>
+  <si>
+    <t>PPP007.jpg</t>
+  </si>
+  <si>
+    <t>PPP008</t>
+  </si>
+  <si>
+    <t>Test kit</t>
+  </si>
+  <si>
+    <t>PPP008.jpg</t>
+  </si>
+  <si>
+    <t>PPP009</t>
+  </si>
+  <si>
+    <t>Mangueras</t>
+  </si>
+  <si>
+    <t>Manguera 1'' x 15 mts</t>
+  </si>
+  <si>
+    <t>PPP009.jpg</t>
+  </si>
+  <si>
+    <t>PPP010</t>
+  </si>
+  <si>
+    <t>Manguera 3/4" x 15 mts</t>
+  </si>
+  <si>
+    <t>PPP010.jpg</t>
+  </si>
+  <si>
+    <t>PPP011</t>
+  </si>
+  <si>
+    <t>Manguera 1/2" x 15 mts</t>
+  </si>
+  <si>
+    <t>PPP011.jpg</t>
+  </si>
+  <si>
+    <t>PPP012</t>
+  </si>
+  <si>
+    <t>Manguera Corrugada 1 1/2" x 10 mts</t>
+  </si>
+  <si>
+    <t>PPP012.jpg</t>
+  </si>
+  <si>
+    <t>PPP013</t>
+  </si>
+  <si>
+    <t>PPP013.jpg</t>
+  </si>
+  <si>
+    <t>Flota Flota</t>
+  </si>
+  <si>
+    <t>Barrefondo 8 Ruedas</t>
+  </si>
+  <si>
+    <t>PPP014.jpg</t>
+  </si>
+  <si>
+    <t>PPP014</t>
+  </si>
+  <si>
+    <t>PPP015</t>
+  </si>
+  <si>
+    <t>Barrefondo Medialuna</t>
+  </si>
+  <si>
+    <t>PPP015.jpg</t>
+  </si>
+  <si>
+    <t>PPP016</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Boya Hongo </t>
+  </si>
+  <si>
+    <t>PPP016.jpg</t>
+  </si>
+  <si>
+    <t>PPP017</t>
+  </si>
+  <si>
+    <t>Boya Satelite</t>
+  </si>
+  <si>
+    <t>PPP017.jpg</t>
+  </si>
+  <si>
+    <t>VAR001</t>
+  </si>
+  <si>
+    <t>VAR002</t>
+  </si>
+  <si>
+    <t>VAR003</t>
+  </si>
+  <si>
+    <t>VAR004</t>
+  </si>
+  <si>
+    <t>VAR005</t>
+  </si>
+  <si>
+    <t>VAR006</t>
+  </si>
+  <si>
+    <t>VAR007</t>
+  </si>
+  <si>
+    <t>VAR008</t>
+  </si>
+  <si>
+    <t>VAR009</t>
+  </si>
+  <si>
+    <t>Velas</t>
+  </si>
+  <si>
+    <t>VAR001.jpg</t>
+  </si>
+  <si>
+    <t>VAR002.jpg</t>
+  </si>
+  <si>
+    <t>VAR003.jpg</t>
+  </si>
+  <si>
+    <t>VAR004.jpg</t>
+  </si>
+  <si>
+    <t>VAR005.jpg</t>
+  </si>
+  <si>
+    <t>VAR006.jpg</t>
+  </si>
+  <si>
+    <t>VAR007.jpg</t>
+  </si>
+  <si>
+    <t>VAR008.jpg</t>
+  </si>
+  <si>
+    <t>VAR009.jpg</t>
+  </si>
+  <si>
+    <t>Velas x 12 de 205 mm make</t>
+  </si>
+  <si>
+    <t>Velas x 4 de 205 mm make</t>
+  </si>
+  <si>
+    <t>Papel</t>
+  </si>
+  <si>
+    <t>Papel Manteca Make</t>
+  </si>
+  <si>
+    <t>Papel Aluminio Make</t>
+  </si>
+  <si>
+    <t>Film Adherente Make  30 metros</t>
+  </si>
+  <si>
+    <t>Bolsa</t>
+  </si>
+  <si>
+    <t>Separador de Freezer Make x 200 unidades</t>
+  </si>
+  <si>
+    <t>Bolsa para cubitos Bolzip</t>
+  </si>
+  <si>
+    <t>Bolzip</t>
+  </si>
+  <si>
+    <t>Palmeta Mata Moscas Plastica</t>
+  </si>
+  <si>
+    <t>insecticida liquido Gorrion x 500 cc</t>
+  </si>
+  <si>
+    <t>Gorrion</t>
   </si>
 </sst>
 </file>
@@ -12237,309 +13170,753 @@
       <c r="A146" t="s">
         <v>160</v>
       </c>
+      <c r="B146" t="s">
+        <v>1575</v>
+      </c>
+      <c r="C146" t="s">
+        <v>1576</v>
+      </c>
+      <c r="D146" t="s">
+        <v>1576</v>
+      </c>
+      <c r="E146" t="s">
+        <v>1074</v>
+      </c>
       <c r="F146" t="s">
-        <v>1132</v>
+        <v>1583</v>
+      </c>
+      <c r="G146">
+        <v>1056</v>
+      </c>
+      <c r="H146" t="s">
+        <v>1076</v>
+      </c>
+      <c r="I146" t="s">
+        <v>1577</v>
+      </c>
+      <c r="J146">
+        <v>2750</v>
       </c>
       <c r="K146">
-        <v>1</v>
-      </c>
-      <c r="L146" t="str">
+        <v>0.3</v>
+      </c>
+      <c r="L146">
         <f t="shared" si="2"/>
-        <v/>
+        <v>3575</v>
       </c>
       <c r="M146" t="s">
         <v>16</v>
       </c>
       <c r="O146" t="s">
         <v>16</v>
+      </c>
+      <c r="P146" t="s">
+        <v>1359</v>
+      </c>
+      <c r="Q146" t="s">
+        <v>1575</v>
       </c>
     </row>
     <row r="147" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A147" t="s">
         <v>161</v>
       </c>
+      <c r="B147" t="s">
+        <v>1578</v>
+      </c>
+      <c r="C147" t="s">
+        <v>1576</v>
+      </c>
+      <c r="D147" t="s">
+        <v>1576</v>
+      </c>
+      <c r="E147" t="s">
+        <v>1074</v>
+      </c>
       <c r="F147" t="s">
-        <v>1132</v>
+        <v>1582</v>
+      </c>
+      <c r="G147">
+        <v>1056</v>
+      </c>
+      <c r="H147" t="s">
+        <v>1540</v>
+      </c>
+      <c r="I147" t="s">
+        <v>1579</v>
+      </c>
+      <c r="J147">
+        <v>1350</v>
       </c>
       <c r="K147">
-        <v>1</v>
-      </c>
-      <c r="L147" t="str">
+        <v>0.3</v>
+      </c>
+      <c r="L147">
         <f t="shared" si="2"/>
-        <v/>
+        <v>1755</v>
       </c>
       <c r="M147" t="s">
         <v>16</v>
       </c>
       <c r="O147" t="s">
         <v>16</v>
+      </c>
+      <c r="P147" t="s">
+        <v>1359</v>
+      </c>
+      <c r="Q147" t="s">
+        <v>1578</v>
       </c>
     </row>
     <row r="148" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A148" t="s">
         <v>162</v>
       </c>
+      <c r="B148" t="s">
+        <v>1584</v>
+      </c>
+      <c r="C148" t="s">
+        <v>1576</v>
+      </c>
+      <c r="D148" t="s">
+        <v>1576</v>
+      </c>
+      <c r="E148" t="s">
+        <v>1074</v>
+      </c>
       <c r="F148" t="s">
-        <v>1132</v>
+        <v>1581</v>
+      </c>
+      <c r="G148">
+        <v>1056</v>
+      </c>
+      <c r="H148" t="s">
+        <v>1589</v>
+      </c>
+      <c r="I148" t="s">
+        <v>1580</v>
+      </c>
+      <c r="J148">
+        <v>7100</v>
       </c>
       <c r="K148">
-        <v>1</v>
-      </c>
-      <c r="L148" t="str">
+        <v>0.3</v>
+      </c>
+      <c r="L148">
         <f t="shared" si="2"/>
-        <v/>
+        <v>9230</v>
       </c>
       <c r="M148" t="s">
         <v>16</v>
       </c>
       <c r="O148" t="s">
         <v>16</v>
+      </c>
+      <c r="P148" t="s">
+        <v>1359</v>
+      </c>
+      <c r="Q148" t="s">
+        <v>1584</v>
       </c>
     </row>
     <row r="149" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A149" t="s">
         <v>163</v>
       </c>
+      <c r="B149" t="s">
+        <v>1585</v>
+      </c>
+      <c r="C149" t="s">
+        <v>1576</v>
+      </c>
+      <c r="D149" t="s">
+        <v>1576</v>
+      </c>
+      <c r="E149" t="s">
+        <v>1074</v>
+      </c>
       <c r="F149" t="s">
-        <v>1132</v>
+        <v>1583</v>
+      </c>
+      <c r="G149" t="s">
+        <v>1588</v>
+      </c>
+      <c r="H149" t="s">
+        <v>1076</v>
+      </c>
+      <c r="I149" t="s">
+        <v>1590</v>
+      </c>
+      <c r="J149">
+        <v>2750</v>
       </c>
       <c r="K149">
-        <v>1</v>
-      </c>
-      <c r="L149" t="str">
+        <v>0.3</v>
+      </c>
+      <c r="L149">
         <f t="shared" si="2"/>
-        <v/>
+        <v>3575</v>
       </c>
       <c r="M149" t="s">
         <v>16</v>
       </c>
       <c r="O149" t="s">
         <v>16</v>
+      </c>
+      <c r="P149" t="s">
+        <v>1359</v>
+      </c>
+      <c r="Q149" t="s">
+        <v>1585</v>
       </c>
     </row>
     <row r="150" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A150" t="s">
         <v>164</v>
       </c>
+      <c r="B150" t="s">
+        <v>1586</v>
+      </c>
+      <c r="C150" t="s">
+        <v>1576</v>
+      </c>
+      <c r="D150" t="s">
+        <v>1576</v>
+      </c>
+      <c r="E150" t="s">
+        <v>1074</v>
+      </c>
       <c r="F150" t="s">
-        <v>1132</v>
+        <v>1582</v>
+      </c>
+      <c r="G150" t="s">
+        <v>1588</v>
+      </c>
+      <c r="H150" t="s">
+        <v>1540</v>
+      </c>
+      <c r="I150" t="s">
+        <v>1591</v>
+      </c>
+      <c r="J150">
+        <v>1350</v>
       </c>
       <c r="K150">
-        <v>1</v>
-      </c>
-      <c r="L150" t="str">
+        <v>0.3</v>
+      </c>
+      <c r="L150">
         <f t="shared" si="2"/>
-        <v/>
+        <v>1755</v>
       </c>
       <c r="M150" t="s">
         <v>16</v>
       </c>
       <c r="O150" t="s">
         <v>16</v>
+      </c>
+      <c r="P150" t="s">
+        <v>1359</v>
+      </c>
+      <c r="Q150" t="s">
+        <v>1586</v>
       </c>
     </row>
     <row r="151" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A151" t="s">
         <v>165</v>
       </c>
+      <c r="B151" t="s">
+        <v>1587</v>
+      </c>
+      <c r="C151" t="s">
+        <v>1576</v>
+      </c>
+      <c r="D151" t="s">
+        <v>1576</v>
+      </c>
+      <c r="E151" t="s">
+        <v>1074</v>
+      </c>
       <c r="F151" t="s">
-        <v>1132</v>
+        <v>1581</v>
+      </c>
+      <c r="G151" t="s">
+        <v>1588</v>
+      </c>
+      <c r="H151" t="s">
+        <v>1589</v>
+      </c>
+      <c r="I151" t="s">
+        <v>1592</v>
+      </c>
+      <c r="J151">
+        <v>7100</v>
       </c>
       <c r="K151">
-        <v>1</v>
-      </c>
-      <c r="L151" t="str">
+        <v>0.3</v>
+      </c>
+      <c r="L151">
         <f t="shared" si="2"/>
-        <v/>
+        <v>9230</v>
       </c>
       <c r="M151" t="s">
         <v>16</v>
       </c>
       <c r="O151" t="s">
         <v>16</v>
+      </c>
+      <c r="P151" t="s">
+        <v>1359</v>
+      </c>
+      <c r="Q151" t="s">
+        <v>1587</v>
       </c>
     </row>
     <row r="152" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A152" t="s">
         <v>166</v>
       </c>
+      <c r="B152" t="s">
+        <v>1593</v>
+      </c>
+      <c r="C152" t="s">
+        <v>1576</v>
+      </c>
+      <c r="D152" t="s">
+        <v>1576</v>
+      </c>
+      <c r="E152" t="s">
+        <v>1074</v>
+      </c>
       <c r="F152" t="s">
-        <v>1132</v>
+        <v>1583</v>
+      </c>
+      <c r="G152" t="s">
+        <v>1596</v>
+      </c>
+      <c r="H152" t="s">
+        <v>1076</v>
+      </c>
+      <c r="I152" t="s">
+        <v>1597</v>
+      </c>
+      <c r="J152">
+        <v>2750</v>
       </c>
       <c r="K152">
-        <v>1</v>
-      </c>
-      <c r="L152" t="str">
+        <v>0.3</v>
+      </c>
+      <c r="L152">
         <f t="shared" si="2"/>
-        <v/>
+        <v>3575</v>
       </c>
       <c r="M152" t="s">
         <v>16</v>
       </c>
       <c r="O152" t="s">
         <v>16</v>
+      </c>
+      <c r="P152" t="s">
+        <v>1359</v>
+      </c>
+      <c r="Q152" t="s">
+        <v>1593</v>
       </c>
     </row>
     <row r="153" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A153" t="s">
         <v>167</v>
       </c>
+      <c r="B153" t="s">
+        <v>1594</v>
+      </c>
+      <c r="C153" t="s">
+        <v>1576</v>
+      </c>
+      <c r="D153" t="s">
+        <v>1576</v>
+      </c>
+      <c r="E153" t="s">
+        <v>1074</v>
+      </c>
       <c r="F153" t="s">
-        <v>1132</v>
+        <v>1582</v>
+      </c>
+      <c r="G153" t="s">
+        <v>1596</v>
+      </c>
+      <c r="H153" t="s">
+        <v>1540</v>
+      </c>
+      <c r="I153" t="s">
+        <v>1598</v>
+      </c>
+      <c r="J153">
+        <v>1350</v>
       </c>
       <c r="K153">
-        <v>1</v>
-      </c>
-      <c r="L153" t="str">
+        <v>0.3</v>
+      </c>
+      <c r="L153">
         <f t="shared" si="2"/>
-        <v/>
+        <v>1755</v>
       </c>
       <c r="M153" t="s">
         <v>16</v>
       </c>
       <c r="O153" t="s">
         <v>16</v>
+      </c>
+      <c r="P153" t="s">
+        <v>1359</v>
+      </c>
+      <c r="Q153" t="s">
+        <v>1594</v>
       </c>
     </row>
     <row r="154" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A154" t="s">
         <v>168</v>
       </c>
+      <c r="B154" t="s">
+        <v>1595</v>
+      </c>
+      <c r="C154" t="s">
+        <v>1576</v>
+      </c>
+      <c r="D154" t="s">
+        <v>1576</v>
+      </c>
+      <c r="E154" t="s">
+        <v>1074</v>
+      </c>
       <c r="F154" t="s">
-        <v>1132</v>
+        <v>1581</v>
+      </c>
+      <c r="G154" t="s">
+        <v>1596</v>
+      </c>
+      <c r="H154" t="s">
+        <v>1589</v>
+      </c>
+      <c r="I154" t="s">
+        <v>1599</v>
+      </c>
+      <c r="J154">
+        <v>7100</v>
       </c>
       <c r="K154">
-        <v>1</v>
-      </c>
-      <c r="L154" t="str">
+        <v>0.3</v>
+      </c>
+      <c r="L154">
         <f t="shared" si="2"/>
-        <v/>
+        <v>9230</v>
       </c>
       <c r="M154" t="s">
         <v>16</v>
       </c>
       <c r="O154" t="s">
         <v>16</v>
+      </c>
+      <c r="P154" t="s">
+        <v>1359</v>
+      </c>
+      <c r="Q154" t="s">
+        <v>1595</v>
       </c>
     </row>
     <row r="155" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A155" t="s">
         <v>169</v>
       </c>
+      <c r="B155" t="s">
+        <v>1600</v>
+      </c>
+      <c r="C155" t="s">
+        <v>1576</v>
+      </c>
+      <c r="D155" t="s">
+        <v>1576</v>
+      </c>
+      <c r="E155" t="s">
+        <v>1074</v>
+      </c>
       <c r="F155" t="s">
-        <v>1132</v>
+        <v>1583</v>
+      </c>
+      <c r="G155" t="s">
+        <v>1458</v>
+      </c>
+      <c r="H155" t="s">
+        <v>1076</v>
+      </c>
+      <c r="I155" t="s">
+        <v>1603</v>
+      </c>
+      <c r="J155">
+        <v>2750</v>
       </c>
       <c r="K155">
-        <v>1</v>
-      </c>
-      <c r="L155" t="str">
+        <v>0.3</v>
+      </c>
+      <c r="L155">
         <f t="shared" si="2"/>
-        <v/>
+        <v>3575</v>
       </c>
       <c r="M155" t="s">
         <v>16</v>
       </c>
       <c r="O155" t="s">
         <v>16</v>
+      </c>
+      <c r="P155" t="s">
+        <v>1359</v>
+      </c>
+      <c r="Q155" t="s">
+        <v>1600</v>
       </c>
     </row>
     <row r="156" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A156" t="s">
         <v>170</v>
       </c>
+      <c r="B156" t="s">
+        <v>1601</v>
+      </c>
+      <c r="C156" t="s">
+        <v>1576</v>
+      </c>
+      <c r="D156" t="s">
+        <v>1576</v>
+      </c>
+      <c r="E156" t="s">
+        <v>1074</v>
+      </c>
       <c r="F156" t="s">
-        <v>1132</v>
+        <v>1582</v>
+      </c>
+      <c r="G156" t="s">
+        <v>1458</v>
+      </c>
+      <c r="H156" t="s">
+        <v>1540</v>
+      </c>
+      <c r="I156" t="s">
+        <v>1604</v>
+      </c>
+      <c r="J156">
+        <v>1350</v>
       </c>
       <c r="K156">
-        <v>1</v>
-      </c>
-      <c r="L156" t="str">
+        <v>0.3</v>
+      </c>
+      <c r="L156">
         <f t="shared" si="2"/>
-        <v/>
+        <v>1755</v>
       </c>
       <c r="M156" t="s">
         <v>16</v>
       </c>
       <c r="O156" t="s">
         <v>16</v>
+      </c>
+      <c r="P156" t="s">
+        <v>1359</v>
+      </c>
+      <c r="Q156" t="s">
+        <v>1601</v>
       </c>
     </row>
     <row r="157" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A157" t="s">
         <v>171</v>
       </c>
+      <c r="B157" t="s">
+        <v>1602</v>
+      </c>
+      <c r="C157" t="s">
+        <v>1576</v>
+      </c>
+      <c r="D157" t="s">
+        <v>1576</v>
+      </c>
+      <c r="E157" t="s">
+        <v>1074</v>
+      </c>
       <c r="F157" t="s">
-        <v>1132</v>
+        <v>1581</v>
+      </c>
+      <c r="G157" t="s">
+        <v>1458</v>
+      </c>
+      <c r="H157" t="s">
+        <v>1589</v>
+      </c>
+      <c r="I157" t="s">
+        <v>1605</v>
+      </c>
+      <c r="J157">
+        <v>7100</v>
       </c>
       <c r="K157">
-        <v>1</v>
-      </c>
-      <c r="L157" t="str">
+        <v>0.3</v>
+      </c>
+      <c r="L157">
         <f t="shared" si="2"/>
-        <v/>
+        <v>9230</v>
       </c>
       <c r="M157" t="s">
         <v>16</v>
       </c>
       <c r="O157" t="s">
         <v>16</v>
+      </c>
+      <c r="P157" t="s">
+        <v>1359</v>
+      </c>
+      <c r="Q157" t="s">
+        <v>1602</v>
       </c>
     </row>
     <row r="158" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A158" t="s">
         <v>172</v>
       </c>
+      <c r="B158" t="s">
+        <v>1606</v>
+      </c>
+      <c r="C158" t="s">
+        <v>1042</v>
+      </c>
+      <c r="D158" t="s">
+        <v>1607</v>
+      </c>
+      <c r="E158" t="s">
+        <v>1074</v>
+      </c>
       <c r="F158" t="s">
-        <v>1132</v>
+        <v>1608</v>
+      </c>
+      <c r="G158" t="s">
+        <v>1614</v>
+      </c>
+      <c r="H158" t="s">
+        <v>1164</v>
+      </c>
+      <c r="I158" t="s">
+        <v>1616</v>
+      </c>
+      <c r="J158">
+        <v>1000</v>
       </c>
       <c r="K158">
-        <v>1</v>
-      </c>
-      <c r="L158" t="str">
+        <v>0.3</v>
+      </c>
+      <c r="L158">
         <f t="shared" si="2"/>
-        <v/>
+        <v>1300</v>
       </c>
       <c r="M158" t="s">
         <v>16</v>
       </c>
       <c r="O158" t="s">
         <v>16</v>
+      </c>
+      <c r="P158" t="s">
+        <v>1359</v>
+      </c>
+      <c r="Q158" t="s">
+        <v>1606</v>
       </c>
     </row>
     <row r="159" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A159" t="s">
         <v>173</v>
       </c>
+      <c r="B159" t="s">
+        <v>1609</v>
+      </c>
+      <c r="C159" t="s">
+        <v>1042</v>
+      </c>
+      <c r="D159" t="s">
+        <v>1607</v>
+      </c>
+      <c r="E159" t="s">
+        <v>1074</v>
+      </c>
       <c r="F159" t="s">
-        <v>1132</v>
+        <v>1611</v>
+      </c>
+      <c r="G159" t="s">
+        <v>1613</v>
+      </c>
+      <c r="H159" t="s">
+        <v>1164</v>
+      </c>
+      <c r="I159" t="s">
+        <v>1617</v>
+      </c>
+      <c r="J159">
+        <v>1200</v>
       </c>
       <c r="K159">
-        <v>1</v>
-      </c>
-      <c r="L159" t="str">
+        <v>0.3</v>
+      </c>
+      <c r="L159">
         <f t="shared" si="2"/>
-        <v/>
+        <v>1560</v>
       </c>
       <c r="M159" t="s">
         <v>16</v>
       </c>
       <c r="O159" t="s">
         <v>16</v>
+      </c>
+      <c r="P159" t="s">
+        <v>1359</v>
+      </c>
+      <c r="Q159" t="s">
+        <v>1609</v>
       </c>
     </row>
     <row r="160" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A160" t="s">
         <v>174</v>
       </c>
+      <c r="B160" t="s">
+        <v>1610</v>
+      </c>
+      <c r="C160" t="s">
+        <v>1042</v>
+      </c>
+      <c r="D160" t="s">
+        <v>1607</v>
+      </c>
+      <c r="E160" t="s">
+        <v>1074</v>
+      </c>
       <c r="F160" t="s">
-        <v>1132</v>
+        <v>1612</v>
+      </c>
+      <c r="G160" t="s">
+        <v>1615</v>
+      </c>
+      <c r="H160" t="s">
+        <v>1164</v>
+      </c>
+      <c r="I160" t="s">
+        <v>1618</v>
+      </c>
+      <c r="J160">
+        <v>1400</v>
       </c>
       <c r="K160">
-        <v>1</v>
-      </c>
-      <c r="L160" t="str">
+        <v>0.3</v>
+      </c>
+      <c r="L160">
         <f t="shared" si="2"/>
-        <v/>
+        <v>1820</v>
       </c>
       <c r="M160" t="s">
         <v>16</v>
@@ -12547,20 +13924,47 @@
       <c r="O160" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="161" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="P160" t="s">
+        <v>1359</v>
+      </c>
+      <c r="Q160" t="s">
+        <v>1610</v>
+      </c>
+    </row>
+    <row r="161" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A161" t="s">
         <v>175</v>
       </c>
+      <c r="B161" t="s">
+        <v>1619</v>
+      </c>
+      <c r="C161" t="s">
+        <v>1042</v>
+      </c>
+      <c r="D161" t="s">
+        <v>1620</v>
+      </c>
+      <c r="E161" t="s">
+        <v>1074</v>
+      </c>
       <c r="F161" t="s">
-        <v>1132</v>
+        <v>1622</v>
+      </c>
+      <c r="H161" t="s">
+        <v>1164</v>
+      </c>
+      <c r="I161" t="s">
+        <v>1621</v>
+      </c>
+      <c r="J161">
+        <v>2000</v>
       </c>
       <c r="K161">
-        <v>1</v>
-      </c>
-      <c r="L161" t="str">
+        <v>0.3</v>
+      </c>
+      <c r="L161">
         <f t="shared" si="2"/>
-        <v/>
+        <v>2600</v>
       </c>
       <c r="M161" t="s">
         <v>16</v>
@@ -12568,20 +13972,47 @@
       <c r="O161" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="162" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="P161" t="s">
+        <v>1359</v>
+      </c>
+      <c r="Q161" t="s">
+        <v>1619</v>
+      </c>
+    </row>
+    <row r="162" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A162" t="s">
         <v>176</v>
       </c>
+      <c r="B162" t="s">
+        <v>1623</v>
+      </c>
+      <c r="C162" t="s">
+        <v>1042</v>
+      </c>
+      <c r="D162" t="s">
+        <v>1620</v>
+      </c>
+      <c r="E162" t="s">
+        <v>1074</v>
+      </c>
       <c r="F162" t="s">
-        <v>1132</v>
+        <v>1624</v>
+      </c>
+      <c r="H162" t="s">
+        <v>1164</v>
+      </c>
+      <c r="I162" t="s">
+        <v>1625</v>
+      </c>
+      <c r="J162">
+        <v>4400</v>
       </c>
       <c r="K162">
-        <v>1</v>
-      </c>
-      <c r="L162" t="str">
+        <v>0.3</v>
+      </c>
+      <c r="L162">
         <f t="shared" si="2"/>
-        <v/>
+        <v>5720</v>
       </c>
       <c r="M162" t="s">
         <v>16</v>
@@ -12589,20 +14020,47 @@
       <c r="O162" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="163" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="P162" t="s">
+        <v>1359</v>
+      </c>
+      <c r="Q162" t="s">
+        <v>1623</v>
+      </c>
+    </row>
+    <row r="163" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A163" t="s">
         <v>177</v>
       </c>
+      <c r="B163" t="s">
+        <v>1626</v>
+      </c>
+      <c r="C163" t="s">
+        <v>1042</v>
+      </c>
+      <c r="D163" t="s">
+        <v>1620</v>
+      </c>
+      <c r="E163" t="s">
+        <v>1074</v>
+      </c>
       <c r="F163" t="s">
-        <v>1132</v>
+        <v>1627</v>
+      </c>
+      <c r="H163" t="s">
+        <v>1164</v>
+      </c>
+      <c r="I163" t="s">
+        <v>1628</v>
+      </c>
+      <c r="J163">
+        <v>7000</v>
       </c>
       <c r="K163">
-        <v>1</v>
-      </c>
-      <c r="L163" t="str">
+        <v>0.3</v>
+      </c>
+      <c r="L163">
         <f t="shared" si="2"/>
-        <v/>
+        <v>9100</v>
       </c>
       <c r="M163" t="s">
         <v>16</v>
@@ -12610,20 +14068,47 @@
       <c r="O163" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="164" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="P163" t="s">
+        <v>1359</v>
+      </c>
+      <c r="Q163" t="s">
+        <v>1626</v>
+      </c>
+    </row>
+    <row r="164" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A164" t="s">
         <v>178</v>
       </c>
+      <c r="B164" t="s">
+        <v>1629</v>
+      </c>
+      <c r="C164" t="s">
+        <v>1042</v>
+      </c>
+      <c r="D164" t="s">
+        <v>1620</v>
+      </c>
+      <c r="E164" t="s">
+        <v>1074</v>
+      </c>
       <c r="F164" t="s">
-        <v>1132</v>
+        <v>1630</v>
+      </c>
+      <c r="H164" t="s">
+        <v>1164</v>
+      </c>
+      <c r="I164" t="s">
+        <v>1631</v>
+      </c>
+      <c r="J164">
+        <v>8800</v>
       </c>
       <c r="K164">
-        <v>1</v>
-      </c>
-      <c r="L164" t="str">
+        <v>0.3</v>
+      </c>
+      <c r="L164">
         <f t="shared" si="2"/>
-        <v/>
+        <v>11440</v>
       </c>
       <c r="M164" t="s">
         <v>16</v>
@@ -12631,20 +14116,47 @@
       <c r="O164" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="165" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="P164" t="s">
+        <v>1359</v>
+      </c>
+      <c r="Q164" t="s">
+        <v>1629</v>
+      </c>
+    </row>
+    <row r="165" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A165" t="s">
         <v>179</v>
       </c>
+      <c r="B165" t="s">
+        <v>1632</v>
+      </c>
+      <c r="C165" t="s">
+        <v>1043</v>
+      </c>
+      <c r="D165" t="s">
+        <v>1043</v>
+      </c>
+      <c r="E165" t="s">
+        <v>1634</v>
+      </c>
       <c r="F165" t="s">
-        <v>1132</v>
+        <v>1633</v>
+      </c>
+      <c r="H165" t="s">
+        <v>1164</v>
+      </c>
+      <c r="I165" t="s">
+        <v>1635</v>
+      </c>
+      <c r="J165">
+        <v>300</v>
       </c>
       <c r="K165">
-        <v>1</v>
-      </c>
-      <c r="L165" t="str">
+        <v>0.3</v>
+      </c>
+      <c r="L165">
         <f t="shared" si="2"/>
-        <v/>
+        <v>390</v>
       </c>
       <c r="M165" t="s">
         <v>16</v>
@@ -12652,20 +14164,47 @@
       <c r="O165" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="166" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="P165" t="s">
+        <v>1359</v>
+      </c>
+      <c r="Q165" t="s">
+        <v>1632</v>
+      </c>
+    </row>
+    <row r="166" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A166" t="s">
         <v>180</v>
       </c>
+      <c r="B166" t="s">
+        <v>1636</v>
+      </c>
+      <c r="C166" t="s">
+        <v>1043</v>
+      </c>
+      <c r="D166" t="s">
+        <v>1043</v>
+      </c>
+      <c r="E166" t="s">
+        <v>1634</v>
+      </c>
       <c r="F166" t="s">
-        <v>1132</v>
+        <v>1638</v>
+      </c>
+      <c r="H166" t="s">
+        <v>1164</v>
+      </c>
+      <c r="I166" t="s">
+        <v>1640</v>
+      </c>
+      <c r="J166">
+        <v>1400</v>
       </c>
       <c r="K166">
-        <v>1</v>
-      </c>
-      <c r="L166" t="str">
+        <v>0.3</v>
+      </c>
+      <c r="L166">
         <f t="shared" si="2"/>
-        <v/>
+        <v>1820</v>
       </c>
       <c r="M166" t="s">
         <v>16</v>
@@ -12673,20 +14212,47 @@
       <c r="O166" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="167" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="P166" t="s">
+        <v>1359</v>
+      </c>
+      <c r="Q166" t="s">
+        <v>1636</v>
+      </c>
+    </row>
+    <row r="167" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A167" t="s">
         <v>181</v>
       </c>
+      <c r="B167" t="s">
+        <v>1637</v>
+      </c>
+      <c r="C167" t="s">
+        <v>1043</v>
+      </c>
+      <c r="D167" t="s">
+        <v>1043</v>
+      </c>
+      <c r="E167" t="s">
+        <v>1634</v>
+      </c>
       <c r="F167" t="s">
-        <v>1132</v>
+        <v>1639</v>
+      </c>
+      <c r="H167" t="s">
+        <v>1164</v>
+      </c>
+      <c r="I167" t="s">
+        <v>1641</v>
+      </c>
+      <c r="J167">
+        <v>400</v>
       </c>
       <c r="K167">
-        <v>1</v>
-      </c>
-      <c r="L167" t="str">
+        <v>0.3</v>
+      </c>
+      <c r="L167">
         <f t="shared" si="2"/>
-        <v/>
+        <v>520</v>
       </c>
       <c r="M167" t="s">
         <v>16</v>
@@ -12694,20 +14260,47 @@
       <c r="O167" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="168" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="P167" t="s">
+        <v>1359</v>
+      </c>
+      <c r="Q167" t="s">
+        <v>1637</v>
+      </c>
+    </row>
+    <row r="168" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A168" t="s">
         <v>182</v>
       </c>
+      <c r="B168" t="s">
+        <v>1642</v>
+      </c>
+      <c r="C168" t="s">
+        <v>1043</v>
+      </c>
+      <c r="D168" t="s">
+        <v>1043</v>
+      </c>
+      <c r="E168" t="s">
+        <v>1634</v>
+      </c>
       <c r="F168" t="s">
-        <v>1132</v>
+        <v>1643</v>
+      </c>
+      <c r="H168" t="s">
+        <v>1589</v>
+      </c>
+      <c r="I168" t="s">
+        <v>1644</v>
+      </c>
+      <c r="J168">
+        <v>2280</v>
       </c>
       <c r="K168">
-        <v>1</v>
-      </c>
-      <c r="L168" t="str">
+        <v>0.3</v>
+      </c>
+      <c r="L168">
         <f t="shared" si="2"/>
-        <v/>
+        <v>2964</v>
       </c>
       <c r="M168" t="s">
         <v>16</v>
@@ -12715,20 +14308,47 @@
       <c r="O168" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="169" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="P168" t="s">
+        <v>1359</v>
+      </c>
+      <c r="Q168" t="s">
+        <v>1642</v>
+      </c>
+    </row>
+    <row r="169" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A169" t="s">
         <v>183</v>
       </c>
+      <c r="B169" t="s">
+        <v>1645</v>
+      </c>
+      <c r="C169" t="s">
+        <v>1043</v>
+      </c>
+      <c r="D169" t="s">
+        <v>1043</v>
+      </c>
+      <c r="E169" t="s">
+        <v>1634</v>
+      </c>
       <c r="F169" t="s">
-        <v>1132</v>
+        <v>1646</v>
+      </c>
+      <c r="H169" t="s">
+        <v>1589</v>
+      </c>
+      <c r="I169" t="s">
+        <v>1647</v>
+      </c>
+      <c r="J169">
+        <v>14000</v>
       </c>
       <c r="K169">
-        <v>1</v>
-      </c>
-      <c r="L169" t="str">
+        <v>0.3</v>
+      </c>
+      <c r="L169">
         <f t="shared" si="2"/>
-        <v/>
+        <v>18200</v>
       </c>
       <c r="M169" t="s">
         <v>16</v>
@@ -12736,20 +14356,47 @@
       <c r="O169" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="170" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="P169" t="s">
+        <v>1359</v>
+      </c>
+      <c r="Q169" t="s">
+        <v>1645</v>
+      </c>
+    </row>
+    <row r="170" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A170" t="s">
         <v>184</v>
       </c>
+      <c r="B170" t="s">
+        <v>1650</v>
+      </c>
+      <c r="C170" t="s">
+        <v>1043</v>
+      </c>
+      <c r="D170" t="s">
+        <v>1043</v>
+      </c>
+      <c r="E170" t="s">
+        <v>1634</v>
+      </c>
       <c r="F170" t="s">
-        <v>1132</v>
+        <v>1648</v>
+      </c>
+      <c r="H170" t="s">
+        <v>1164</v>
+      </c>
+      <c r="I170" t="s">
+        <v>1649</v>
+      </c>
+      <c r="J170">
+        <v>650</v>
       </c>
       <c r="K170">
-        <v>1</v>
-      </c>
-      <c r="L170" t="str">
+        <v>0.3</v>
+      </c>
+      <c r="L170">
         <f t="shared" si="2"/>
-        <v/>
+        <v>845</v>
       </c>
       <c r="M170" t="s">
         <v>16</v>
@@ -12757,20 +14404,47 @@
       <c r="O170" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="171" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="P170" t="s">
+        <v>1359</v>
+      </c>
+      <c r="Q170" t="s">
+        <v>1650</v>
+      </c>
+    </row>
+    <row r="171" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A171" t="s">
         <v>185</v>
       </c>
+      <c r="B171" t="s">
+        <v>1651</v>
+      </c>
+      <c r="C171" t="s">
+        <v>1043</v>
+      </c>
+      <c r="D171" t="s">
+        <v>1043</v>
+      </c>
+      <c r="E171" t="s">
+        <v>1074</v>
+      </c>
       <c r="F171" t="s">
-        <v>1132</v>
+        <v>1652</v>
+      </c>
+      <c r="H171" t="s">
+        <v>1164</v>
+      </c>
+      <c r="I171" t="s">
+        <v>1653</v>
+      </c>
+      <c r="J171">
+        <v>1700</v>
       </c>
       <c r="K171">
-        <v>1</v>
-      </c>
-      <c r="L171" t="str">
+        <v>0.3</v>
+      </c>
+      <c r="L171">
         <f t="shared" si="2"/>
-        <v/>
+        <v>2210</v>
       </c>
       <c r="M171" t="s">
         <v>16</v>
@@ -12778,20 +14452,47 @@
       <c r="O171" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="172" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="P171" t="s">
+        <v>1359</v>
+      </c>
+      <c r="Q171" t="s">
+        <v>1651</v>
+      </c>
+    </row>
+    <row r="172" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A172" t="s">
         <v>186</v>
       </c>
+      <c r="B172" t="s">
+        <v>1654</v>
+      </c>
+      <c r="C172" t="s">
+        <v>1659</v>
+      </c>
+      <c r="D172" t="s">
+        <v>1666</v>
+      </c>
+      <c r="E172" t="s">
+        <v>1074</v>
+      </c>
       <c r="F172" t="s">
-        <v>1132</v>
+        <v>1663</v>
+      </c>
+      <c r="H172" t="s">
+        <v>1164</v>
+      </c>
+      <c r="I172" t="s">
+        <v>1660</v>
+      </c>
+      <c r="J172">
+        <v>20000</v>
       </c>
       <c r="K172">
-        <v>1</v>
-      </c>
-      <c r="L172" t="str">
+        <v>0.5</v>
+      </c>
+      <c r="L172">
         <f t="shared" si="2"/>
-        <v/>
+        <v>30000</v>
       </c>
       <c r="M172" t="s">
         <v>16</v>
@@ -12799,20 +14500,47 @@
       <c r="O172" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="173" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="P172" t="s">
+        <v>1359</v>
+      </c>
+      <c r="Q172" t="s">
+        <v>1654</v>
+      </c>
+    </row>
+    <row r="173" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A173" t="s">
         <v>187</v>
       </c>
+      <c r="B173" t="s">
+        <v>1655</v>
+      </c>
+      <c r="C173" t="s">
+        <v>1659</v>
+      </c>
+      <c r="D173" t="s">
+        <v>1666</v>
+      </c>
+      <c r="E173" t="s">
+        <v>1074</v>
+      </c>
       <c r="F173" t="s">
-        <v>1132</v>
+        <v>1664</v>
+      </c>
+      <c r="H173" t="s">
+        <v>1164</v>
+      </c>
+      <c r="I173" t="s">
+        <v>1661</v>
+      </c>
+      <c r="J173">
+        <v>4000</v>
       </c>
       <c r="K173">
-        <v>1</v>
-      </c>
-      <c r="L173" t="str">
+        <v>0.5</v>
+      </c>
+      <c r="L173">
         <f t="shared" si="2"/>
-        <v/>
+        <v>6000</v>
       </c>
       <c r="M173" t="s">
         <v>16</v>
@@ -12820,20 +14548,47 @@
       <c r="O173" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="174" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="P173" t="s">
+        <v>1359</v>
+      </c>
+      <c r="Q173" t="s">
+        <v>1655</v>
+      </c>
+    </row>
+    <row r="174" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A174" t="s">
         <v>188</v>
       </c>
+      <c r="B174" t="s">
+        <v>1658</v>
+      </c>
+      <c r="C174" t="s">
+        <v>1659</v>
+      </c>
+      <c r="D174" t="s">
+        <v>1666</v>
+      </c>
+      <c r="E174" t="s">
+        <v>1074</v>
+      </c>
       <c r="F174" t="s">
-        <v>1132</v>
+        <v>1665</v>
+      </c>
+      <c r="H174" t="s">
+        <v>1164</v>
+      </c>
+      <c r="I174" t="s">
+        <v>1662</v>
+      </c>
+      <c r="J174">
+        <v>27000</v>
       </c>
       <c r="K174">
-        <v>1</v>
-      </c>
-      <c r="L174" t="str">
+        <v>0.5</v>
+      </c>
+      <c r="L174">
         <f t="shared" si="2"/>
-        <v/>
+        <v>40500</v>
       </c>
       <c r="M174" t="s">
         <v>16</v>
@@ -12841,20 +14596,47 @@
       <c r="O174" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="175" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="P174" t="s">
+        <v>1359</v>
+      </c>
+      <c r="Q174" t="s">
+        <v>1658</v>
+      </c>
+    </row>
+    <row r="175" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A175" t="s">
         <v>189</v>
       </c>
+      <c r="B175" t="s">
+        <v>1656</v>
+      </c>
+      <c r="C175" t="s">
+        <v>1659</v>
+      </c>
+      <c r="D175" t="s">
+        <v>1667</v>
+      </c>
+      <c r="E175" t="s">
+        <v>1074</v>
+      </c>
       <c r="F175" t="s">
-        <v>1132</v>
+        <v>1668</v>
+      </c>
+      <c r="H175" t="s">
+        <v>1589</v>
+      </c>
+      <c r="I175" t="s">
+        <v>1670</v>
+      </c>
+      <c r="J175">
+        <v>700</v>
       </c>
       <c r="K175">
-        <v>1</v>
-      </c>
-      <c r="L175" t="str">
+        <v>0.5</v>
+      </c>
+      <c r="L175">
         <f t="shared" si="2"/>
-        <v/>
+        <v>1050</v>
       </c>
       <c r="M175" t="s">
         <v>16</v>
@@ -12862,20 +14644,47 @@
       <c r="O175" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="176" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="P175" t="s">
+        <v>1359</v>
+      </c>
+      <c r="Q175" t="s">
+        <v>1656</v>
+      </c>
+    </row>
+    <row r="176" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A176" t="s">
         <v>190</v>
       </c>
+      <c r="B176" t="s">
+        <v>1657</v>
+      </c>
+      <c r="C176" t="s">
+        <v>1659</v>
+      </c>
+      <c r="D176" t="s">
+        <v>1667</v>
+      </c>
+      <c r="E176" t="s">
+        <v>1074</v>
+      </c>
       <c r="F176" t="s">
-        <v>1132</v>
+        <v>1669</v>
+      </c>
+      <c r="H176" t="s">
+        <v>1589</v>
+      </c>
+      <c r="I176" t="s">
+        <v>1671</v>
+      </c>
+      <c r="J176">
+        <v>800</v>
       </c>
       <c r="K176">
-        <v>1</v>
-      </c>
-      <c r="L176" t="str">
+        <v>0.5</v>
+      </c>
+      <c r="L176">
         <f t="shared" si="2"/>
-        <v/>
+        <v>1200</v>
       </c>
       <c r="M176" t="s">
         <v>16</v>
@@ -12883,20 +14692,47 @@
       <c r="O176" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="177" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="P176" t="s">
+        <v>1359</v>
+      </c>
+      <c r="Q176" t="s">
+        <v>1657</v>
+      </c>
+    </row>
+    <row r="177" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A177" t="s">
         <v>191</v>
       </c>
+      <c r="B177" t="s">
+        <v>1672</v>
+      </c>
+      <c r="C177" t="s">
+        <v>1673</v>
+      </c>
+      <c r="D177" t="s">
+        <v>1673</v>
+      </c>
+      <c r="E177" t="s">
+        <v>1074</v>
+      </c>
       <c r="F177" t="s">
-        <v>1132</v>
+        <v>1678</v>
+      </c>
+      <c r="H177" t="s">
+        <v>1164</v>
+      </c>
+      <c r="I177" t="s">
+        <v>1684</v>
+      </c>
+      <c r="J177">
+        <v>1400</v>
       </c>
       <c r="K177">
-        <v>1</v>
-      </c>
-      <c r="L177" t="str">
+        <v>0.5</v>
+      </c>
+      <c r="L177">
         <f t="shared" si="2"/>
-        <v/>
+        <v>2100</v>
       </c>
       <c r="M177" t="s">
         <v>16</v>
@@ -12904,20 +14740,47 @@
       <c r="O177" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="178" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="P177" t="s">
+        <v>1359</v>
+      </c>
+      <c r="Q177" t="s">
+        <v>1672</v>
+      </c>
+    </row>
+    <row r="178" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A178" t="s">
         <v>192</v>
       </c>
+      <c r="B178" t="s">
+        <v>1674</v>
+      </c>
+      <c r="C178" t="s">
+        <v>1673</v>
+      </c>
+      <c r="D178" t="s">
+        <v>1673</v>
+      </c>
+      <c r="E178" t="s">
+        <v>1074</v>
+      </c>
       <c r="F178" t="s">
-        <v>1132</v>
+        <v>1679</v>
+      </c>
+      <c r="H178" t="s">
+        <v>1164</v>
+      </c>
+      <c r="I178" t="s">
+        <v>1685</v>
+      </c>
+      <c r="J178">
+        <v>700</v>
       </c>
       <c r="K178">
-        <v>1</v>
-      </c>
-      <c r="L178" t="str">
+        <v>0.5</v>
+      </c>
+      <c r="L178">
         <f t="shared" si="2"/>
-        <v/>
+        <v>1050</v>
       </c>
       <c r="M178" t="s">
         <v>16</v>
@@ -12925,20 +14788,47 @@
       <c r="O178" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="179" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="P178" t="s">
+        <v>1359</v>
+      </c>
+      <c r="Q178" t="s">
+        <v>1674</v>
+      </c>
+    </row>
+    <row r="179" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A179" t="s">
         <v>193</v>
       </c>
+      <c r="B179" t="s">
+        <v>1675</v>
+      </c>
+      <c r="C179" t="s">
+        <v>1673</v>
+      </c>
+      <c r="D179" t="s">
+        <v>1673</v>
+      </c>
+      <c r="E179" t="s">
+        <v>1680</v>
+      </c>
       <c r="F179" t="s">
-        <v>1132</v>
+        <v>1686</v>
+      </c>
+      <c r="H179" t="s">
+        <v>1164</v>
+      </c>
+      <c r="I179" t="s">
+        <v>1687</v>
+      </c>
+      <c r="J179">
+        <v>1800</v>
       </c>
       <c r="K179">
-        <v>1</v>
-      </c>
-      <c r="L179" t="str">
+        <v>0.5</v>
+      </c>
+      <c r="L179">
         <f t="shared" si="2"/>
-        <v/>
+        <v>2700</v>
       </c>
       <c r="M179" t="s">
         <v>16</v>
@@ -12946,20 +14836,47 @@
       <c r="O179" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="180" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="P179" t="s">
+        <v>1359</v>
+      </c>
+      <c r="Q179" t="s">
+        <v>1675</v>
+      </c>
+    </row>
+    <row r="180" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A180" t="s">
         <v>194</v>
       </c>
+      <c r="B180" t="s">
+        <v>1676</v>
+      </c>
+      <c r="C180" t="s">
+        <v>1673</v>
+      </c>
+      <c r="D180" t="s">
+        <v>1673</v>
+      </c>
+      <c r="E180" t="s">
+        <v>1682</v>
+      </c>
       <c r="F180" t="s">
-        <v>1132</v>
+        <v>1681</v>
+      </c>
+      <c r="H180" t="s">
+        <v>1164</v>
+      </c>
+      <c r="I180" t="s">
+        <v>1688</v>
+      </c>
+      <c r="J180">
+        <v>1400</v>
       </c>
       <c r="K180">
-        <v>1</v>
-      </c>
-      <c r="L180" t="str">
+        <v>0.5</v>
+      </c>
+      <c r="L180">
         <f t="shared" si="2"/>
-        <v/>
+        <v>2100</v>
       </c>
       <c r="M180" t="s">
         <v>16</v>
@@ -12967,20 +14884,47 @@
       <c r="O180" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="181" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="P180" t="s">
+        <v>1359</v>
+      </c>
+      <c r="Q180" t="s">
+        <v>1676</v>
+      </c>
+    </row>
+    <row r="181" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A181" t="s">
         <v>195</v>
       </c>
+      <c r="B181" t="s">
+        <v>1677</v>
+      </c>
+      <c r="C181" t="s">
+        <v>1673</v>
+      </c>
+      <c r="D181" t="s">
+        <v>1673</v>
+      </c>
+      <c r="E181" t="s">
+        <v>1074</v>
+      </c>
       <c r="F181" t="s">
-        <v>1132</v>
+        <v>1683</v>
+      </c>
+      <c r="H181" t="s">
+        <v>1164</v>
+      </c>
+      <c r="I181" t="s">
+        <v>1689</v>
+      </c>
+      <c r="J181">
+        <v>2600</v>
       </c>
       <c r="K181">
-        <v>1</v>
-      </c>
-      <c r="L181" t="str">
+        <v>0.5</v>
+      </c>
+      <c r="L181">
         <f t="shared" si="2"/>
-        <v/>
+        <v>3900</v>
       </c>
       <c r="M181" t="s">
         <v>16</v>
@@ -12988,20 +14932,47 @@
       <c r="O181" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="182" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="P181" t="s">
+        <v>1359</v>
+      </c>
+      <c r="Q181" t="s">
+        <v>1677</v>
+      </c>
+    </row>
+    <row r="182" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A182" t="s">
         <v>196</v>
       </c>
+      <c r="B182" t="s">
+        <v>1690</v>
+      </c>
+      <c r="C182" t="s">
+        <v>1053</v>
+      </c>
+      <c r="D182" t="s">
+        <v>1698</v>
+      </c>
+      <c r="E182" t="s">
+        <v>1699</v>
+      </c>
       <c r="F182" t="s">
-        <v>1132</v>
+        <v>1700</v>
+      </c>
+      <c r="H182" t="s">
+        <v>1164</v>
+      </c>
+      <c r="I182" t="s">
+        <v>1701</v>
+      </c>
+      <c r="J182">
+        <v>2600</v>
       </c>
       <c r="K182">
-        <v>1</v>
-      </c>
-      <c r="L182" t="str">
+        <v>0.5</v>
+      </c>
+      <c r="L182">
         <f t="shared" si="2"/>
-        <v/>
+        <v>3900</v>
       </c>
       <c r="M182" t="s">
         <v>16</v>
@@ -13009,20 +14980,47 @@
       <c r="O182" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="183" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="P182" t="s">
+        <v>1359</v>
+      </c>
+      <c r="Q182" t="s">
+        <v>1690</v>
+      </c>
+    </row>
+    <row r="183" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A183" t="s">
         <v>197</v>
       </c>
+      <c r="B183" t="s">
+        <v>1691</v>
+      </c>
+      <c r="C183" t="s">
+        <v>1053</v>
+      </c>
+      <c r="D183" t="s">
+        <v>1709</v>
+      </c>
+      <c r="E183" t="s">
+        <v>1710</v>
+      </c>
       <c r="F183" t="s">
-        <v>1132</v>
+        <v>1711</v>
+      </c>
+      <c r="H183" t="s">
+        <v>1164</v>
+      </c>
+      <c r="I183" t="s">
+        <v>1702</v>
+      </c>
+      <c r="J183">
+        <v>3200</v>
       </c>
       <c r="K183">
-        <v>1</v>
-      </c>
-      <c r="L183" t="str">
+        <v>0.5</v>
+      </c>
+      <c r="L183">
         <f t="shared" si="2"/>
-        <v/>
+        <v>4800</v>
       </c>
       <c r="M183" t="s">
         <v>16</v>
@@ -13030,20 +15028,47 @@
       <c r="O183" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="184" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="P183" t="s">
+        <v>1359</v>
+      </c>
+      <c r="Q183" t="s">
+        <v>1691</v>
+      </c>
+    </row>
+    <row r="184" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A184" t="s">
         <v>198</v>
       </c>
+      <c r="B184" t="s">
+        <v>1693</v>
+      </c>
+      <c r="C184" t="s">
+        <v>1053</v>
+      </c>
+      <c r="D184" t="s">
+        <v>1712</v>
+      </c>
+      <c r="E184" t="s">
+        <v>1713</v>
+      </c>
       <c r="F184" t="s">
-        <v>1132</v>
+        <v>1714</v>
+      </c>
+      <c r="H184" t="s">
+        <v>1164</v>
+      </c>
+      <c r="I184" t="s">
+        <v>1703</v>
+      </c>
+      <c r="J184">
+        <v>4600</v>
       </c>
       <c r="K184">
-        <v>1</v>
-      </c>
-      <c r="L184" t="str">
+        <v>0.5</v>
+      </c>
+      <c r="L184">
         <f t="shared" si="2"/>
-        <v/>
+        <v>6900</v>
       </c>
       <c r="M184" t="s">
         <v>16</v>
@@ -13051,20 +15076,47 @@
       <c r="O184" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="185" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="P184" t="s">
+        <v>1359</v>
+      </c>
+      <c r="Q184" t="s">
+        <v>1693</v>
+      </c>
+    </row>
+    <row r="185" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A185" t="s">
         <v>199</v>
       </c>
+      <c r="B185" t="s">
+        <v>1694</v>
+      </c>
+      <c r="C185" t="s">
+        <v>1053</v>
+      </c>
+      <c r="D185" t="s">
+        <v>1715</v>
+      </c>
+      <c r="E185" t="s">
+        <v>1716</v>
+      </c>
       <c r="F185" t="s">
-        <v>1132</v>
+        <v>1717</v>
+      </c>
+      <c r="H185" t="s">
+        <v>1164</v>
+      </c>
+      <c r="I185" t="s">
+        <v>1704</v>
+      </c>
+      <c r="J185">
+        <v>2600</v>
       </c>
       <c r="K185">
-        <v>1</v>
-      </c>
-      <c r="L185" t="str">
+        <v>0.5</v>
+      </c>
+      <c r="L185">
         <f t="shared" si="2"/>
-        <v/>
+        <v>3900</v>
       </c>
       <c r="M185" t="s">
         <v>16</v>
@@ -13072,20 +15124,47 @@
       <c r="O185" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="186" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="P185" t="s">
+        <v>1359</v>
+      </c>
+      <c r="Q185" t="s">
+        <v>1694</v>
+      </c>
+    </row>
+    <row r="186" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A186" t="s">
         <v>200</v>
       </c>
+      <c r="B186" t="s">
+        <v>1695</v>
+      </c>
+      <c r="C186" t="s">
+        <v>1053</v>
+      </c>
+      <c r="D186" t="s">
+        <v>1718</v>
+      </c>
+      <c r="E186" t="s">
+        <v>1719</v>
+      </c>
       <c r="F186" t="s">
-        <v>1132</v>
+        <v>1719</v>
+      </c>
+      <c r="H186" t="s">
+        <v>1164</v>
+      </c>
+      <c r="I186" t="s">
+        <v>1705</v>
+      </c>
+      <c r="J186">
+        <v>2900</v>
       </c>
       <c r="K186">
-        <v>1</v>
-      </c>
-      <c r="L186" t="str">
+        <v>0.5</v>
+      </c>
+      <c r="L186">
         <f t="shared" si="2"/>
-        <v/>
+        <v>4350</v>
       </c>
       <c r="M186" t="s">
         <v>16</v>
@@ -13093,20 +15172,47 @@
       <c r="O186" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="187" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="P186" t="s">
+        <v>1359</v>
+      </c>
+      <c r="Q186" t="s">
+        <v>1695</v>
+      </c>
+    </row>
+    <row r="187" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A187" t="s">
         <v>201</v>
       </c>
+      <c r="B187" t="s">
+        <v>1696</v>
+      </c>
+      <c r="C187" t="s">
+        <v>1053</v>
+      </c>
+      <c r="D187" t="s">
+        <v>1720</v>
+      </c>
+      <c r="E187" t="s">
+        <v>1721</v>
+      </c>
       <c r="F187" t="s">
-        <v>1132</v>
+        <v>1722</v>
+      </c>
+      <c r="H187" t="s">
+        <v>1164</v>
+      </c>
+      <c r="I187" t="s">
+        <v>1706</v>
+      </c>
+      <c r="J187">
+        <v>4200</v>
       </c>
       <c r="K187">
-        <v>1</v>
-      </c>
-      <c r="L187" t="str">
+        <v>0.5</v>
+      </c>
+      <c r="L187">
         <f t="shared" si="2"/>
-        <v/>
+        <v>6300</v>
       </c>
       <c r="M187" t="s">
         <v>16</v>
@@ -13114,20 +15220,47 @@
       <c r="O187" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="188" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="P187" t="s">
+        <v>1359</v>
+      </c>
+      <c r="Q187" t="s">
+        <v>1696</v>
+      </c>
+    </row>
+    <row r="188" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A188" t="s">
         <v>202</v>
       </c>
+      <c r="B188" t="s">
+        <v>1697</v>
+      </c>
+      <c r="C188" t="s">
+        <v>1053</v>
+      </c>
+      <c r="D188" t="s">
+        <v>1720</v>
+      </c>
+      <c r="E188" t="s">
+        <v>1723</v>
+      </c>
       <c r="F188" t="s">
-        <v>1132</v>
+        <v>1724</v>
+      </c>
+      <c r="H188" t="s">
+        <v>1164</v>
+      </c>
+      <c r="I188" t="s">
+        <v>1707</v>
+      </c>
+      <c r="J188">
+        <v>6000</v>
       </c>
       <c r="K188">
-        <v>1</v>
-      </c>
-      <c r="L188" t="str">
+        <v>0.5</v>
+      </c>
+      <c r="L188">
         <f t="shared" si="2"/>
-        <v/>
+        <v>9000</v>
       </c>
       <c r="M188" t="s">
         <v>16</v>
@@ -13135,20 +15268,47 @@
       <c r="O188" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="189" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="P188" t="s">
+        <v>1359</v>
+      </c>
+      <c r="Q188" t="s">
+        <v>1697</v>
+      </c>
+    </row>
+    <row r="189" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A189" t="s">
         <v>203</v>
       </c>
+      <c r="B189" t="s">
+        <v>1692</v>
+      </c>
+      <c r="C189" t="s">
+        <v>1053</v>
+      </c>
+      <c r="D189" t="s">
+        <v>1720</v>
+      </c>
+      <c r="E189" t="s">
+        <v>1723</v>
+      </c>
       <c r="F189" t="s">
-        <v>1132</v>
+        <v>1725</v>
+      </c>
+      <c r="H189" t="s">
+        <v>1164</v>
+      </c>
+      <c r="I189" t="s">
+        <v>1708</v>
+      </c>
+      <c r="J189">
+        <v>5000</v>
       </c>
       <c r="K189">
-        <v>1</v>
-      </c>
-      <c r="L189" t="str">
+        <v>0.5</v>
+      </c>
+      <c r="L189">
         <f t="shared" si="2"/>
-        <v/>
+        <v>7500</v>
       </c>
       <c r="M189" t="s">
         <v>16</v>
@@ -13156,20 +15316,50 @@
       <c r="O189" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="190" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="P189" t="s">
+        <v>1359</v>
+      </c>
+      <c r="Q189" t="s">
+        <v>1692</v>
+      </c>
+    </row>
+    <row r="190" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A190" t="s">
         <v>204</v>
       </c>
+      <c r="B190" t="s">
+        <v>1726</v>
+      </c>
+      <c r="C190" t="s">
+        <v>1730</v>
+      </c>
+      <c r="D190" t="s">
+        <v>1731</v>
+      </c>
+      <c r="E190" t="s">
+        <v>1634</v>
+      </c>
       <c r="F190" t="s">
-        <v>1132</v>
+        <v>1732</v>
+      </c>
+      <c r="G190" t="s">
+        <v>1733</v>
+      </c>
+      <c r="H190" t="s">
+        <v>1164</v>
+      </c>
+      <c r="I190" t="s">
+        <v>1740</v>
+      </c>
+      <c r="J190">
+        <v>1300</v>
       </c>
       <c r="K190">
-        <v>1</v>
-      </c>
-      <c r="L190" t="str">
+        <v>0.5</v>
+      </c>
+      <c r="L190">
         <f t="shared" si="2"/>
-        <v/>
+        <v>1950</v>
       </c>
       <c r="M190" t="s">
         <v>16</v>
@@ -13177,20 +15367,50 @@
       <c r="O190" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="191" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="P190" t="s">
+        <v>1359</v>
+      </c>
+      <c r="Q190" t="s">
+        <v>1726</v>
+      </c>
+    </row>
+    <row r="191" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A191" t="s">
         <v>205</v>
       </c>
+      <c r="B191" t="s">
+        <v>1727</v>
+      </c>
+      <c r="C191" t="s">
+        <v>1730</v>
+      </c>
+      <c r="D191" t="s">
+        <v>1731</v>
+      </c>
+      <c r="E191" t="s">
+        <v>1634</v>
+      </c>
       <c r="F191" t="s">
-        <v>1132</v>
+        <v>1732</v>
+      </c>
+      <c r="G191" t="s">
+        <v>1734</v>
+      </c>
+      <c r="H191" t="s">
+        <v>1164</v>
+      </c>
+      <c r="I191" t="s">
+        <v>1743</v>
+      </c>
+      <c r="J191">
+        <v>1300</v>
       </c>
       <c r="K191">
-        <v>1</v>
-      </c>
-      <c r="L191" t="str">
+        <v>0.5</v>
+      </c>
+      <c r="L191">
         <f t="shared" si="2"/>
-        <v/>
+        <v>1950</v>
       </c>
       <c r="M191" t="s">
         <v>16</v>
@@ -13198,20 +15418,50 @@
       <c r="O191" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="192" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="P191" t="s">
+        <v>1359</v>
+      </c>
+      <c r="Q191" t="s">
+        <v>1727</v>
+      </c>
+    </row>
+    <row r="192" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A192" t="s">
         <v>206</v>
       </c>
+      <c r="B192" t="s">
+        <v>1728</v>
+      </c>
+      <c r="C192" t="s">
+        <v>1730</v>
+      </c>
+      <c r="D192" t="s">
+        <v>1731</v>
+      </c>
+      <c r="E192" t="s">
+        <v>1634</v>
+      </c>
       <c r="F192" t="s">
-        <v>1132</v>
+        <v>1732</v>
+      </c>
+      <c r="G192" t="s">
+        <v>1735</v>
+      </c>
+      <c r="H192" t="s">
+        <v>1164</v>
+      </c>
+      <c r="I192" t="s">
+        <v>1744</v>
+      </c>
+      <c r="J192">
+        <v>1300</v>
       </c>
       <c r="K192">
-        <v>1</v>
-      </c>
-      <c r="L192" t="str">
+        <v>0.5</v>
+      </c>
+      <c r="L192">
         <f t="shared" si="2"/>
-        <v/>
+        <v>1950</v>
       </c>
       <c r="M192" t="s">
         <v>16</v>
@@ -13219,20 +15469,50 @@
       <c r="O192" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="193" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="P192" t="s">
+        <v>1359</v>
+      </c>
+      <c r="Q192" t="s">
+        <v>1728</v>
+      </c>
+    </row>
+    <row r="193" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A193" t="s">
         <v>207</v>
       </c>
+      <c r="B193" t="s">
+        <v>1729</v>
+      </c>
+      <c r="C193" t="s">
+        <v>1730</v>
+      </c>
+      <c r="D193" t="s">
+        <v>1731</v>
+      </c>
+      <c r="E193" t="s">
+        <v>1634</v>
+      </c>
       <c r="F193" t="s">
-        <v>1132</v>
+        <v>1732</v>
+      </c>
+      <c r="G193" t="s">
+        <v>1736</v>
+      </c>
+      <c r="H193" t="s">
+        <v>1164</v>
+      </c>
+      <c r="I193" t="s">
+        <v>1745</v>
+      </c>
+      <c r="J193">
+        <v>1300</v>
       </c>
       <c r="K193">
-        <v>1</v>
-      </c>
-      <c r="L193" t="str">
+        <v>0.5</v>
+      </c>
+      <c r="L193">
         <f t="shared" si="2"/>
-        <v/>
+        <v>1950</v>
       </c>
       <c r="M193" t="s">
         <v>16</v>
@@ -13240,20 +15520,47 @@
       <c r="O193" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="194" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="P193" t="s">
+        <v>1359</v>
+      </c>
+      <c r="Q193" t="s">
+        <v>1729</v>
+      </c>
+    </row>
+    <row r="194" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A194" t="s">
         <v>208</v>
       </c>
+      <c r="B194" t="s">
+        <v>1738</v>
+      </c>
+      <c r="C194" t="s">
+        <v>1730</v>
+      </c>
+      <c r="D194" t="s">
+        <v>1731</v>
+      </c>
+      <c r="E194" t="s">
+        <v>1074</v>
+      </c>
       <c r="F194" t="s">
-        <v>1132</v>
+        <v>1737</v>
+      </c>
+      <c r="H194" t="s">
+        <v>1589</v>
+      </c>
+      <c r="I194" t="s">
+        <v>1741</v>
+      </c>
+      <c r="J194">
+        <v>7000</v>
       </c>
       <c r="K194">
-        <v>1</v>
-      </c>
-      <c r="L194" t="str">
+        <v>0.5</v>
+      </c>
+      <c r="L194">
         <f t="shared" ref="L194:L257" si="6">IF(J194="","",J194*(1+K194))</f>
-        <v/>
+        <v>10500</v>
       </c>
       <c r="M194" t="s">
         <v>16</v>
@@ -13261,20 +15568,47 @@
       <c r="O194" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="195" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="P194" t="s">
+        <v>1359</v>
+      </c>
+      <c r="Q194" t="s">
+        <v>1738</v>
+      </c>
+    </row>
+    <row r="195" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A195" t="s">
         <v>209</v>
       </c>
+      <c r="B195" t="s">
+        <v>1739</v>
+      </c>
+      <c r="C195" t="s">
+        <v>1730</v>
+      </c>
+      <c r="D195" t="s">
+        <v>1731</v>
+      </c>
+      <c r="E195" t="s">
+        <v>1074</v>
+      </c>
       <c r="F195" t="s">
-        <v>1132</v>
+        <v>1746</v>
+      </c>
+      <c r="H195" t="s">
+        <v>1589</v>
+      </c>
+      <c r="I195" t="s">
+        <v>1742</v>
+      </c>
+      <c r="J195">
+        <v>8000</v>
       </c>
       <c r="K195">
-        <v>1</v>
-      </c>
-      <c r="L195" t="str">
+        <v>0.5</v>
+      </c>
+      <c r="L195">
         <f t="shared" si="6"/>
-        <v/>
+        <v>12000</v>
       </c>
       <c r="M195" t="s">
         <v>16</v>
@@ -13282,20 +15616,47 @@
       <c r="O195" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="196" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="P195" t="s">
+        <v>1359</v>
+      </c>
+      <c r="Q195" t="s">
+        <v>1739</v>
+      </c>
+    </row>
+    <row r="196" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A196" t="s">
         <v>210</v>
       </c>
+      <c r="B196" t="s">
+        <v>1747</v>
+      </c>
+      <c r="C196" t="s">
+        <v>1730</v>
+      </c>
+      <c r="D196" t="s">
+        <v>1044</v>
+      </c>
+      <c r="E196" t="s">
+        <v>1748</v>
+      </c>
       <c r="F196" t="s">
-        <v>1132</v>
+        <v>1749</v>
+      </c>
+      <c r="H196" t="s">
+        <v>1164</v>
+      </c>
+      <c r="I196" t="s">
+        <v>1750</v>
+      </c>
+      <c r="J196">
+        <v>7000</v>
       </c>
       <c r="K196">
-        <v>1</v>
-      </c>
-      <c r="L196" t="str">
+        <v>0.5</v>
+      </c>
+      <c r="L196">
         <f t="shared" si="6"/>
-        <v/>
+        <v>10500</v>
       </c>
       <c r="M196" t="s">
         <v>16</v>
@@ -13303,20 +15664,47 @@
       <c r="O196" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="197" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="P196" t="s">
+        <v>1359</v>
+      </c>
+      <c r="Q196" t="s">
+        <v>1747</v>
+      </c>
+    </row>
+    <row r="197" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A197" t="s">
         <v>211</v>
       </c>
+      <c r="B197" t="s">
+        <v>1751</v>
+      </c>
+      <c r="C197" t="s">
+        <v>1730</v>
+      </c>
+      <c r="D197" t="s">
+        <v>1044</v>
+      </c>
+      <c r="E197" t="s">
+        <v>1753</v>
+      </c>
       <c r="F197" t="s">
-        <v>1132</v>
+        <v>1752</v>
+      </c>
+      <c r="H197" t="s">
+        <v>1164</v>
+      </c>
+      <c r="I197" t="s">
+        <v>1754</v>
+      </c>
+      <c r="J197">
+        <v>1300</v>
       </c>
       <c r="K197">
         <v>1</v>
       </c>
-      <c r="L197" t="str">
+      <c r="L197">
         <f t="shared" si="6"/>
-        <v/>
+        <v>2600</v>
       </c>
       <c r="M197" t="s">
         <v>16</v>
@@ -13324,20 +15712,47 @@
       <c r="O197" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="198" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="P197" t="s">
+        <v>1359</v>
+      </c>
+      <c r="Q197" t="s">
+        <v>1751</v>
+      </c>
+    </row>
+    <row r="198" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A198" t="s">
         <v>212</v>
       </c>
+      <c r="B198" t="s">
+        <v>1755</v>
+      </c>
+      <c r="C198" t="s">
+        <v>1730</v>
+      </c>
+      <c r="D198" t="s">
+        <v>1044</v>
+      </c>
+      <c r="E198" t="s">
+        <v>1756</v>
+      </c>
       <c r="F198" t="s">
-        <v>1132</v>
+        <v>1757</v>
+      </c>
+      <c r="H198" t="s">
+        <v>1164</v>
+      </c>
+      <c r="I198" t="s">
+        <v>1758</v>
+      </c>
+      <c r="J198">
+        <v>2100</v>
       </c>
       <c r="K198">
-        <v>1</v>
-      </c>
-      <c r="L198" t="str">
+        <v>0.5</v>
+      </c>
+      <c r="L198">
         <f t="shared" si="6"/>
-        <v/>
+        <v>3150</v>
       </c>
       <c r="M198" t="s">
         <v>16</v>
@@ -13345,20 +15760,47 @@
       <c r="O198" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="199" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="P198" t="s">
+        <v>1359</v>
+      </c>
+      <c r="Q198" t="s">
+        <v>1755</v>
+      </c>
+    </row>
+    <row r="199" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A199" t="s">
         <v>213</v>
       </c>
+      <c r="B199" t="s">
+        <v>1761</v>
+      </c>
+      <c r="C199" t="s">
+        <v>1730</v>
+      </c>
+      <c r="D199" t="s">
+        <v>1044</v>
+      </c>
+      <c r="E199" t="s">
+        <v>1760</v>
+      </c>
       <c r="F199" t="s">
-        <v>1132</v>
+        <v>1759</v>
+      </c>
+      <c r="H199" t="s">
+        <v>1164</v>
+      </c>
+      <c r="I199" t="s">
+        <v>1762</v>
+      </c>
+      <c r="J199">
+        <v>2000</v>
       </c>
       <c r="K199">
-        <v>1</v>
-      </c>
-      <c r="L199" t="str">
+        <v>0.5</v>
+      </c>
+      <c r="L199">
         <f t="shared" si="6"/>
-        <v/>
+        <v>3000</v>
       </c>
       <c r="M199" t="s">
         <v>16</v>
@@ -13366,20 +15808,47 @@
       <c r="O199" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="200" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="P199" t="s">
+        <v>1359</v>
+      </c>
+      <c r="Q199" t="s">
+        <v>1761</v>
+      </c>
+    </row>
+    <row r="200" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A200" t="s">
         <v>214</v>
       </c>
+      <c r="B200" t="s">
+        <v>1763</v>
+      </c>
+      <c r="C200" t="s">
+        <v>1730</v>
+      </c>
+      <c r="D200" t="s">
+        <v>1044</v>
+      </c>
+      <c r="E200" t="s">
+        <v>1634</v>
+      </c>
       <c r="F200" t="s">
-        <v>1132</v>
+        <v>1764</v>
+      </c>
+      <c r="H200" t="s">
+        <v>1164</v>
+      </c>
+      <c r="I200" t="s">
+        <v>1765</v>
+      </c>
+      <c r="J200">
+        <v>6600</v>
       </c>
       <c r="K200">
-        <v>1</v>
-      </c>
-      <c r="L200" t="str">
+        <v>0.5</v>
+      </c>
+      <c r="L200">
         <f t="shared" si="6"/>
-        <v/>
+        <v>9900</v>
       </c>
       <c r="M200" t="s">
         <v>16</v>
@@ -13387,20 +15856,47 @@
       <c r="O200" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="201" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="P200" t="s">
+        <v>1359</v>
+      </c>
+      <c r="Q200" t="s">
+        <v>1763</v>
+      </c>
+    </row>
+    <row r="201" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A201" t="s">
         <v>215</v>
       </c>
+      <c r="B201" t="s">
+        <v>1770</v>
+      </c>
+      <c r="C201" t="s">
+        <v>1730</v>
+      </c>
+      <c r="D201" t="s">
+        <v>1768</v>
+      </c>
+      <c r="E201" t="s">
+        <v>1769</v>
+      </c>
       <c r="F201" t="s">
-        <v>1132</v>
+        <v>1766</v>
+      </c>
+      <c r="H201" t="s">
+        <v>1164</v>
+      </c>
+      <c r="I201" t="s">
+        <v>1767</v>
+      </c>
+      <c r="J201">
+        <v>1000</v>
       </c>
       <c r="K201">
         <v>1</v>
       </c>
-      <c r="L201" t="str">
+      <c r="L201">
         <f t="shared" si="6"/>
-        <v/>
+        <v>2000</v>
       </c>
       <c r="M201" t="s">
         <v>16</v>
@@ -13408,602 +15904,1598 @@
       <c r="O201" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="202" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="P201" t="s">
+        <v>1359</v>
+      </c>
+      <c r="Q201" t="s">
+        <v>1770</v>
+      </c>
+    </row>
+    <row r="202" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A202" t="s">
         <v>216</v>
       </c>
+      <c r="B202" t="s">
+        <v>1774</v>
+      </c>
+      <c r="C202" t="s">
+        <v>1730</v>
+      </c>
+      <c r="D202" t="s">
+        <v>1768</v>
+      </c>
+      <c r="E202" t="s">
+        <v>1773</v>
+      </c>
       <c r="F202" t="s">
-        <v>1132</v>
+        <v>1771</v>
+      </c>
+      <c r="H202" t="s">
+        <v>1164</v>
+      </c>
+      <c r="I202" t="s">
+        <v>1772</v>
+      </c>
+      <c r="J202">
+        <v>6600</v>
       </c>
       <c r="K202">
-        <v>1</v>
-      </c>
-      <c r="L202" t="str">
+        <v>0.5</v>
+      </c>
+      <c r="L202">
         <f t="shared" si="6"/>
-        <v/>
+        <v>9900</v>
+      </c>
+      <c r="M202" t="s">
+        <v>16</v>
       </c>
       <c r="O202" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="203" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="P202" t="s">
+        <v>1359</v>
+      </c>
+      <c r="Q202" t="s">
+        <v>1774</v>
+      </c>
+    </row>
+    <row r="203" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A203" t="s">
         <v>217</v>
       </c>
+      <c r="B203" t="s">
+        <v>1775</v>
+      </c>
+      <c r="C203" t="s">
+        <v>1781</v>
+      </c>
+      <c r="D203" t="s">
+        <v>1782</v>
+      </c>
+      <c r="E203" t="s">
+        <v>1787</v>
+      </c>
       <c r="F203" t="s">
-        <v>1132</v>
+        <v>1783</v>
+      </c>
+      <c r="H203" t="s">
+        <v>1164</v>
+      </c>
+      <c r="I203" t="s">
+        <v>1784</v>
+      </c>
+      <c r="J203">
+        <v>6400</v>
       </c>
       <c r="K203">
-        <v>1</v>
-      </c>
-      <c r="L203" t="str">
+        <v>0.5</v>
+      </c>
+      <c r="L203">
         <f t="shared" si="6"/>
-        <v/>
+        <v>9600</v>
+      </c>
+      <c r="M203" t="s">
+        <v>16</v>
       </c>
       <c r="O203" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="204" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="P203" t="s">
+        <v>1359</v>
+      </c>
+      <c r="Q203" t="s">
+        <v>1775</v>
+      </c>
+    </row>
+    <row r="204" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A204" t="s">
         <v>218</v>
       </c>
+      <c r="B204" t="s">
+        <v>1776</v>
+      </c>
+      <c r="C204" t="s">
+        <v>1781</v>
+      </c>
+      <c r="D204" t="s">
+        <v>1782</v>
+      </c>
+      <c r="E204" t="s">
+        <v>1787</v>
+      </c>
       <c r="F204" t="s">
-        <v>1132</v>
+        <v>1786</v>
+      </c>
+      <c r="H204" t="s">
+        <v>1164</v>
+      </c>
+      <c r="I204" t="s">
+        <v>1785</v>
+      </c>
+      <c r="J204">
+        <v>10000</v>
       </c>
       <c r="K204">
-        <v>1</v>
-      </c>
-      <c r="L204" t="str">
+        <v>0.5</v>
+      </c>
+      <c r="L204">
         <f t="shared" si="6"/>
-        <v/>
+        <v>15000</v>
+      </c>
+      <c r="M204" t="s">
+        <v>16</v>
       </c>
       <c r="O204" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="205" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="P204" t="s">
+        <v>1359</v>
+      </c>
+      <c r="Q204" t="s">
+        <v>1776</v>
+      </c>
+    </row>
+    <row r="205" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A205" t="s">
         <v>219</v>
       </c>
+      <c r="B205" t="s">
+        <v>1777</v>
+      </c>
+      <c r="C205" t="s">
+        <v>1781</v>
+      </c>
+      <c r="D205" t="s">
+        <v>1782</v>
+      </c>
+      <c r="E205" t="s">
+        <v>1074</v>
+      </c>
       <c r="F205" t="s">
-        <v>1132</v>
+        <v>1788</v>
+      </c>
+      <c r="H205" t="s">
+        <v>1164</v>
+      </c>
+      <c r="I205" t="s">
+        <v>1789</v>
+      </c>
+      <c r="J205">
+        <v>2400</v>
       </c>
       <c r="K205">
-        <v>1</v>
-      </c>
-      <c r="L205" t="str">
+        <v>0.5</v>
+      </c>
+      <c r="L205">
         <f t="shared" si="6"/>
-        <v/>
+        <v>3600</v>
+      </c>
+      <c r="M205" t="s">
+        <v>16</v>
       </c>
       <c r="O205" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="206" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="P205" t="s">
+        <v>1359</v>
+      </c>
+      <c r="Q205" t="s">
+        <v>1777</v>
+      </c>
+    </row>
+    <row r="206" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A206" t="s">
         <v>220</v>
       </c>
+      <c r="B206" t="s">
+        <v>1778</v>
+      </c>
+      <c r="C206" t="s">
+        <v>1781</v>
+      </c>
+      <c r="D206" t="s">
+        <v>1782</v>
+      </c>
+      <c r="E206" t="s">
+        <v>1074</v>
+      </c>
       <c r="F206" t="s">
-        <v>1132</v>
+        <v>1791</v>
+      </c>
+      <c r="H206" t="s">
+        <v>1164</v>
+      </c>
+      <c r="I206" t="s">
+        <v>1790</v>
+      </c>
+      <c r="J206">
+        <v>3200</v>
       </c>
       <c r="K206">
-        <v>1</v>
-      </c>
-      <c r="L206" t="str">
+        <v>0.5</v>
+      </c>
+      <c r="L206">
         <f t="shared" si="6"/>
-        <v/>
+        <v>4800</v>
+      </c>
+      <c r="M206" t="s">
+        <v>16</v>
       </c>
       <c r="O206" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="207" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="P206" t="s">
+        <v>1359</v>
+      </c>
+      <c r="Q206" t="s">
+        <v>1778</v>
+      </c>
+    </row>
+    <row r="207" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A207" t="s">
         <v>221</v>
       </c>
+      <c r="B207" t="s">
+        <v>1779</v>
+      </c>
+      <c r="C207" t="s">
+        <v>1781</v>
+      </c>
+      <c r="D207" t="s">
+        <v>1782</v>
+      </c>
+      <c r="E207" t="s">
+        <v>1787</v>
+      </c>
       <c r="F207" t="s">
-        <v>1132</v>
+        <v>1792</v>
+      </c>
+      <c r="H207" t="s">
+        <v>1164</v>
+      </c>
+      <c r="I207" t="s">
+        <v>1793</v>
+      </c>
+      <c r="J207">
+        <v>11800</v>
       </c>
       <c r="K207">
-        <v>1</v>
-      </c>
-      <c r="L207" t="str">
+        <v>0.5</v>
+      </c>
+      <c r="L207">
         <f t="shared" si="6"/>
-        <v/>
+        <v>17700</v>
+      </c>
+      <c r="M207" t="s">
+        <v>16</v>
       </c>
       <c r="O207" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="208" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="P207" t="s">
+        <v>1359</v>
+      </c>
+      <c r="Q207" t="s">
+        <v>1779</v>
+      </c>
+    </row>
+    <row r="208" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A208" t="s">
         <v>222</v>
       </c>
+      <c r="B208" t="s">
+        <v>1780</v>
+      </c>
+      <c r="C208" t="s">
+        <v>1781</v>
+      </c>
+      <c r="D208" t="s">
+        <v>1782</v>
+      </c>
+      <c r="E208" t="s">
+        <v>1074</v>
+      </c>
       <c r="F208" t="s">
-        <v>1132</v>
+        <v>1794</v>
+      </c>
+      <c r="H208" t="s">
+        <v>1164</v>
+      </c>
+      <c r="I208" t="s">
+        <v>1795</v>
+      </c>
+      <c r="J208">
+        <v>11000</v>
       </c>
       <c r="K208">
-        <v>1</v>
-      </c>
-      <c r="L208" t="str">
+        <v>0.5</v>
+      </c>
+      <c r="L208">
         <f t="shared" si="6"/>
-        <v/>
+        <v>16500</v>
+      </c>
+      <c r="M208" t="s">
+        <v>16</v>
       </c>
       <c r="O208" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="209" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="P208" t="s">
+        <v>1359</v>
+      </c>
+      <c r="Q208" t="s">
+        <v>1780</v>
+      </c>
+    </row>
+    <row r="209" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A209" t="s">
         <v>223</v>
       </c>
+      <c r="B209" t="s">
+        <v>1796</v>
+      </c>
+      <c r="C209" t="s">
+        <v>1797</v>
+      </c>
+      <c r="D209" t="s">
+        <v>1798</v>
+      </c>
+      <c r="E209" t="s">
+        <v>1801</v>
+      </c>
       <c r="F209" t="s">
-        <v>1132</v>
+        <v>1799</v>
+      </c>
+      <c r="H209" t="s">
+        <v>1540</v>
+      </c>
+      <c r="I209" t="s">
+        <v>1800</v>
+      </c>
+      <c r="J209">
+        <v>5000</v>
       </c>
       <c r="K209">
-        <v>1</v>
-      </c>
-      <c r="L209" t="str">
+        <v>0.5</v>
+      </c>
+      <c r="L209">
         <f t="shared" si="6"/>
-        <v/>
+        <v>7500</v>
+      </c>
+      <c r="M209" t="s">
+        <v>16</v>
       </c>
       <c r="O209" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="210" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="P209" t="s">
+        <v>1359</v>
+      </c>
+      <c r="Q209" t="s">
+        <v>1796</v>
+      </c>
+    </row>
+    <row r="210" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A210" t="s">
         <v>224</v>
       </c>
+      <c r="B210" t="s">
+        <v>1805</v>
+      </c>
+      <c r="C210" t="s">
+        <v>1797</v>
+      </c>
+      <c r="D210" t="s">
+        <v>1798</v>
+      </c>
+      <c r="E210" t="s">
+        <v>1801</v>
+      </c>
       <c r="F210" t="s">
-        <v>1132</v>
+        <v>1802</v>
+      </c>
+      <c r="H210" t="s">
+        <v>1540</v>
+      </c>
+      <c r="I210" t="s">
+        <v>1803</v>
+      </c>
+      <c r="J210">
+        <v>4500</v>
       </c>
       <c r="K210">
-        <v>1</v>
-      </c>
-      <c r="L210" t="str">
+        <v>0.5</v>
+      </c>
+      <c r="L210">
         <f t="shared" si="6"/>
-        <v/>
+        <v>6750</v>
+      </c>
+      <c r="M210" t="s">
+        <v>16</v>
       </c>
       <c r="O210" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="211" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="P210" t="s">
+        <v>1359</v>
+      </c>
+      <c r="Q210" t="s">
+        <v>1805</v>
+      </c>
+    </row>
+    <row r="211" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A211" t="s">
         <v>225</v>
       </c>
+      <c r="B211" t="s">
+        <v>1804</v>
+      </c>
+      <c r="C211" t="s">
+        <v>1797</v>
+      </c>
+      <c r="D211" t="s">
+        <v>1798</v>
+      </c>
+      <c r="E211" t="s">
+        <v>1074</v>
+      </c>
       <c r="F211" t="s">
-        <v>1132</v>
+        <v>1806</v>
+      </c>
+      <c r="H211" t="s">
+        <v>1076</v>
+      </c>
+      <c r="I211" t="s">
+        <v>1807</v>
+      </c>
+      <c r="J211">
+        <v>5800</v>
       </c>
       <c r="K211">
-        <v>1</v>
-      </c>
-      <c r="L211" t="str">
+        <v>0.5</v>
+      </c>
+      <c r="L211">
         <f t="shared" si="6"/>
-        <v/>
+        <v>8700</v>
+      </c>
+      <c r="M211" t="s">
+        <v>16</v>
       </c>
       <c r="O211" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="212" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="P211" t="s">
+        <v>1359</v>
+      </c>
+      <c r="Q211" t="s">
+        <v>1804</v>
+      </c>
+    </row>
+    <row r="212" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A212" t="s">
         <v>226</v>
       </c>
+      <c r="B212" t="s">
+        <v>1808</v>
+      </c>
+      <c r="C212" t="s">
+        <v>1797</v>
+      </c>
+      <c r="D212" t="s">
+        <v>1810</v>
+      </c>
+      <c r="E212" t="s">
+        <v>1074</v>
+      </c>
       <c r="F212" t="s">
-        <v>1132</v>
+        <v>1811</v>
+      </c>
+      <c r="H212" t="s">
+        <v>1812</v>
+      </c>
+      <c r="I212" t="s">
+        <v>1813</v>
+      </c>
+      <c r="J212">
+        <v>185000</v>
       </c>
       <c r="K212">
-        <v>1</v>
-      </c>
-      <c r="L212" t="str">
+        <v>0.5</v>
+      </c>
+      <c r="L212">
         <f t="shared" si="6"/>
-        <v/>
+        <v>277500</v>
+      </c>
+      <c r="M212" t="s">
+        <v>16</v>
       </c>
       <c r="O212" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="213" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="P212" t="s">
+        <v>1359</v>
+      </c>
+      <c r="Q212" t="s">
+        <v>1808</v>
+      </c>
+    </row>
+    <row r="213" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A213" t="s">
         <v>227</v>
       </c>
+      <c r="B213" t="s">
+        <v>1809</v>
+      </c>
+      <c r="C213" t="s">
+        <v>1797</v>
+      </c>
+      <c r="D213" t="s">
+        <v>1810</v>
+      </c>
+      <c r="E213" t="s">
+        <v>1074</v>
+      </c>
       <c r="F213" t="s">
-        <v>1132</v>
+        <v>1815</v>
+      </c>
+      <c r="H213" t="s">
+        <v>1816</v>
+      </c>
+      <c r="I213" t="s">
+        <v>1814</v>
+      </c>
+      <c r="J213">
+        <v>4800</v>
       </c>
       <c r="K213">
-        <v>1</v>
-      </c>
-      <c r="L213" t="str">
+        <v>0.5</v>
+      </c>
+      <c r="L213">
         <f t="shared" si="6"/>
-        <v/>
+        <v>7200</v>
+      </c>
+      <c r="M213" t="s">
+        <v>16</v>
       </c>
       <c r="O213" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="214" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="P213" t="s">
+        <v>1359</v>
+      </c>
+      <c r="Q213" t="s">
+        <v>1809</v>
+      </c>
+    </row>
+    <row r="214" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A214" t="s">
         <v>228</v>
       </c>
+      <c r="B214" t="s">
+        <v>1817</v>
+      </c>
+      <c r="C214" t="s">
+        <v>1797</v>
+      </c>
+      <c r="D214" t="s">
+        <v>1810</v>
+      </c>
+      <c r="E214" t="s">
+        <v>1074</v>
+      </c>
       <c r="F214" t="s">
-        <v>1132</v>
+        <v>1818</v>
+      </c>
+      <c r="H214" t="s">
+        <v>1164</v>
+      </c>
+      <c r="I214" t="s">
+        <v>1819</v>
+      </c>
+      <c r="J214">
+        <v>4400</v>
       </c>
       <c r="K214">
-        <v>1</v>
-      </c>
-      <c r="L214" t="str">
+        <v>0.5</v>
+      </c>
+      <c r="L214">
         <f t="shared" si="6"/>
-        <v/>
+        <v>6600</v>
+      </c>
+      <c r="M214" t="s">
+        <v>16</v>
       </c>
       <c r="O214" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="215" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="P214" t="s">
+        <v>1359</v>
+      </c>
+      <c r="Q214" t="s">
+        <v>1817</v>
+      </c>
+    </row>
+    <row r="215" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A215" t="s">
         <v>229</v>
       </c>
+      <c r="B215" t="s">
+        <v>1821</v>
+      </c>
+      <c r="C215" t="s">
+        <v>1797</v>
+      </c>
+      <c r="D215" t="s">
+        <v>1810</v>
+      </c>
+      <c r="E215" t="s">
+        <v>1074</v>
+      </c>
       <c r="F215" t="s">
-        <v>1132</v>
+        <v>1820</v>
+      </c>
+      <c r="H215" t="s">
+        <v>1589</v>
+      </c>
+      <c r="I215" t="s">
+        <v>1822</v>
+      </c>
+      <c r="J215">
+        <v>26000</v>
       </c>
       <c r="K215">
-        <v>1</v>
-      </c>
-      <c r="L215" t="str">
+        <v>0.5</v>
+      </c>
+      <c r="L215">
         <f t="shared" si="6"/>
-        <v/>
+        <v>39000</v>
+      </c>
+      <c r="M215" t="s">
+        <v>16</v>
       </c>
       <c r="O215" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="216" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="P215" t="s">
+        <v>1359</v>
+      </c>
+      <c r="Q215" t="s">
+        <v>1821</v>
+      </c>
+    </row>
+    <row r="216" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A216" t="s">
         <v>230</v>
       </c>
+      <c r="B216" t="s">
+        <v>1823</v>
+      </c>
+      <c r="C216" t="s">
+        <v>1797</v>
+      </c>
+      <c r="D216" t="s">
+        <v>1810</v>
+      </c>
+      <c r="E216" t="s">
+        <v>1074</v>
+      </c>
       <c r="F216" t="s">
-        <v>1132</v>
+        <v>1824</v>
+      </c>
+      <c r="H216" t="s">
+        <v>1164</v>
+      </c>
+      <c r="I216" t="s">
+        <v>1825</v>
+      </c>
+      <c r="J216">
+        <v>7000</v>
       </c>
       <c r="K216">
-        <v>1</v>
-      </c>
-      <c r="L216" t="str">
+        <v>0.5</v>
+      </c>
+      <c r="L216">
         <f t="shared" si="6"/>
-        <v/>
+        <v>10500</v>
+      </c>
+      <c r="M216" t="s">
+        <v>16</v>
       </c>
       <c r="O216" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="217" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="P216" t="s">
+        <v>1359</v>
+      </c>
+      <c r="Q216" t="s">
+        <v>1823</v>
+      </c>
+    </row>
+    <row r="217" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A217" t="s">
         <v>231</v>
       </c>
+      <c r="B217" t="s">
+        <v>1826</v>
+      </c>
+      <c r="C217" t="s">
+        <v>1797</v>
+      </c>
+      <c r="D217" t="s">
+        <v>1827</v>
+      </c>
+      <c r="E217" t="s">
+        <v>1074</v>
+      </c>
       <c r="F217" t="s">
-        <v>1132</v>
+        <v>1828</v>
+      </c>
+      <c r="H217" t="s">
+        <v>1164</v>
+      </c>
+      <c r="I217" t="s">
+        <v>1829</v>
+      </c>
+      <c r="J217">
+        <v>12700</v>
       </c>
       <c r="K217">
-        <v>1</v>
-      </c>
-      <c r="L217" t="str">
+        <v>0.5</v>
+      </c>
+      <c r="L217">
         <f t="shared" si="6"/>
-        <v/>
+        <v>19050</v>
+      </c>
+      <c r="M217" t="s">
+        <v>16</v>
       </c>
       <c r="O217" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="218" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="P217" t="s">
+        <v>1359</v>
+      </c>
+      <c r="Q217" t="s">
+        <v>1826</v>
+      </c>
+    </row>
+    <row r="218" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A218" t="s">
         <v>232</v>
       </c>
+      <c r="B218" t="s">
+        <v>1830</v>
+      </c>
+      <c r="C218" t="s">
+        <v>1797</v>
+      </c>
+      <c r="D218" t="s">
+        <v>1827</v>
+      </c>
+      <c r="E218" t="s">
+        <v>1074</v>
+      </c>
       <c r="F218" t="s">
-        <v>1132</v>
+        <v>1831</v>
+      </c>
+      <c r="H218" t="s">
+        <v>1164</v>
+      </c>
+      <c r="I218" t="s">
+        <v>1832</v>
+      </c>
+      <c r="J218">
+        <v>9000</v>
       </c>
       <c r="K218">
-        <v>1</v>
-      </c>
-      <c r="L218" t="str">
+        <v>0.5</v>
+      </c>
+      <c r="L218">
         <f t="shared" si="6"/>
-        <v/>
+        <v>13500</v>
+      </c>
+      <c r="M218" t="s">
+        <v>16</v>
       </c>
       <c r="O218" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="219" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="P218" t="s">
+        <v>1359</v>
+      </c>
+      <c r="Q218" t="s">
+        <v>1830</v>
+      </c>
+    </row>
+    <row r="219" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A219" t="s">
         <v>233</v>
       </c>
+      <c r="B219" t="s">
+        <v>1833</v>
+      </c>
+      <c r="C219" t="s">
+        <v>1797</v>
+      </c>
+      <c r="D219" t="s">
+        <v>1827</v>
+      </c>
+      <c r="E219" t="s">
+        <v>1074</v>
+      </c>
       <c r="F219" t="s">
-        <v>1132</v>
+        <v>1834</v>
+      </c>
+      <c r="H219" t="s">
+        <v>1164</v>
+      </c>
+      <c r="I219" t="s">
+        <v>1835</v>
+      </c>
+      <c r="J219">
+        <v>4500</v>
       </c>
       <c r="K219">
-        <v>1</v>
-      </c>
-      <c r="L219" t="str">
+        <v>0.5</v>
+      </c>
+      <c r="L219">
         <f t="shared" si="6"/>
-        <v/>
+        <v>6750</v>
+      </c>
+      <c r="M219" t="s">
+        <v>16</v>
       </c>
       <c r="O219" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="220" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="P219" t="s">
+        <v>1359</v>
+      </c>
+      <c r="Q219" t="s">
+        <v>1833</v>
+      </c>
+    </row>
+    <row r="220" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A220" t="s">
         <v>234</v>
       </c>
+      <c r="B220" t="s">
+        <v>1836</v>
+      </c>
+      <c r="C220" t="s">
+        <v>1797</v>
+      </c>
+      <c r="D220" t="s">
+        <v>1827</v>
+      </c>
+      <c r="E220" t="s">
+        <v>1074</v>
+      </c>
       <c r="F220" t="s">
-        <v>1132</v>
+        <v>1837</v>
+      </c>
+      <c r="H220" t="s">
+        <v>1164</v>
+      </c>
+      <c r="I220" t="s">
+        <v>1838</v>
+      </c>
+      <c r="J220">
+        <v>19000</v>
       </c>
       <c r="K220">
-        <v>1</v>
-      </c>
-      <c r="L220" t="str">
+        <v>0.5</v>
+      </c>
+      <c r="L220">
         <f t="shared" si="6"/>
-        <v/>
+        <v>28500</v>
+      </c>
+      <c r="M220" t="s">
+        <v>16</v>
       </c>
       <c r="O220" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="221" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="P220" t="s">
+        <v>1359</v>
+      </c>
+      <c r="Q220" t="s">
+        <v>1836</v>
+      </c>
+    </row>
+    <row r="221" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A221" t="s">
         <v>235</v>
       </c>
+      <c r="B221" t="s">
+        <v>1839</v>
+      </c>
+      <c r="C221" t="s">
+        <v>1797</v>
+      </c>
+      <c r="D221" t="s">
+        <v>1797</v>
+      </c>
+      <c r="E221" t="s">
+        <v>1074</v>
+      </c>
       <c r="F221" t="s">
-        <v>1132</v>
+        <v>1841</v>
+      </c>
+      <c r="H221" t="s">
+        <v>1164</v>
+      </c>
+      <c r="I221" t="s">
+        <v>1840</v>
+      </c>
+      <c r="J221">
+        <v>1000</v>
       </c>
       <c r="K221">
         <v>1</v>
       </c>
-      <c r="L221" t="str">
+      <c r="L221">
         <f t="shared" si="6"/>
-        <v/>
+        <v>2000</v>
+      </c>
+      <c r="M221" t="s">
+        <v>16</v>
       </c>
       <c r="O221" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="222" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="P221" t="s">
+        <v>1359</v>
+      </c>
+      <c r="Q221" t="s">
+        <v>1839</v>
+      </c>
+    </row>
+    <row r="222" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A222" t="s">
         <v>236</v>
       </c>
+      <c r="B222" t="s">
+        <v>1844</v>
+      </c>
+      <c r="C222" t="s">
+        <v>1797</v>
+      </c>
+      <c r="D222" t="s">
+        <v>1797</v>
+      </c>
+      <c r="E222" t="s">
+        <v>1074</v>
+      </c>
       <c r="F222" t="s">
-        <v>1132</v>
+        <v>1842</v>
+      </c>
+      <c r="H222" t="s">
+        <v>1164</v>
+      </c>
+      <c r="I222" t="s">
+        <v>1843</v>
+      </c>
+      <c r="J222">
+        <v>14000</v>
       </c>
       <c r="K222">
-        <v>1</v>
-      </c>
-      <c r="L222" t="str">
+        <v>0.5</v>
+      </c>
+      <c r="L222">
         <f t="shared" si="6"/>
-        <v/>
+        <v>21000</v>
+      </c>
+      <c r="M222" t="s">
+        <v>16</v>
       </c>
       <c r="O222" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="223" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="P222" t="s">
+        <v>1359</v>
+      </c>
+      <c r="Q222" t="s">
+        <v>1844</v>
+      </c>
+    </row>
+    <row r="223" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A223" t="s">
         <v>237</v>
       </c>
+      <c r="B223" t="s">
+        <v>1845</v>
+      </c>
+      <c r="C223" t="s">
+        <v>1797</v>
+      </c>
+      <c r="D223" t="s">
+        <v>1797</v>
+      </c>
+      <c r="E223" t="s">
+        <v>1074</v>
+      </c>
       <c r="F223" t="s">
-        <v>1132</v>
+        <v>1846</v>
+      </c>
+      <c r="H223" t="s">
+        <v>1164</v>
+      </c>
+      <c r="I223" t="s">
+        <v>1847</v>
+      </c>
+      <c r="J223">
+        <v>11000</v>
       </c>
       <c r="K223">
-        <v>1</v>
-      </c>
-      <c r="L223" t="str">
+        <v>0.5</v>
+      </c>
+      <c r="L223">
         <f t="shared" si="6"/>
-        <v/>
+        <v>16500</v>
+      </c>
+      <c r="M223" t="s">
+        <v>16</v>
       </c>
       <c r="O223" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="224" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="P223" t="s">
+        <v>1359</v>
+      </c>
+      <c r="Q223" t="s">
+        <v>1845</v>
+      </c>
+    </row>
+    <row r="224" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A224" t="s">
         <v>238</v>
       </c>
+      <c r="B224" t="s">
+        <v>1848</v>
+      </c>
+      <c r="C224" t="s">
+        <v>1797</v>
+      </c>
+      <c r="D224" t="s">
+        <v>1797</v>
+      </c>
+      <c r="E224" t="s">
+        <v>1074</v>
+      </c>
       <c r="F224" t="s">
-        <v>1132</v>
+        <v>1849</v>
+      </c>
+      <c r="H224" t="s">
+        <v>1164</v>
+      </c>
+      <c r="I224" t="s">
+        <v>1850</v>
+      </c>
+      <c r="J224">
+        <v>2000</v>
       </c>
       <c r="K224">
-        <v>1</v>
-      </c>
-      <c r="L224" t="str">
+        <v>0.5</v>
+      </c>
+      <c r="L224">
         <f t="shared" si="6"/>
-        <v/>
+        <v>3000</v>
+      </c>
+      <c r="M224" t="s">
+        <v>16</v>
       </c>
       <c r="O224" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="225" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="P224" t="s">
+        <v>1359</v>
+      </c>
+      <c r="Q224" t="s">
+        <v>1848</v>
+      </c>
+    </row>
+    <row r="225" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A225" t="s">
         <v>239</v>
       </c>
+      <c r="B225" t="s">
+        <v>1851</v>
+      </c>
+      <c r="C225" t="s">
+        <v>1797</v>
+      </c>
+      <c r="D225" t="s">
+        <v>1797</v>
+      </c>
+      <c r="E225" t="s">
+        <v>1074</v>
+      </c>
       <c r="F225" t="s">
-        <v>1132</v>
+        <v>1852</v>
+      </c>
+      <c r="H225" t="s">
+        <v>1164</v>
+      </c>
+      <c r="I225" t="s">
+        <v>1853</v>
+      </c>
+      <c r="J225">
+        <v>2400</v>
       </c>
       <c r="K225">
-        <v>1</v>
-      </c>
-      <c r="L225" t="str">
+        <v>0.5</v>
+      </c>
+      <c r="L225">
         <f t="shared" si="6"/>
-        <v/>
+        <v>3600</v>
+      </c>
+      <c r="M225" t="s">
+        <v>16</v>
       </c>
       <c r="O225" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="226" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="P225" t="s">
+        <v>1359</v>
+      </c>
+      <c r="Q225" t="s">
+        <v>1851</v>
+      </c>
+    </row>
+    <row r="226" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A226" t="s">
         <v>240</v>
       </c>
+      <c r="B226" t="s">
+        <v>1854</v>
+      </c>
+      <c r="C226" t="s">
+        <v>1046</v>
+      </c>
+      <c r="D226" t="s">
+        <v>1863</v>
+      </c>
+      <c r="E226" t="s">
+        <v>1634</v>
+      </c>
       <c r="F226" t="s">
-        <v>1132</v>
+        <v>1874</v>
+      </c>
+      <c r="H226" t="s">
+        <v>1164</v>
+      </c>
+      <c r="I226" t="s">
+        <v>1864</v>
+      </c>
+      <c r="J226">
+        <v>1050</v>
       </c>
       <c r="K226">
         <v>1</v>
       </c>
-      <c r="L226" t="str">
+      <c r="L226">
         <f t="shared" si="6"/>
-        <v/>
+        <v>2100</v>
+      </c>
+      <c r="M226" t="s">
+        <v>16</v>
       </c>
       <c r="O226" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="227" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="P226" t="s">
+        <v>1359</v>
+      </c>
+      <c r="Q226" t="s">
+        <v>1854</v>
+      </c>
+    </row>
+    <row r="227" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A227" t="s">
         <v>241</v>
       </c>
+      <c r="B227" t="s">
+        <v>1855</v>
+      </c>
+      <c r="C227" t="s">
+        <v>1046</v>
+      </c>
+      <c r="D227" t="s">
+        <v>1863</v>
+      </c>
+      <c r="E227" t="s">
+        <v>1634</v>
+      </c>
       <c r="F227" t="s">
-        <v>1132</v>
+        <v>1873</v>
+      </c>
+      <c r="H227" t="s">
+        <v>1164</v>
+      </c>
+      <c r="I227" t="s">
+        <v>1865</v>
+      </c>
+      <c r="J227">
+        <v>2500</v>
       </c>
       <c r="K227">
         <v>1</v>
       </c>
-      <c r="L227" t="str">
+      <c r="L227">
         <f t="shared" si="6"/>
-        <v/>
+        <v>5000</v>
+      </c>
+      <c r="M227" t="s">
+        <v>16</v>
       </c>
       <c r="O227" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="228" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="P227" t="s">
+        <v>1359</v>
+      </c>
+      <c r="Q227" t="s">
+        <v>1855</v>
+      </c>
+    </row>
+    <row r="228" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A228" t="s">
         <v>242</v>
       </c>
+      <c r="B228" t="s">
+        <v>1856</v>
+      </c>
+      <c r="C228" t="s">
+        <v>1046</v>
+      </c>
+      <c r="D228" t="s">
+        <v>1875</v>
+      </c>
+      <c r="E228" t="s">
+        <v>1634</v>
+      </c>
       <c r="F228" t="s">
-        <v>1132</v>
+        <v>1876</v>
+      </c>
+      <c r="H228" t="s">
+        <v>1164</v>
+      </c>
+      <c r="I228" t="s">
+        <v>1866</v>
+      </c>
+      <c r="J228">
+        <v>1250</v>
       </c>
       <c r="K228">
         <v>1</v>
       </c>
-      <c r="L228" t="str">
+      <c r="L228">
         <f t="shared" si="6"/>
-        <v/>
+        <v>2500</v>
+      </c>
+      <c r="M228" t="s">
+        <v>16</v>
       </c>
       <c r="O228" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="229" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="P228" t="s">
+        <v>1359</v>
+      </c>
+      <c r="Q228" t="s">
+        <v>1856</v>
+      </c>
+    </row>
+    <row r="229" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A229" t="s">
         <v>243</v>
       </c>
+      <c r="B229" t="s">
+        <v>1857</v>
+      </c>
+      <c r="C229" t="s">
+        <v>1046</v>
+      </c>
+      <c r="D229" t="s">
+        <v>1875</v>
+      </c>
+      <c r="E229" t="s">
+        <v>1634</v>
+      </c>
       <c r="F229" t="s">
-        <v>1132</v>
+        <v>1877</v>
+      </c>
+      <c r="H229" t="s">
+        <v>1164</v>
+      </c>
+      <c r="I229" t="s">
+        <v>1867</v>
+      </c>
+      <c r="J229">
+        <v>1200</v>
       </c>
       <c r="K229">
         <v>1</v>
       </c>
-      <c r="L229" t="str">
+      <c r="L229">
         <f t="shared" si="6"/>
-        <v/>
+        <v>2400</v>
+      </c>
+      <c r="M229" t="s">
+        <v>16</v>
       </c>
       <c r="O229" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="230" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="P229" t="s">
+        <v>1359</v>
+      </c>
+      <c r="Q229" t="s">
+        <v>1857</v>
+      </c>
+    </row>
+    <row r="230" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A230" t="s">
         <v>244</v>
       </c>
+      <c r="B230" t="s">
+        <v>1858</v>
+      </c>
+      <c r="C230" t="s">
+        <v>1046</v>
+      </c>
+      <c r="D230" t="s">
+        <v>1875</v>
+      </c>
+      <c r="E230" t="s">
+        <v>1634</v>
+      </c>
       <c r="F230" t="s">
-        <v>1132</v>
+        <v>1878</v>
+      </c>
+      <c r="H230" t="s">
+        <v>1164</v>
+      </c>
+      <c r="I230" t="s">
+        <v>1868</v>
+      </c>
+      <c r="J230">
+        <v>1500</v>
       </c>
       <c r="K230">
         <v>1</v>
       </c>
-      <c r="L230" t="str">
+      <c r="L230">
         <f t="shared" si="6"/>
-        <v/>
+        <v>3000</v>
+      </c>
+      <c r="M230" t="s">
+        <v>16</v>
       </c>
       <c r="O230" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="231" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="P230" t="s">
+        <v>1359</v>
+      </c>
+      <c r="Q230" t="s">
+        <v>1858</v>
+      </c>
+    </row>
+    <row r="231" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A231" t="s">
         <v>245</v>
       </c>
+      <c r="B231" t="s">
+        <v>1859</v>
+      </c>
+      <c r="C231" t="s">
+        <v>1046</v>
+      </c>
+      <c r="D231" t="s">
+        <v>1879</v>
+      </c>
+      <c r="E231" t="s">
+        <v>1634</v>
+      </c>
       <c r="F231" t="s">
-        <v>1132</v>
+        <v>1880</v>
+      </c>
+      <c r="H231" t="s">
+        <v>1164</v>
+      </c>
+      <c r="I231" t="s">
+        <v>1869</v>
+      </c>
+      <c r="J231">
+        <v>2800</v>
       </c>
       <c r="K231">
         <v>1</v>
       </c>
-      <c r="L231" t="str">
+      <c r="L231">
         <f t="shared" si="6"/>
-        <v/>
+        <v>5600</v>
+      </c>
+      <c r="M231" t="s">
+        <v>16</v>
       </c>
       <c r="O231" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="232" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="P231" t="s">
+        <v>1359</v>
+      </c>
+      <c r="Q231" t="s">
+        <v>1859</v>
+      </c>
+    </row>
+    <row r="232" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A232" t="s">
         <v>246</v>
       </c>
+      <c r="B232" t="s">
+        <v>1860</v>
+      </c>
+      <c r="C232" t="s">
+        <v>1046</v>
+      </c>
+      <c r="D232" t="s">
+        <v>1879</v>
+      </c>
+      <c r="E232" t="s">
+        <v>1882</v>
+      </c>
       <c r="F232" t="s">
-        <v>1132</v>
+        <v>1881</v>
+      </c>
+      <c r="H232" t="s">
+        <v>1164</v>
+      </c>
+      <c r="I232" t="s">
+        <v>1870</v>
+      </c>
+      <c r="J232">
+        <v>2500</v>
       </c>
       <c r="K232">
         <v>1</v>
       </c>
-      <c r="L232" t="str">
+      <c r="L232">
         <f t="shared" si="6"/>
-        <v/>
+        <v>5000</v>
+      </c>
+      <c r="M232" t="s">
+        <v>16</v>
       </c>
       <c r="O232" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="233" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="P232" t="s">
+        <v>1359</v>
+      </c>
+      <c r="Q232" t="s">
+        <v>1860</v>
+      </c>
+    </row>
+    <row r="233" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A233" t="s">
         <v>247</v>
       </c>
+      <c r="B233" t="s">
+        <v>1861</v>
+      </c>
+      <c r="C233" t="s">
+        <v>1046</v>
+      </c>
+      <c r="D233" t="s">
+        <v>1046</v>
+      </c>
+      <c r="E233" t="s">
+        <v>1074</v>
+      </c>
       <c r="F233" t="s">
-        <v>1132</v>
+        <v>1883</v>
+      </c>
+      <c r="H233" t="s">
+        <v>1164</v>
+      </c>
+      <c r="I233" t="s">
+        <v>1871</v>
+      </c>
+      <c r="J233">
+        <v>500</v>
       </c>
       <c r="K233">
         <v>1</v>
       </c>
-      <c r="L233" t="str">
+      <c r="L233">
         <f t="shared" si="6"/>
-        <v/>
+        <v>1000</v>
+      </c>
+      <c r="M233" t="s">
+        <v>16</v>
       </c>
       <c r="O233" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="234" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="P233" t="s">
+        <v>1359</v>
+      </c>
+      <c r="Q233" t="s">
+        <v>1861</v>
+      </c>
+    </row>
+    <row r="234" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A234" t="s">
         <v>248</v>
       </c>
+      <c r="B234" t="s">
+        <v>1862</v>
+      </c>
+      <c r="C234" t="s">
+        <v>1046</v>
+      </c>
+      <c r="D234" t="s">
+        <v>1720</v>
+      </c>
+      <c r="E234" t="s">
+        <v>1885</v>
+      </c>
       <c r="F234" t="s">
-        <v>1132</v>
+        <v>1884</v>
+      </c>
+      <c r="H234" t="s">
+        <v>1164</v>
+      </c>
+      <c r="I234" t="s">
+        <v>1872</v>
+      </c>
+      <c r="J234">
+        <v>5000</v>
       </c>
       <c r="K234">
-        <v>1</v>
-      </c>
-      <c r="L234" t="str">
+        <v>0.5</v>
+      </c>
+      <c r="L234">
         <f t="shared" si="6"/>
-        <v/>
+        <v>7500</v>
+      </c>
+      <c r="M234" t="s">
+        <v>16</v>
       </c>
       <c r="O234" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="235" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="P234" t="s">
+        <v>1359</v>
+      </c>
+      <c r="Q234" t="s">
+        <v>1862</v>
+      </c>
+    </row>
+    <row r="235" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A235" t="s">
         <v>249</v>
       </c>
@@ -14021,7 +17513,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="236" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="236" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A236" t="s">
         <v>250</v>
       </c>
@@ -14039,7 +17531,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="237" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="237" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A237" t="s">
         <v>251</v>
       </c>
@@ -14057,7 +17549,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="238" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="238" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A238" t="s">
         <v>252</v>
       </c>
@@ -14075,7 +17567,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="239" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="239" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A239" t="s">
         <v>253</v>
       </c>
@@ -14093,7 +17585,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="240" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="240" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A240" t="s">
         <v>254</v>
       </c>

--- a/public/Plantilla_Quimica_Bethel_2.0.xlsx
+++ b/public/Plantilla_Quimica_Bethel_2.0.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\facun\Desktop\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BE20CAF8-9A1E-45E4-BC13-64511238C9FC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{570E5A8E-AEE0-4AE6-A1F9-7CC7B3E1D0EA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="19440" windowHeight="14880" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -12479,7 +12479,7 @@
         <v>16</v>
       </c>
       <c r="P131" t="s">
-        <v>1358</v>
+        <v>1359</v>
       </c>
       <c r="Q131" t="s">
         <v>1520</v>
@@ -12527,7 +12527,7 @@
         <v>16</v>
       </c>
       <c r="P132" t="s">
-        <v>1358</v>
+        <v>1359</v>
       </c>
       <c r="Q132" t="s">
         <v>1521</v>
@@ -12575,7 +12575,7 @@
         <v>16</v>
       </c>
       <c r="P133" t="s">
-        <v>1358</v>
+        <v>1359</v>
       </c>
       <c r="Q133" t="s">
         <v>1522</v>
@@ -12623,7 +12623,7 @@
         <v>16</v>
       </c>
       <c r="P134" t="s">
-        <v>1359</v>
+        <v>1358</v>
       </c>
       <c r="Q134" t="s">
         <v>1538</v>
@@ -12671,7 +12671,7 @@
         <v>16</v>
       </c>
       <c r="P135" t="s">
-        <v>1359</v>
+        <v>1358</v>
       </c>
       <c r="Q135" t="s">
         <v>1538</v>
@@ -12719,7 +12719,7 @@
         <v>16</v>
       </c>
       <c r="P136" t="s">
-        <v>1359</v>
+        <v>1358</v>
       </c>
       <c r="Q136" t="s">
         <v>1546</v>
@@ -12767,7 +12767,7 @@
         <v>16</v>
       </c>
       <c r="P137" t="s">
-        <v>1359</v>
+        <v>1358</v>
       </c>
       <c r="Q137" t="s">
         <v>1547</v>
@@ -12815,7 +12815,7 @@
         <v>16</v>
       </c>
       <c r="P138" t="s">
-        <v>1359</v>
+        <v>1358</v>
       </c>
       <c r="Q138" t="s">
         <v>1552</v>
@@ -12863,7 +12863,7 @@
         <v>16</v>
       </c>
       <c r="P139" t="s">
-        <v>1359</v>
+        <v>1358</v>
       </c>
       <c r="Q139" t="s">
         <v>1555</v>
@@ -12911,7 +12911,7 @@
         <v>16</v>
       </c>
       <c r="P140" t="s">
-        <v>1359</v>
+        <v>1358</v>
       </c>
       <c r="Q140" t="s">
         <v>1557</v>
@@ -12959,7 +12959,7 @@
         <v>16</v>
       </c>
       <c r="P141" t="s">
-        <v>1359</v>
+        <v>1358</v>
       </c>
       <c r="Q141" t="s">
         <v>1560</v>
@@ -13010,7 +13010,7 @@
         <v>16</v>
       </c>
       <c r="P142" t="s">
-        <v>1359</v>
+        <v>1358</v>
       </c>
       <c r="Q142" t="s">
         <v>1563</v>
@@ -13058,7 +13058,7 @@
         <v>16</v>
       </c>
       <c r="P143" t="s">
-        <v>1359</v>
+        <v>1358</v>
       </c>
       <c r="Q143" t="s">
         <v>1565</v>
@@ -13109,7 +13109,7 @@
         <v>16</v>
       </c>
       <c r="P144" t="s">
-        <v>1359</v>
+        <v>1358</v>
       </c>
       <c r="Q144" t="s">
         <v>1569</v>
@@ -13160,7 +13160,7 @@
         <v>16</v>
       </c>
       <c r="P145" t="s">
-        <v>1359</v>
+        <v>1358</v>
       </c>
       <c r="Q145" t="s">
         <v>1570</v>
@@ -13211,7 +13211,7 @@
         <v>16</v>
       </c>
       <c r="P146" t="s">
-        <v>1359</v>
+        <v>1358</v>
       </c>
       <c r="Q146" t="s">
         <v>1575</v>
@@ -13364,7 +13364,7 @@
         <v>16</v>
       </c>
       <c r="P149" t="s">
-        <v>1359</v>
+        <v>1358</v>
       </c>
       <c r="Q149" t="s">
         <v>1585</v>
@@ -13517,7 +13517,7 @@
         <v>16</v>
       </c>
       <c r="P152" t="s">
-        <v>1359</v>
+        <v>1358</v>
       </c>
       <c r="Q152" t="s">
         <v>1593</v>
@@ -13670,7 +13670,7 @@
         <v>16</v>
       </c>
       <c r="P155" t="s">
-        <v>1359</v>
+        <v>1358</v>
       </c>
       <c r="Q155" t="s">
         <v>1600</v>
@@ -15077,7 +15077,7 @@
         <v>16</v>
       </c>
       <c r="P184" t="s">
-        <v>1359</v>
+        <v>1358</v>
       </c>
       <c r="Q184" t="s">
         <v>1693</v>

--- a/public/Plantilla_Quimica_Bethel_2.0.xlsx
+++ b/public/Plantilla_Quimica_Bethel_2.0.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\facun\Desktop\QUIMICA - V3\public\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\facun\Desktop\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="11_F8449C350852DB6FABFFBED53F9D6A548010FA40" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0A591419-D7BB-4E3E-99E9-3E64D7E0D527}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="16220" windowHeight="12220" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="7910" yWindow="0" windowWidth="8180" windowHeight="12090" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="PRODUCTOS" sheetId="1" r:id="rId1"/>
@@ -24,12 +24,25 @@
     <sheet name="TARIFAS ENVÍO" sheetId="9" r:id="rId9"/>
     <sheet name="CONTROL PRECIOS" sheetId="10" r:id="rId10"/>
   </sheets>
-  <calcPr calcId="181029"/>
+  <calcPr calcId="191029"/>
+  <extLst>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
+  </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7544" uniqueCount="2202">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7570" uniqueCount="2212">
   <si>
     <t>ID</t>
   </si>
@@ -6636,6 +6649,36 @@
   </si>
   <si>
     <t>RJR015-REPASADOR</t>
+  </si>
+  <si>
+    <t>CIF001</t>
+  </si>
+  <si>
+    <t>CIF</t>
+  </si>
+  <si>
+    <t>KING</t>
+  </si>
+  <si>
+    <t>Limpiador Cremoso CIF x 5 litros</t>
+  </si>
+  <si>
+    <t>CIF001.jpg</t>
+  </si>
+  <si>
+    <t>CIF limpiador cremoso</t>
+  </si>
+  <si>
+    <t>CIF002</t>
+  </si>
+  <si>
+    <t>Limpiador Cremoso CIF x 1 litros</t>
+  </si>
+  <si>
+    <t>CIF002.jpg</t>
+  </si>
+  <si>
+    <t>CIF-CREMOSO</t>
   </si>
 </sst>
 </file>
@@ -27314,7 +27357,7 @@
         <v>0.39984797202797201</v>
       </c>
     </row>
-    <row r="225" spans="1:27" x14ac:dyDescent="0.35">
+    <row r="225" spans="1:29" x14ac:dyDescent="0.35">
       <c r="A225" s="10" t="s">
         <v>1297</v>
       </c>
@@ -27400,7 +27443,7 @@
         <v>0.40008562499999994</v>
       </c>
     </row>
-    <row r="226" spans="1:27" x14ac:dyDescent="0.35">
+    <row r="226" spans="1:29" x14ac:dyDescent="0.35">
       <c r="A226" s="10" t="s">
         <v>1302</v>
       </c>
@@ -27486,7 +27529,7 @@
         <v>0.39968739659367397</v>
       </c>
     </row>
-    <row r="227" spans="1:27" x14ac:dyDescent="0.35">
+    <row r="227" spans="1:29" x14ac:dyDescent="0.35">
       <c r="A227" s="10" t="s">
         <v>1309</v>
       </c>
@@ -27572,7 +27615,7 @@
         <v>0.40013735159817349</v>
       </c>
     </row>
-    <row r="228" spans="1:27" x14ac:dyDescent="0.35">
+    <row r="228" spans="1:29" x14ac:dyDescent="0.35">
       <c r="A228" s="10" t="s">
         <v>1314</v>
       </c>
@@ -27658,7 +27701,7 @@
         <v>0.39987056179775282</v>
       </c>
     </row>
-    <row r="229" spans="1:27" x14ac:dyDescent="0.35">
+    <row r="229" spans="1:29" x14ac:dyDescent="0.35">
       <c r="A229" s="10" t="s">
         <v>1321</v>
       </c>
@@ -27744,7 +27787,7 @@
         <v>0.40050306636155608</v>
       </c>
     </row>
-    <row r="230" spans="1:27" x14ac:dyDescent="0.35">
+    <row r="230" spans="1:29" x14ac:dyDescent="0.35">
       <c r="A230" s="10" t="s">
         <v>1326</v>
       </c>
@@ -27830,7 +27873,7 @@
         <v>0.39945757700205342</v>
       </c>
     </row>
-    <row r="231" spans="1:27" x14ac:dyDescent="0.35">
+    <row r="231" spans="1:29" x14ac:dyDescent="0.35">
       <c r="A231" s="10" t="s">
         <v>1331</v>
       </c>
@@ -27916,7 +27959,7 @@
         <v>0.40027762711864406</v>
       </c>
     </row>
-    <row r="232" spans="1:27" x14ac:dyDescent="0.35">
+    <row r="232" spans="1:29" x14ac:dyDescent="0.35">
       <c r="A232" s="10" t="s">
         <v>1338</v>
       </c>
@@ -28002,7 +28045,7 @@
         <v>0.40013735159817349</v>
       </c>
     </row>
-    <row r="233" spans="1:27" x14ac:dyDescent="0.35">
+    <row r="233" spans="1:29" x14ac:dyDescent="0.35">
       <c r="A233" s="10" t="s">
         <v>1344</v>
       </c>
@@ -28088,7 +28131,7 @@
         <v>0.39991119496855343</v>
       </c>
     </row>
-    <row r="234" spans="1:27" x14ac:dyDescent="0.35">
+    <row r="234" spans="1:29" x14ac:dyDescent="0.35">
       <c r="A234" s="10" t="s">
         <v>1351</v>
       </c>
@@ -28174,23 +28217,59 @@
         <v>0.39981074074074074</v>
       </c>
     </row>
-    <row r="235" spans="1:27" x14ac:dyDescent="0.35">
+    <row r="235" spans="1:29" x14ac:dyDescent="0.35">
       <c r="A235" s="10" t="s">
         <v>1357</v>
       </c>
+      <c r="B235" t="s">
+        <v>2202</v>
+      </c>
+      <c r="C235" t="s">
+        <v>31</v>
+      </c>
+      <c r="D235" t="s">
+        <v>2203</v>
+      </c>
+      <c r="E235" t="s">
+        <v>2204</v>
+      </c>
       <c r="F235" t="s">
-        <v>1358</v>
+        <v>2205</v>
+      </c>
+      <c r="H235" t="s">
+        <v>136</v>
+      </c>
+      <c r="I235" t="s">
+        <v>2206</v>
+      </c>
+      <c r="J235">
+        <v>8000</v>
       </c>
       <c r="K235">
-        <v>1</v>
-      </c>
-      <c r="L235" t="str">
+        <v>0.5</v>
+      </c>
+      <c r="L235">
         <f t="shared" si="12"/>
-        <v/>
+        <v>12000</v>
+      </c>
+      <c r="M235" t="s">
+        <v>38</v>
       </c>
       <c r="O235" t="s">
         <v>38</v>
       </c>
+      <c r="P235" t="s">
+        <v>39</v>
+      </c>
+      <c r="Q235" t="s">
+        <v>2202</v>
+      </c>
+      <c r="R235" t="s">
+        <v>2207</v>
+      </c>
+      <c r="S235" t="s">
+        <v>2207</v>
+      </c>
       <c r="T235" s="2">
         <f>'SUPUESTOS PRECIOS'!$B$9</f>
         <v>0</v>
@@ -28211,36 +28290,78 @@
         <f>'SUPUESTOS PRECIOS'!$B$2</f>
         <v>0.4</v>
       </c>
-      <c r="Y235" s="3" t="str">
+      <c r="Y235" s="3">
         <f t="shared" si="13"/>
-        <v/>
-      </c>
-      <c r="Z235" s="3" t="str">
+        <v>15890</v>
+      </c>
+      <c r="Z235" s="3">
         <f t="shared" si="14"/>
-        <v/>
-      </c>
-      <c r="AA235" s="11" t="str">
+        <v>6358.6848</v>
+      </c>
+      <c r="AA235" s="11">
         <f t="shared" si="15"/>
-        <v/>
-      </c>
-    </row>
-    <row r="236" spans="1:27" x14ac:dyDescent="0.35">
+        <v>0.40016896161107612</v>
+      </c>
+      <c r="AB235" t="s">
+        <v>2211</v>
+      </c>
+      <c r="AC235" t="s">
+        <v>836</v>
+      </c>
+    </row>
+    <row r="236" spans="1:29" x14ac:dyDescent="0.35">
       <c r="A236" s="10" t="s">
         <v>1359</v>
       </c>
+      <c r="B236" t="s">
+        <v>2208</v>
+      </c>
+      <c r="C236" t="s">
+        <v>31</v>
+      </c>
+      <c r="D236" t="s">
+        <v>2203</v>
+      </c>
+      <c r="E236" t="s">
+        <v>2204</v>
+      </c>
       <c r="F236" t="s">
-        <v>1358</v>
+        <v>2209</v>
+      </c>
+      <c r="H236" t="s">
+        <v>136</v>
+      </c>
+      <c r="I236" t="s">
+        <v>2210</v>
+      </c>
+      <c r="J236">
+        <v>2600</v>
       </c>
       <c r="K236">
-        <v>1</v>
-      </c>
-      <c r="L236" t="str">
+        <v>0.5</v>
+      </c>
+      <c r="L236">
         <f t="shared" si="12"/>
-        <v/>
+        <v>3900</v>
+      </c>
+      <c r="M236" t="s">
+        <v>38</v>
       </c>
       <c r="O236" t="s">
         <v>38</v>
       </c>
+      <c r="P236" t="s">
+        <v>39</v>
+      </c>
+      <c r="Q236" t="s">
+        <v>2208</v>
+      </c>
+      <c r="R236" t="s">
+        <v>2207</v>
+      </c>
+      <c r="S236" t="s">
+        <v>2207</v>
+      </c>
       <c r="T236" s="2">
         <f>'SUPUESTOS PRECIOS'!$B$9</f>
         <v>0</v>
@@ -28261,20 +28382,26 @@
         <f>'SUPUESTOS PRECIOS'!$B$2</f>
         <v>0.4</v>
       </c>
-      <c r="Y236" s="3" t="str">
+      <c r="Y236" s="3">
         <f t="shared" si="13"/>
-        <v/>
-      </c>
-      <c r="Z236" s="3" t="str">
+        <v>6740</v>
+      </c>
+      <c r="Z236" s="3">
         <f t="shared" si="14"/>
-        <v/>
-      </c>
-      <c r="AA236" s="11" t="str">
+        <v>2697.2568000000001</v>
+      </c>
+      <c r="AA236" s="11">
         <f t="shared" si="15"/>
-        <v/>
-      </c>
-    </row>
-    <row r="237" spans="1:27" x14ac:dyDescent="0.35">
+        <v>0.40018646884273001</v>
+      </c>
+      <c r="AB236" t="s">
+        <v>2211</v>
+      </c>
+      <c r="AC236" t="s">
+        <v>842</v>
+      </c>
+    </row>
+    <row r="237" spans="1:29" x14ac:dyDescent="0.35">
       <c r="A237" s="10" t="s">
         <v>1360</v>
       </c>
@@ -28324,7 +28451,7 @@
         <v/>
       </c>
     </row>
-    <row r="238" spans="1:27" x14ac:dyDescent="0.35">
+    <row r="238" spans="1:29" x14ac:dyDescent="0.35">
       <c r="A238" s="10" t="s">
         <v>1361</v>
       </c>
@@ -28374,7 +28501,7 @@
         <v/>
       </c>
     </row>
-    <row r="239" spans="1:27" x14ac:dyDescent="0.35">
+    <row r="239" spans="1:29" x14ac:dyDescent="0.35">
       <c r="A239" s="10" t="s">
         <v>1362</v>
       </c>
@@ -28424,7 +28551,7 @@
         <v/>
       </c>
     </row>
-    <row r="240" spans="1:27" x14ac:dyDescent="0.35">
+    <row r="240" spans="1:29" x14ac:dyDescent="0.35">
       <c r="A240" s="10" t="s">
         <v>1363</v>
       </c>
@@ -66585,7 +66712,7 @@
       </c>
       <c r="B4" s="18">
         <f>COUNTIFS(PRODUCTOS!$J$2:$J$1001,"&gt;0",PRODUCTOS!$Y$2:$Y$1001,"&gt;0")</f>
-        <v>232</v>
+        <v>234</v>
       </c>
     </row>
     <row r="5" spans="1:4" x14ac:dyDescent="0.35">
@@ -66594,7 +66721,7 @@
       </c>
       <c r="B5" s="18">
         <f>COUNTIFS(PRODUCTOS!$B$2:$B$1001,"&lt;&gt;",PRODUCTOS!$J$2:$J$1001,"&gt;0")</f>
-        <v>232</v>
+        <v>234</v>
       </c>
     </row>
     <row r="6" spans="1:4" x14ac:dyDescent="0.35">
@@ -66603,7 +66730,7 @@
       </c>
       <c r="B6" s="29">
         <f>AVERAGEIF(PRODUCTOS!$Y$2:$Y$1001,"&gt;0",PRODUCTOS!$AA$2:$AA$1001)</f>
-        <v>0.399975785031225</v>
+        <v>0.3999775109303334</v>
       </c>
     </row>
     <row r="7" spans="1:4" x14ac:dyDescent="0.35">
